--- a/見積もり/NTTDU様-案件管理-概算見積もり_最新.xlsx
+++ b/見積もり/NTTDU様-案件管理-概算見積もり_最新.xlsx
@@ -8,15 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ishid\Desktop\project_management\見積もり\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3827C68-DF4F-4518-9694-07033EF66A0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6760448-E5F0-4FD3-AC13-E37414981CEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{15EF4DE1-B99D-4880-9633-29B1123E0732}"/>
   </bookViews>
   <sheets>
-    <sheet name="新入社員研修" sheetId="4" r:id="rId1"/>
-    <sheet name="案件企画・講師アサイン" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet1" sheetId="5" r:id="rId3"/>
+    <sheet name="新入社員研修" sheetId="8" r:id="rId1"/>
+    <sheet name="新入社員研修（詳細）" sheetId="4" r:id="rId2"/>
+    <sheet name="案件企画・講師アサイン" sheetId="2" r:id="rId3"/>
+    <sheet name="項目表" sheetId="5" r:id="rId4"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">新入社員研修!$B$2:$D$398</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -27,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="682" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1476" uniqueCount="175">
   <si>
     <t>備考</t>
     <rPh sb="0" eb="2">
@@ -1643,38 +1647,6 @@
   <si>
     <t>以下の流れを検討する。
 # 検討対象
-・登録ルール・方法の整理
-# 作成ツール/システム
-　SMSの自動化による対応</t>
-    <rPh sb="0" eb="2">
-      <t>イカ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>ナガ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>ケントウ</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="26" eb="28">
-      <t>ホウホウ</t>
-    </rPh>
-    <rPh sb="29" eb="31">
-      <t>セイリ</t>
-    </rPh>
-    <rPh sb="50" eb="53">
-      <t>ジドウカ</t>
-    </rPh>
-    <rPh sb="56" eb="58">
-      <t>タイオウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>以下の流れを検討する。
-# 検討対象
 ・共有ルール・方法の整理
 # 作成ツール/システム
 　なし</t>
@@ -2275,12 +2247,193 @@
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>以下の流れを確認し、改善する。
+マテリアルの管理～マテリアルの作成～マテリアルの確認～マテリアルのデプロイ～マテリアルのデプロイ後の確認</t>
+    <rPh sb="0" eb="2">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ナガ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>カイゼン</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>カンリ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="64" eb="65">
+      <t>ゴ</t>
+    </rPh>
+    <rPh sb="66" eb="68">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>以下の流れを確認し、改善する。
+教材の管理～コース別データの作成～コース別データの確認</t>
+    <rPh sb="25" eb="26">
+      <t>ベツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>以下の流れを確認し、改善する。
+マスター（年度別）の作成～マスター（年度別）の確認
+クラス（年度別）の作成～クラス（年度別）の確認
+ユーザー（年度別）の作成～ユーザー（年度別）の確認</t>
+    <rPh sb="26" eb="28">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="46" eb="49">
+      <t>ネンドベツ</t>
+    </rPh>
+    <rPh sb="51" eb="53">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="63" eb="65">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>以下の流れを確認し、改善する。
+テンプレートの作成～テンプレートの確認
+スペース（年度別）の作成～スペース（年度別）の確認
+コース別データのデプロイ～コース別データのデプロイ後の確認
+ユーザー（年度別）の作成～ユーザー（年度別）の確認</t>
+    <rPh sb="23" eb="24">
+      <t>サク</t>
+    </rPh>
+    <rPh sb="39" eb="42">
+      <t>ネンドベツ</t>
+    </rPh>
+    <rPh sb="65" eb="66">
+      <t>ベツ</t>
+    </rPh>
+    <rPh sb="73" eb="75">
+      <t>キョウザイ</t>
+    </rPh>
+    <rPh sb="87" eb="88">
+      <t>ゴ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>以下の流れを確認し、改善する。
+実施～集計～共有～フィードバック</t>
+    <rPh sb="16" eb="18">
+      <t>ジッシ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>シュウケイ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>キョウユウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>以下の流れを確認し、改善する。
+実施～集計～督促～再集計～共有～フィードバック</t>
+    <rPh sb="16" eb="18">
+      <t>ジッシ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>トクソク</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>シュウケイ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>キョウユウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>以下の流れを確認し、改善する。
+対応～登録～共有～更新～再共有</t>
+    <rPh sb="16" eb="18">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>キョウユウ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>キョウユウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>以下の流れを確認し、改善する。
+実施～集計～督促～再集計～共有～レポート化</t>
+  </si>
+  <si>
+    <t>以下の流れを検討する。
+# 検討対象
+・登録ルール・方法の整理（kintoneのAI機能を検証するかも）
+# 作成ツール/システム
+　SMSの自動化による対応</t>
+    <rPh sb="0" eb="2">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ナガ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ケントウ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>ホウホウ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>セイリ</t>
+    </rPh>
+    <rPh sb="42" eb="44">
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>ケンショウ</t>
+    </rPh>
+    <rPh sb="71" eb="74">
+      <t>ジドウカ</t>
+    </rPh>
+    <rPh sb="77" eb="79">
+      <t>タイオウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2317,6 +2470,13 @@
       <color theme="1"/>
       <name val="Segoe UI Symbol"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
     </font>
   </fonts>
   <fills count="4">
@@ -2449,7 +2609,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2531,11 +2691,14 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -2546,6 +2709,15 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -2555,14 +2727,14 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2877,6 +3049,2966 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43519A57-0157-4E94-A8ED-B58B74152C39}">
+  <sheetPr filterMode="1"/>
+  <dimension ref="B2:D400"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="8.796875" style="1"/>
+    <col min="2" max="2" width="19" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="78.296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.3984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.8984375" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="8.796875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B2" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="24" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4" ht="54" x14ac:dyDescent="0.45">
+      <c r="B3" s="41" t="s">
+        <v>122</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="D3" s="6">
+        <f>SUM('新入社員研修（詳細）'!H3:H36)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B4" s="18"/>
+      <c r="C4" s="27" t="s">
+        <v>130</v>
+      </c>
+      <c r="D4" s="40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B5" s="18"/>
+      <c r="C5" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="D5" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B6" s="18"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B7" s="18"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B8" s="18"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B9" s="18"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B10" s="18"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B11" s="18"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B12" s="18"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B13" s="18"/>
+      <c r="C13" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="D13" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B14" s="18"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B15" s="18"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B16" s="18"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B17" s="18"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B18" s="18"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B19" s="18"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B20" s="18"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B21" s="18"/>
+      <c r="C21" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="D21" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B22" s="18"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B23" s="18"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B24" s="18"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B25" s="18"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B26" s="18"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B27" s="18"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B28" s="18"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B29" s="18"/>
+      <c r="C29" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D29" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B30" s="18"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B31" s="18"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B32" s="18"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B33" s="18"/>
+      <c r="C33" s="3"/>
+      <c r="D33" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B34" s="18"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B35" s="18"/>
+      <c r="C35" s="3"/>
+      <c r="D35" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B36" s="18"/>
+      <c r="C36" s="3"/>
+      <c r="D36" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:4" ht="36" x14ac:dyDescent="0.45">
+      <c r="B37" s="41" t="s">
+        <v>123</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="D37" s="6">
+        <f>SUM('新入社員研修（詳細）'!H37:H61)</f>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="38" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B38" s="18"/>
+      <c r="C38" s="27" t="s">
+        <v>132</v>
+      </c>
+      <c r="D38" s="40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B39" s="18"/>
+      <c r="C39" s="3"/>
+      <c r="D39" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B40" s="18"/>
+      <c r="C40" s="3"/>
+      <c r="D40" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B41" s="18"/>
+      <c r="C41" s="3"/>
+      <c r="D41" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B42" s="18"/>
+      <c r="C42" s="3"/>
+      <c r="D42" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B43" s="18"/>
+      <c r="C43" s="3"/>
+      <c r="D43" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B44" s="18"/>
+      <c r="C44" s="3"/>
+      <c r="D44" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B45" s="18"/>
+      <c r="C45" s="3"/>
+      <c r="D45" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B46" s="18"/>
+      <c r="C46" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="D46" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B47" s="18"/>
+      <c r="C47" s="3"/>
+      <c r="D47" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="48" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B48" s="18"/>
+      <c r="C48" s="3"/>
+      <c r="D48" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B49" s="18"/>
+      <c r="C49" s="3"/>
+      <c r="D49" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B50" s="18"/>
+      <c r="C50" s="3"/>
+      <c r="D50" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B51" s="18"/>
+      <c r="C51" s="3"/>
+      <c r="D51" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B52" s="18"/>
+      <c r="C52" s="3"/>
+      <c r="D52" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B53" s="18"/>
+      <c r="C53" s="3"/>
+      <c r="D53" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B54" s="18"/>
+      <c r="C54" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="D54" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B55" s="18"/>
+      <c r="C55" s="3"/>
+      <c r="D55" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="56" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B56" s="18"/>
+      <c r="C56" s="3"/>
+      <c r="D56" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B57" s="18"/>
+      <c r="C57" s="3"/>
+      <c r="D57" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B58" s="18"/>
+      <c r="C58" s="3"/>
+      <c r="D58" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="59" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B59" s="18"/>
+      <c r="C59" s="3"/>
+      <c r="D59" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B60" s="18"/>
+      <c r="C60" s="3"/>
+      <c r="D60" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B61" s="19"/>
+      <c r="C61" s="3"/>
+      <c r="D61" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="2:4" ht="72" x14ac:dyDescent="0.45">
+      <c r="B62" s="41" t="s">
+        <v>101</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="D62" s="6">
+        <f>SUM('新入社員研修（詳細）'!H62:H110)</f>
+        <v>72</v>
+      </c>
+    </row>
+    <row r="63" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B63" s="18"/>
+      <c r="C63" s="27" t="s">
+        <v>160</v>
+      </c>
+      <c r="D63" s="40">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B64" s="18"/>
+      <c r="C64" s="3"/>
+      <c r="D64" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="65" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B65" s="18"/>
+      <c r="C65" s="3"/>
+      <c r="D65" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B66" s="18"/>
+      <c r="C66" s="3"/>
+      <c r="D66" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B67" s="18"/>
+      <c r="C67" s="3"/>
+      <c r="D67" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="68" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B68" s="18"/>
+      <c r="C68" s="3"/>
+      <c r="D68" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B69" s="18"/>
+      <c r="C69" s="3"/>
+      <c r="D69" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B70" s="18"/>
+      <c r="C70" s="3"/>
+      <c r="D70" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B71" s="18"/>
+      <c r="C71" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="D71" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B72" s="18"/>
+      <c r="C72" s="3"/>
+      <c r="D72" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B73" s="18"/>
+      <c r="C73" s="3"/>
+      <c r="D73" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B74" s="18"/>
+      <c r="C74" s="3"/>
+      <c r="D74" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="75" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B75" s="18"/>
+      <c r="C75" s="3"/>
+      <c r="D75" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="76" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B76" s="18"/>
+      <c r="C76" s="3"/>
+      <c r="D76" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B77" s="18"/>
+      <c r="C77" s="3"/>
+      <c r="D77" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B78" s="18"/>
+      <c r="C78" s="3"/>
+      <c r="D78" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B79" s="18"/>
+      <c r="C79" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D79" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="80" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B80" s="18"/>
+      <c r="C80" s="3"/>
+      <c r="D80" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="81" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B81" s="18"/>
+      <c r="C81" s="3"/>
+      <c r="D81" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B82" s="18"/>
+      <c r="C82" s="3"/>
+      <c r="D82" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="83" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B83" s="18"/>
+      <c r="C83" s="3"/>
+      <c r="D83" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B84" s="18"/>
+      <c r="C84" s="3"/>
+      <c r="D84" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B85" s="18"/>
+      <c r="C85" s="3"/>
+      <c r="D85" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B86" s="18"/>
+      <c r="C86" s="3"/>
+      <c r="D86" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B87" s="18"/>
+      <c r="C87" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="D87" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B88" s="18"/>
+      <c r="C88" s="3"/>
+      <c r="D88" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="89" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B89" s="18"/>
+      <c r="C89" s="3"/>
+      <c r="D89" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B90" s="18"/>
+      <c r="C90" s="3"/>
+      <c r="D90" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="91" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B91" s="18"/>
+      <c r="C91" s="3"/>
+      <c r="D91" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="92" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B92" s="18"/>
+      <c r="C92" s="3"/>
+      <c r="D92" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B93" s="18"/>
+      <c r="C93" s="3"/>
+      <c r="D93" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B94" s="18"/>
+      <c r="C94" s="3"/>
+      <c r="D94" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B95" s="18"/>
+      <c r="C95" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="D95" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B96" s="18"/>
+      <c r="C96" s="3"/>
+      <c r="D96" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="97" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B97" s="18"/>
+      <c r="C97" s="3"/>
+      <c r="D97" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B98" s="18"/>
+      <c r="C98" s="3"/>
+      <c r="D98" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="99" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B99" s="18"/>
+      <c r="C99" s="3"/>
+      <c r="D99" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="100" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B100" s="18"/>
+      <c r="C100" s="3"/>
+      <c r="D100" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B101" s="18"/>
+      <c r="C101" s="3"/>
+      <c r="D101" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B102" s="18"/>
+      <c r="C102" s="3"/>
+      <c r="D102" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B103" s="18"/>
+      <c r="C103" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="D103" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B104" s="18"/>
+      <c r="C104" s="3"/>
+      <c r="D104" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B105" s="18"/>
+      <c r="C105" s="3"/>
+      <c r="D105" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B106" s="18"/>
+      <c r="C106" s="3"/>
+      <c r="D106" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B107" s="18"/>
+      <c r="C107" s="3"/>
+      <c r="D107" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B108" s="18"/>
+      <c r="C108" s="3"/>
+      <c r="D108" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B109" s="18"/>
+      <c r="C109" s="3"/>
+      <c r="D109" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B110" s="19"/>
+      <c r="C110" s="3"/>
+      <c r="D110" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="2:4" ht="90" x14ac:dyDescent="0.45">
+      <c r="B111" s="41" t="s">
+        <v>102</v>
+      </c>
+      <c r="C111" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="D111" s="6">
+        <f>SUM('新入社員研修（詳細）'!H111:H175)</f>
+        <v>68</v>
+      </c>
+    </row>
+    <row r="112" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B112" s="18"/>
+      <c r="C112" s="27" t="s">
+        <v>133</v>
+      </c>
+      <c r="D112" s="40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B113" s="18"/>
+      <c r="C113" s="3"/>
+      <c r="D113" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B114" s="18"/>
+      <c r="C114" s="3"/>
+      <c r="D114" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B115" s="18"/>
+      <c r="C115" s="3"/>
+      <c r="D115" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B116" s="18"/>
+      <c r="C116" s="3"/>
+      <c r="D116" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B117" s="18"/>
+      <c r="C117" s="3"/>
+      <c r="D117" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B118" s="18"/>
+      <c r="C118" s="3"/>
+      <c r="D118" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B119" s="18"/>
+      <c r="C119" s="3"/>
+      <c r="D119" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B120" s="18"/>
+      <c r="C120" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="D120" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B121" s="18"/>
+      <c r="C121" s="3"/>
+      <c r="D121" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B122" s="18"/>
+      <c r="C122" s="3"/>
+      <c r="D122" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B123" s="18"/>
+      <c r="C123" s="3"/>
+      <c r="D123" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B124" s="18"/>
+      <c r="C124" s="3"/>
+      <c r="D124" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B125" s="18"/>
+      <c r="C125" s="3"/>
+      <c r="D125" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B126" s="18"/>
+      <c r="C126" s="3"/>
+      <c r="D126" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B127" s="18"/>
+      <c r="C127" s="3"/>
+      <c r="D127" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B128" s="18"/>
+      <c r="C128" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="D128" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B129" s="18"/>
+      <c r="C129" s="3"/>
+      <c r="D129" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="130" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B130" s="18"/>
+      <c r="C130" s="3"/>
+      <c r="D130" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B131" s="18"/>
+      <c r="C131" s="3"/>
+      <c r="D131" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="132" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B132" s="18"/>
+      <c r="C132" s="3"/>
+      <c r="D132" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="133" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B133" s="18"/>
+      <c r="C133" s="3"/>
+      <c r="D133" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B134" s="18"/>
+      <c r="C134" s="3"/>
+      <c r="D134" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B135" s="18"/>
+      <c r="C135" s="3"/>
+      <c r="D135" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B136" s="18"/>
+      <c r="C136" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="D136" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B137" s="18"/>
+      <c r="C137" s="3"/>
+      <c r="D137" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="138" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B138" s="18"/>
+      <c r="C138" s="3"/>
+      <c r="D138" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B139" s="18"/>
+      <c r="C139" s="3"/>
+      <c r="D139" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="140" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B140" s="18"/>
+      <c r="C140" s="3"/>
+      <c r="D140" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="141" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B141" s="18"/>
+      <c r="C141" s="3"/>
+      <c r="D141" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B142" s="18"/>
+      <c r="C142" s="3"/>
+      <c r="D142" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B143" s="18"/>
+      <c r="C143" s="3"/>
+      <c r="D143" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B144" s="18"/>
+      <c r="C144" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D144" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B145" s="18"/>
+      <c r="C145" s="3"/>
+      <c r="D145" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B146" s="18"/>
+      <c r="C146" s="3"/>
+      <c r="D146" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B147" s="18"/>
+      <c r="C147" s="3"/>
+      <c r="D147" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B148" s="18"/>
+      <c r="C148" s="3"/>
+      <c r="D148" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B149" s="18"/>
+      <c r="C149" s="3"/>
+      <c r="D149" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B150" s="18"/>
+      <c r="C150" s="3"/>
+      <c r="D150" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B151" s="18"/>
+      <c r="C151" s="3"/>
+      <c r="D151" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B152" s="18"/>
+      <c r="C152" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="D152" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B153" s="18"/>
+      <c r="C153" s="3"/>
+      <c r="D153" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B154" s="18"/>
+      <c r="C154" s="3"/>
+      <c r="D154" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B155" s="18"/>
+      <c r="C155" s="3"/>
+      <c r="D155" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B156" s="18"/>
+      <c r="C156" s="3"/>
+      <c r="D156" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B157" s="18"/>
+      <c r="C157" s="3"/>
+      <c r="D157" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B158" s="18"/>
+      <c r="C158" s="3"/>
+      <c r="D158" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B159" s="18"/>
+      <c r="C159" s="3"/>
+      <c r="D159" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B160" s="18"/>
+      <c r="C160" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="D160" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="161" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B161" s="18"/>
+      <c r="C161" s="3"/>
+      <c r="D161" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="162" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B162" s="18"/>
+      <c r="C162" s="3"/>
+      <c r="D162" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B163" s="18"/>
+      <c r="C163" s="3"/>
+      <c r="D163" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="164" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B164" s="18"/>
+      <c r="C164" s="3"/>
+      <c r="D164" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="165" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B165" s="18"/>
+      <c r="C165" s="3"/>
+      <c r="D165" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B166" s="18"/>
+      <c r="C166" s="3"/>
+      <c r="D166" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="167" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B167" s="18"/>
+      <c r="C167" s="3"/>
+      <c r="D167" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="168" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B168" s="18"/>
+      <c r="C168" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D168" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="169" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B169" s="18"/>
+      <c r="C169" s="3"/>
+      <c r="D169" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="170" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B170" s="18"/>
+      <c r="C170" s="3"/>
+      <c r="D170" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B171" s="18"/>
+      <c r="C171" s="3"/>
+      <c r="D171" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="172" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B172" s="18"/>
+      <c r="C172" s="3"/>
+      <c r="D172" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="173" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B173" s="18"/>
+      <c r="C173" s="3"/>
+      <c r="D173" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="174" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B174" s="18"/>
+      <c r="C174" s="3"/>
+      <c r="D174" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="175" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B175" s="19"/>
+      <c r="C175" s="3"/>
+      <c r="D175" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="176" spans="2:4" ht="36" x14ac:dyDescent="0.45">
+      <c r="B176" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C176" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="D176" s="6">
+        <f>SUM('新入社員研修（詳細）'!H176:H208)</f>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="177" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B177" s="12"/>
+      <c r="C177" s="27" t="s">
+        <v>137</v>
+      </c>
+      <c r="D177" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B178" s="18"/>
+      <c r="C178" s="3"/>
+      <c r="D178" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B179" s="18"/>
+      <c r="C179" s="3"/>
+      <c r="D179" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B180" s="18"/>
+      <c r="C180" s="3"/>
+      <c r="D180" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B181" s="18"/>
+      <c r="C181" s="3"/>
+      <c r="D181" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B182" s="18"/>
+      <c r="C182" s="3"/>
+      <c r="D182" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B183" s="18"/>
+      <c r="C183" s="3"/>
+      <c r="D183" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B184" s="18"/>
+      <c r="C184" s="3"/>
+      <c r="D184" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B185" s="12"/>
+      <c r="C185" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="D185" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="186" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B186" s="18"/>
+      <c r="C186" s="3"/>
+      <c r="D186" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="187" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B187" s="18"/>
+      <c r="C187" s="3"/>
+      <c r="D187" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B188" s="18"/>
+      <c r="C188" s="3"/>
+      <c r="D188" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="189" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B189" s="18"/>
+      <c r="C189" s="3"/>
+      <c r="D189" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="190" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B190" s="18"/>
+      <c r="C190" s="3"/>
+      <c r="D190" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="191" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B191" s="18"/>
+      <c r="C191" s="3"/>
+      <c r="D191" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="192" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B192" s="18"/>
+      <c r="C192" s="3"/>
+      <c r="D192" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="193" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B193" s="12"/>
+      <c r="C193" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="D193" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="194" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B194" s="18"/>
+      <c r="C194" s="3"/>
+      <c r="D194" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B195" s="18"/>
+      <c r="C195" s="3"/>
+      <c r="D195" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B196" s="18"/>
+      <c r="C196" s="3"/>
+      <c r="D196" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B197" s="18"/>
+      <c r="C197" s="3"/>
+      <c r="D197" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B198" s="18"/>
+      <c r="C198" s="3"/>
+      <c r="D198" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B199" s="18"/>
+      <c r="C199" s="3"/>
+      <c r="D199" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B200" s="18"/>
+      <c r="C200" s="3"/>
+      <c r="D200" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B201" s="18"/>
+      <c r="C201" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D201" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B202" s="18"/>
+      <c r="C202" s="3"/>
+      <c r="D202" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B203" s="18"/>
+      <c r="C203" s="3"/>
+      <c r="D203" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B204" s="18"/>
+      <c r="C204" s="3"/>
+      <c r="D204" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B205" s="18"/>
+      <c r="C205" s="3"/>
+      <c r="D205" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B206" s="18"/>
+      <c r="C206" s="3"/>
+      <c r="D206" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B207" s="18"/>
+      <c r="C207" s="3"/>
+      <c r="D207" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B208" s="19"/>
+      <c r="C208" s="3"/>
+      <c r="D208" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209" spans="2:4" ht="36" x14ac:dyDescent="0.45">
+      <c r="B209" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C209" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="D209" s="6">
+        <f>SUM('新入社員研修（詳細）'!H209:H257)</f>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="210" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B210" s="12"/>
+      <c r="C210" s="27" t="s">
+        <v>137</v>
+      </c>
+      <c r="D210" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B211" s="18"/>
+      <c r="C211" s="3"/>
+      <c r="D211" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B212" s="18"/>
+      <c r="C212" s="3"/>
+      <c r="D212" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B213" s="18"/>
+      <c r="C213" s="3"/>
+      <c r="D213" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B214" s="18"/>
+      <c r="C214" s="3"/>
+      <c r="D214" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B215" s="18"/>
+      <c r="C215" s="3"/>
+      <c r="D215" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B216" s="18"/>
+      <c r="C216" s="3"/>
+      <c r="D216" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B217" s="18"/>
+      <c r="C217" s="3"/>
+      <c r="D217" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B218" s="12"/>
+      <c r="C218" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="D218" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="219" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B219" s="18"/>
+      <c r="C219" s="3"/>
+      <c r="D219" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="220" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B220" s="18"/>
+      <c r="C220" s="3"/>
+      <c r="D220" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B221" s="18"/>
+      <c r="C221" s="3"/>
+      <c r="D221" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="222" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B222" s="18"/>
+      <c r="C222" s="3"/>
+      <c r="D222" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="223" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B223" s="18"/>
+      <c r="C223" s="3"/>
+      <c r="D223" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="224" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B224" s="18"/>
+      <c r="C224" s="3"/>
+      <c r="D224" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="225" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B225" s="18"/>
+      <c r="C225" s="3"/>
+      <c r="D225" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="226" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B226" s="12"/>
+      <c r="C226" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D226" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B227" s="18"/>
+      <c r="C227" s="3"/>
+      <c r="D227" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B228" s="18"/>
+      <c r="C228" s="3"/>
+      <c r="D228" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B229" s="18"/>
+      <c r="C229" s="3"/>
+      <c r="D229" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B230" s="18"/>
+      <c r="C230" s="3"/>
+      <c r="D230" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B231" s="18"/>
+      <c r="C231" s="3"/>
+      <c r="D231" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B232" s="18"/>
+      <c r="C232" s="3"/>
+      <c r="D232" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B233" s="18"/>
+      <c r="C233" s="3"/>
+      <c r="D233" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B234" s="18"/>
+      <c r="C234" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D234" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B235" s="18"/>
+      <c r="C235" s="3"/>
+      <c r="D235" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B236" s="18"/>
+      <c r="C236" s="3"/>
+      <c r="D236" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B237" s="18"/>
+      <c r="C237" s="3"/>
+      <c r="D237" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B238" s="18"/>
+      <c r="C238" s="3"/>
+      <c r="D238" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B239" s="18"/>
+      <c r="C239" s="3"/>
+      <c r="D239" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B240" s="18"/>
+      <c r="C240" s="3"/>
+      <c r="D240" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B241" s="18"/>
+      <c r="C241" s="3"/>
+      <c r="D241" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B242" s="18"/>
+      <c r="C242" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="D242" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="243" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B243" s="18"/>
+      <c r="C243" s="3"/>
+      <c r="D243" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="244" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B244" s="18"/>
+      <c r="C244" s="3"/>
+      <c r="D244" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="245" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B245" s="18"/>
+      <c r="C245" s="3"/>
+      <c r="D245" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="246" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B246" s="18"/>
+      <c r="C246" s="3"/>
+      <c r="D246" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="247" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B247" s="18"/>
+      <c r="C247" s="3"/>
+      <c r="D247" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="248" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B248" s="18"/>
+      <c r="C248" s="3"/>
+      <c r="D248" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="249" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B249" s="18"/>
+      <c r="C249" s="3"/>
+      <c r="D249" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="250" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B250" s="18"/>
+      <c r="C250" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D250" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B251" s="18"/>
+      <c r="C251" s="3"/>
+      <c r="D251" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="252" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B252" s="18"/>
+      <c r="C252" s="3"/>
+      <c r="D252" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B253" s="18"/>
+      <c r="C253" s="3"/>
+      <c r="D253" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="254" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B254" s="18"/>
+      <c r="C254" s="3"/>
+      <c r="D254" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="255" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B255" s="18"/>
+      <c r="C255" s="3"/>
+      <c r="D255" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="256" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B256" s="18"/>
+      <c r="C256" s="3"/>
+      <c r="D256" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="257" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B257" s="19"/>
+      <c r="C257" s="3"/>
+      <c r="D257" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="258" spans="2:4" ht="36" x14ac:dyDescent="0.45">
+      <c r="B258" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C258" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="D258" s="6">
+        <f>SUM('新入社員研修（詳細）'!H258:H298)</f>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="259" spans="2:4" ht="108" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B259" s="12"/>
+      <c r="C259" s="27" t="s">
+        <v>157</v>
+      </c>
+      <c r="D259" s="40">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="260" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B260" s="18"/>
+      <c r="D260" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="261" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B261" s="18"/>
+      <c r="C261" s="3"/>
+      <c r="D261" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B262" s="18"/>
+      <c r="C262" s="3"/>
+      <c r="D262" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="263" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B263" s="18"/>
+      <c r="C263" s="3"/>
+      <c r="D263" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="264" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B264" s="18"/>
+      <c r="C264" s="3"/>
+      <c r="D264" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="265" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B265" s="18"/>
+      <c r="C265" s="3"/>
+      <c r="D265" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="266" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B266" s="18"/>
+      <c r="C266" s="3"/>
+      <c r="D266" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="267" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B267" s="12"/>
+      <c r="C267" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="D267" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="268" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B268" s="18"/>
+      <c r="C268" s="3"/>
+      <c r="D268" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="269" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B269" s="18"/>
+      <c r="C269" s="3"/>
+      <c r="D269" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="270" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B270" s="18"/>
+      <c r="C270" s="3"/>
+      <c r="D270" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="271" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B271" s="18"/>
+      <c r="C271" s="3"/>
+      <c r="D271" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="272" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B272" s="18"/>
+      <c r="C272" s="3"/>
+      <c r="D272" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="273" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B273" s="18"/>
+      <c r="C273" s="3"/>
+      <c r="D273" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="274" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B274" s="18"/>
+      <c r="C274" s="3"/>
+      <c r="D274" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="275" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B275" s="18"/>
+      <c r="C275" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="D275" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="276" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B276" s="18"/>
+      <c r="C276" s="3"/>
+      <c r="D276" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="277" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B277" s="18"/>
+      <c r="C277" s="3"/>
+      <c r="D277" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="278" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B278" s="18"/>
+      <c r="C278" s="3"/>
+      <c r="D278" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="279" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B279" s="18"/>
+      <c r="C279" s="3"/>
+      <c r="D279" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="280" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B280" s="18"/>
+      <c r="C280" s="3"/>
+      <c r="D280" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B281" s="18"/>
+      <c r="C281" s="3"/>
+      <c r="D281" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="282" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B282" s="18"/>
+      <c r="C282" s="3"/>
+      <c r="D282" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="283" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B283" s="18"/>
+      <c r="C283" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="D283" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="284" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B284" s="18"/>
+      <c r="D284" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="285" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B285" s="18"/>
+      <c r="C285" s="3"/>
+      <c r="D285" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="286" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B286" s="18"/>
+      <c r="C286" s="3"/>
+      <c r="D286" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="287" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B287" s="18"/>
+      <c r="C287" s="3"/>
+      <c r="D287" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="288" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B288" s="18"/>
+      <c r="C288" s="3"/>
+      <c r="D288" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="289" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B289" s="18"/>
+      <c r="C289" s="3"/>
+      <c r="D289" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="290" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B290" s="18"/>
+      <c r="C290" s="3"/>
+      <c r="D290" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="291" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B291" s="18"/>
+      <c r="C291" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D291" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="292" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B292" s="18"/>
+      <c r="D292" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="293" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B293" s="18"/>
+      <c r="C293" s="3"/>
+      <c r="D293" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="294" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B294" s="18"/>
+      <c r="C294" s="3"/>
+      <c r="D294" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="295" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B295" s="18"/>
+      <c r="C295" s="3"/>
+      <c r="D295" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="296" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B296" s="18"/>
+      <c r="C296" s="3"/>
+      <c r="D296" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="297" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B297" s="18"/>
+      <c r="C297" s="3"/>
+      <c r="D297" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="298" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B298" s="18"/>
+      <c r="C298" s="3"/>
+      <c r="D298" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="299" spans="2:4" ht="36" x14ac:dyDescent="0.45">
+      <c r="B299" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C299" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="D299" s="6">
+        <f>SUM('新入社員研修（詳細）'!H299:H347)</f>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="300" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B300" s="12"/>
+      <c r="C300" s="27" t="s">
+        <v>137</v>
+      </c>
+      <c r="D300" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="301" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B301" s="18"/>
+      <c r="C301" s="3"/>
+      <c r="D301" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="302" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B302" s="18"/>
+      <c r="C302" s="3"/>
+      <c r="D302" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="303" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B303" s="18"/>
+      <c r="C303" s="3"/>
+      <c r="D303" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="304" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B304" s="18"/>
+      <c r="C304" s="3"/>
+      <c r="D304" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="305" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B305" s="18"/>
+      <c r="C305" s="3"/>
+      <c r="D305" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="306" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B306" s="18"/>
+      <c r="C306" s="3"/>
+      <c r="D306" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="307" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B307" s="18"/>
+      <c r="C307" s="3"/>
+      <c r="D307" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="308" spans="2:4" ht="108" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B308" s="12"/>
+      <c r="C308" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="D308" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="309" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B309" s="18"/>
+      <c r="C309" s="3"/>
+      <c r="D309" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="310" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B310" s="18"/>
+      <c r="C310" s="3"/>
+      <c r="D310" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="311" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B311" s="18"/>
+      <c r="C311" s="3"/>
+      <c r="D311" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="312" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B312" s="18"/>
+      <c r="C312" s="3"/>
+      <c r="D312" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="313" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B313" s="18"/>
+      <c r="C313" s="3"/>
+      <c r="D313" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="314" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B314" s="18"/>
+      <c r="C314" s="3"/>
+      <c r="D314" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="315" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B315" s="18"/>
+      <c r="C315" s="3"/>
+      <c r="D315" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="316" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B316" s="12"/>
+      <c r="C316" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D316" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="317" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B317" s="18"/>
+      <c r="C317" s="3"/>
+      <c r="D317" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="318" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B318" s="18"/>
+      <c r="C318" s="3"/>
+      <c r="D318" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="319" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B319" s="18"/>
+      <c r="C319" s="3"/>
+      <c r="D319" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="320" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B320" s="18"/>
+      <c r="C320" s="3"/>
+      <c r="D320" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="321" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B321" s="18"/>
+      <c r="C321" s="3"/>
+      <c r="D321" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="322" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B322" s="18"/>
+      <c r="C322" s="3"/>
+      <c r="D322" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="323" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B323" s="18"/>
+      <c r="C323" s="3"/>
+      <c r="D323" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="324" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B324" s="12"/>
+      <c r="C324" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D324" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="325" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B325" s="18"/>
+      <c r="C325" s="3"/>
+      <c r="D325" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="326" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B326" s="18"/>
+      <c r="C326" s="3"/>
+      <c r="D326" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="327" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B327" s="18"/>
+      <c r="C327" s="3"/>
+      <c r="D327" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="328" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B328" s="18"/>
+      <c r="C328" s="3"/>
+      <c r="D328" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="329" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B329" s="18"/>
+      <c r="C329" s="3"/>
+      <c r="D329" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="330" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B330" s="18"/>
+      <c r="C330" s="3"/>
+      <c r="D330" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="331" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B331" s="18"/>
+      <c r="C331" s="3"/>
+      <c r="D331" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="332" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B332" s="12"/>
+      <c r="C332" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="D332" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="333" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B333" s="18"/>
+      <c r="C333" s="3"/>
+      <c r="D333" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="334" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B334" s="18"/>
+      <c r="C334" s="3"/>
+      <c r="D334" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="335" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B335" s="18"/>
+      <c r="C335" s="3"/>
+      <c r="D335" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="336" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B336" s="18"/>
+      <c r="C336" s="3"/>
+      <c r="D336" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="337" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B337" s="18"/>
+      <c r="C337" s="3"/>
+      <c r="D337" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="338" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B338" s="18"/>
+      <c r="C338" s="3"/>
+      <c r="D338" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="339" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B339" s="18"/>
+      <c r="C339" s="3"/>
+      <c r="D339" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="340" spans="2:4" ht="126" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B340" s="12"/>
+      <c r="C340" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="D340" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="341" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B341" s="18"/>
+      <c r="C341" s="3"/>
+      <c r="D341" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="342" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B342" s="18"/>
+      <c r="C342" s="3"/>
+      <c r="D342" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="343" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B343" s="18"/>
+      <c r="C343" s="3"/>
+      <c r="D343" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="344" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B344" s="18"/>
+      <c r="C344" s="3"/>
+      <c r="D344" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="345" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B345" s="18"/>
+      <c r="C345" s="3"/>
+      <c r="D345" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="346" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B346" s="18"/>
+      <c r="C346" s="3"/>
+      <c r="D346" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="347" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B347" s="19"/>
+      <c r="C347" s="3"/>
+      <c r="D347" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="348" spans="2:4" ht="36" x14ac:dyDescent="0.45">
+      <c r="B348" s="41" t="s">
+        <v>19</v>
+      </c>
+      <c r="C348" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="D348" s="6">
+        <f>SUM('新入社員研修（詳細）'!H348:H396)</f>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="349" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B349" s="18"/>
+      <c r="C349" s="27" t="s">
+        <v>137</v>
+      </c>
+      <c r="D349" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="350" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B350" s="18"/>
+      <c r="C350" s="3"/>
+      <c r="D350" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="351" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B351" s="18"/>
+      <c r="C351" s="3"/>
+      <c r="D351" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="352" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B352" s="18"/>
+      <c r="C352" s="3"/>
+      <c r="D352" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="353" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B353" s="18"/>
+      <c r="C353" s="3"/>
+      <c r="D353" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="354" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B354" s="18"/>
+      <c r="C354" s="3"/>
+      <c r="D354" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="355" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B355" s="18"/>
+      <c r="C355" s="3"/>
+      <c r="D355" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="356" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B356" s="18"/>
+      <c r="C356" s="3"/>
+      <c r="D356" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="357" spans="2:4" ht="108" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B357" s="18"/>
+      <c r="C357" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="D357" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="358" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B358" s="18"/>
+      <c r="C358" s="3"/>
+      <c r="D358" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="359" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B359" s="18"/>
+      <c r="C359" s="3"/>
+      <c r="D359" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="360" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B360" s="18"/>
+      <c r="C360" s="3"/>
+      <c r="D360" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="361" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B361" s="18"/>
+      <c r="C361" s="3"/>
+      <c r="D361" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="362" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B362" s="18"/>
+      <c r="C362" s="3"/>
+      <c r="D362" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="363" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B363" s="18"/>
+      <c r="C363" s="3"/>
+      <c r="D363" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="364" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B364" s="18"/>
+      <c r="C364" s="3"/>
+      <c r="D364" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="365" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B365" s="18"/>
+      <c r="C365" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D365" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="366" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B366" s="18"/>
+      <c r="C366" s="3"/>
+      <c r="D366" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="367" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B367" s="18"/>
+      <c r="C367" s="3"/>
+      <c r="D367" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="368" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B368" s="18"/>
+      <c r="C368" s="3"/>
+      <c r="D368" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="369" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B369" s="18"/>
+      <c r="C369" s="3"/>
+      <c r="D369" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="370" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B370" s="18"/>
+      <c r="C370" s="3"/>
+      <c r="D370" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="371" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B371" s="18"/>
+      <c r="C371" s="3"/>
+      <c r="D371" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="372" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B372" s="18"/>
+      <c r="C372" s="3"/>
+      <c r="D372" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="373" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B373" s="18"/>
+      <c r="C373" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D373" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="374" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B374" s="18"/>
+      <c r="C374" s="3"/>
+      <c r="D374" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="375" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B375" s="18"/>
+      <c r="C375" s="3"/>
+      <c r="D375" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="376" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B376" s="18"/>
+      <c r="C376" s="3"/>
+      <c r="D376" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="377" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B377" s="18"/>
+      <c r="C377" s="3"/>
+      <c r="D377" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="378" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B378" s="18"/>
+      <c r="C378" s="3"/>
+      <c r="D378" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="379" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B379" s="18"/>
+      <c r="C379" s="3"/>
+      <c r="D379" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="380" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B380" s="18"/>
+      <c r="C380" s="3"/>
+      <c r="D380" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="381" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B381" s="18"/>
+      <c r="C381" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="D381" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="382" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B382" s="18"/>
+      <c r="C382" s="3"/>
+      <c r="D382" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="383" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B383" s="18"/>
+      <c r="C383" s="3"/>
+      <c r="D383" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="384" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B384" s="18"/>
+      <c r="C384" s="3"/>
+      <c r="D384" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="385" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B385" s="18"/>
+      <c r="C385" s="3"/>
+      <c r="D385" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="386" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B386" s="18"/>
+      <c r="C386" s="3"/>
+      <c r="D386" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="387" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B387" s="18"/>
+      <c r="C387" s="3"/>
+      <c r="D387" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="388" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B388" s="18"/>
+      <c r="C388" s="3"/>
+      <c r="D388" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="389" spans="2:4" ht="126" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B389" s="18"/>
+      <c r="C389" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="D389" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="390" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B390" s="18"/>
+      <c r="C390" s="3"/>
+      <c r="D390" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="391" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B391" s="18"/>
+      <c r="C391" s="3"/>
+      <c r="D391" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="392" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B392" s="18"/>
+      <c r="C392" s="3"/>
+      <c r="D392" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="393" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B393" s="18"/>
+      <c r="C393" s="3"/>
+      <c r="D393" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="394" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B394" s="18"/>
+      <c r="C394" s="3"/>
+      <c r="D394" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="395" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B395" s="18"/>
+      <c r="C395" s="3"/>
+      <c r="D395" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="396" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B396" s="19"/>
+      <c r="C396" s="3"/>
+      <c r="D396" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="397" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="D397" s="7">
+        <f>SUM(D3:D396)</f>
+        <v>680</v>
+      </c>
+    </row>
+    <row r="398" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="D398" s="29">
+        <f>ROUNDUP(D397*1.3,0)</f>
+        <v>884</v>
+      </c>
+    </row>
+    <row r="399" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="D399" s="7">
+        <f>'新入社員研修（詳細）'!H397</f>
+        <v>341</v>
+      </c>
+    </row>
+    <row r="400" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="D400" s="29">
+        <f>'新入社員研修（詳細）'!H398</f>
+        <v>444</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="B2:D398" xr:uid="{43519A57-0157-4E94-A8ED-B58B74152C39}">
+    <filterColumn colId="0">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+  </autoFilter>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0519C31-7F32-441C-8A86-8C46FCB2408F}">
   <dimension ref="B2:H398"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
@@ -2925,8 +6057,8 @@
       <c r="D3" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="E3" s="36" t="s">
-        <v>125</v>
+      <c r="E3" s="23" t="s">
+        <v>72</v>
       </c>
       <c r="F3" s="23" t="s">
         <v>72</v>
@@ -2946,7 +6078,7 @@
       <c r="D4" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E4" s="36" t="s">
+      <c r="E4" s="28" t="s">
         <v>125</v>
       </c>
       <c r="F4" s="23" t="s">
@@ -2967,14 +6099,14 @@
       <c r="D5" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E5" s="36" t="s">
+      <c r="E5" s="28" t="s">
         <v>125</v>
       </c>
       <c r="F5" s="23" t="s">
         <v>72</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H5" s="6">
         <v>2</v>
@@ -2986,9 +6118,11 @@
       <c r="D6" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E6" s="36"/>
-      <c r="F6" s="23" t="s">
-        <v>72</v>
+      <c r="E6" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F6" s="28" t="s">
+        <v>125</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="6">
@@ -3001,9 +6135,11 @@
       <c r="D7" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E7" s="36"/>
-      <c r="F7" s="23" t="s">
-        <v>72</v>
+      <c r="E7" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F7" s="28" t="s">
+        <v>125</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="6">
@@ -3016,9 +6152,11 @@
       <c r="D8" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E8" s="36"/>
-      <c r="F8" s="23" t="s">
-        <v>72</v>
+      <c r="E8" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F8" s="28" t="s">
+        <v>125</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="6">
@@ -3031,9 +6169,11 @@
       <c r="D9" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E9" s="36"/>
-      <c r="F9" s="23" t="s">
-        <v>72</v>
+      <c r="E9" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F9" s="28" t="s">
+        <v>125</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="6">
@@ -3046,9 +6186,11 @@
       <c r="D10" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E10" s="36"/>
-      <c r="F10" s="23" t="s">
-        <v>72</v>
+      <c r="E10" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F10" s="28" t="s">
+        <v>125</v>
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="6">
@@ -3061,9 +6203,11 @@
       <c r="D11" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E11" s="36"/>
-      <c r="F11" s="23" t="s">
-        <v>72</v>
+      <c r="E11" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F11" s="28" t="s">
+        <v>125</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="6">
@@ -3076,9 +6220,11 @@
       <c r="D12" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E12" s="36"/>
-      <c r="F12" s="23" t="s">
-        <v>72</v>
+      <c r="E12" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F12" s="28" t="s">
+        <v>125</v>
       </c>
       <c r="G12" s="3"/>
       <c r="H12" s="6">
@@ -3093,14 +6239,14 @@
       <c r="D13" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E13" s="36" t="s">
-        <v>125</v>
+      <c r="E13" s="23" t="s">
+        <v>72</v>
       </c>
       <c r="F13" s="23" t="s">
         <v>72</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H13" s="6">
         <v>1</v>
@@ -3112,9 +6258,11 @@
       <c r="D14" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E14" s="36"/>
-      <c r="F14" s="23" t="s">
-        <v>72</v>
+      <c r="E14" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F14" s="28" t="s">
+        <v>125</v>
       </c>
       <c r="G14" s="3"/>
       <c r="H14" s="6">
@@ -3127,8 +6275,10 @@
       <c r="D15" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E15" s="36"/>
-      <c r="F15" s="36" t="s">
+      <c r="E15" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F15" s="28" t="s">
         <v>125</v>
       </c>
       <c r="G15" s="3"/>
@@ -3142,9 +6292,11 @@
       <c r="D16" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E16" s="36"/>
-      <c r="F16" s="23" t="s">
-        <v>72</v>
+      <c r="E16" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F16" s="28" t="s">
+        <v>125</v>
       </c>
       <c r="G16" s="3"/>
       <c r="H16" s="6">
@@ -3157,9 +6309,11 @@
       <c r="D17" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E17" s="36"/>
-      <c r="F17" s="23" t="s">
-        <v>72</v>
+      <c r="E17" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F17" s="28" t="s">
+        <v>125</v>
       </c>
       <c r="G17" s="3"/>
       <c r="H17" s="6">
@@ -3172,9 +6326,11 @@
       <c r="D18" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E18" s="36"/>
-      <c r="F18" s="23" t="s">
-        <v>72</v>
+      <c r="E18" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F18" s="28" t="s">
+        <v>125</v>
       </c>
       <c r="G18" s="3"/>
       <c r="H18" s="6">
@@ -3187,9 +6343,11 @@
       <c r="D19" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E19" s="36"/>
-      <c r="F19" s="23" t="s">
-        <v>72</v>
+      <c r="E19" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F19" s="28" t="s">
+        <v>125</v>
       </c>
       <c r="G19" s="3"/>
       <c r="H19" s="6">
@@ -3202,9 +6360,11 @@
       <c r="D20" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E20" s="36"/>
-      <c r="F20" s="23" t="s">
-        <v>72</v>
+      <c r="E20" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F20" s="28" t="s">
+        <v>125</v>
       </c>
       <c r="G20" s="3"/>
       <c r="H20" s="6">
@@ -3219,10 +6379,12 @@
       <c r="D21" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E21" s="36" t="s">
-        <v>125</v>
-      </c>
-      <c r="F21" s="23"/>
+      <c r="E21" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F21" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G21" s="3" t="s">
         <v>131</v>
       </c>
@@ -3236,8 +6398,12 @@
       <c r="D22" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E22" s="36"/>
-      <c r="F22" s="23"/>
+      <c r="E22" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F22" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G22" s="3"/>
       <c r="H22" s="6">
         <v>0</v>
@@ -3249,8 +6415,12 @@
       <c r="D23" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E23" s="36"/>
-      <c r="F23" s="23"/>
+      <c r="E23" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F23" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G23" s="3"/>
       <c r="H23" s="6">
         <v>0</v>
@@ -3262,8 +6432,12 @@
       <c r="D24" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E24" s="36"/>
-      <c r="F24" s="23"/>
+      <c r="E24" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F24" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G24" s="3"/>
       <c r="H24" s="6">
         <v>0</v>
@@ -3275,8 +6449,12 @@
       <c r="D25" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E25" s="36"/>
-      <c r="F25" s="23"/>
+      <c r="E25" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F25" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G25" s="3"/>
       <c r="H25" s="6">
         <v>0</v>
@@ -3288,8 +6466,12 @@
       <c r="D26" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E26" s="36"/>
-      <c r="F26" s="23"/>
+      <c r="E26" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F26" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G26" s="3"/>
       <c r="H26" s="6">
         <v>0</v>
@@ -3301,8 +6483,12 @@
       <c r="D27" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E27" s="36"/>
-      <c r="F27" s="23"/>
+      <c r="E27" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F27" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G27" s="3"/>
       <c r="H27" s="6">
         <v>0</v>
@@ -3314,8 +6500,12 @@
       <c r="D28" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E28" s="36"/>
-      <c r="F28" s="23"/>
+      <c r="E28" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F28" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G28" s="3"/>
       <c r="H28" s="6">
         <v>0</v>
@@ -3329,12 +6519,14 @@
       <c r="D29" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E29" s="36" t="s">
-        <v>125</v>
-      </c>
-      <c r="F29" s="23"/>
+      <c r="E29" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F29" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G29" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H29" s="6">
         <v>1</v>
@@ -3346,8 +6538,12 @@
       <c r="D30" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E30" s="36"/>
-      <c r="F30" s="23"/>
+      <c r="E30" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F30" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G30" s="3"/>
       <c r="H30" s="6">
         <v>0</v>
@@ -3359,8 +6555,12 @@
       <c r="D31" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E31" s="36"/>
-      <c r="F31" s="23"/>
+      <c r="E31" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F31" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G31" s="3"/>
       <c r="H31" s="6">
         <v>0</v>
@@ -3372,8 +6572,12 @@
       <c r="D32" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E32" s="36"/>
-      <c r="F32" s="23"/>
+      <c r="E32" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F32" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G32" s="3"/>
       <c r="H32" s="6">
         <v>0</v>
@@ -3385,8 +6589,12 @@
       <c r="D33" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E33" s="36"/>
-      <c r="F33" s="23"/>
+      <c r="E33" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F33" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G33" s="3"/>
       <c r="H33" s="6">
         <v>0</v>
@@ -3398,8 +6606,12 @@
       <c r="D34" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E34" s="36"/>
-      <c r="F34" s="23"/>
+      <c r="E34" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F34" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G34" s="3"/>
       <c r="H34" s="6">
         <v>0</v>
@@ -3411,8 +6623,12 @@
       <c r="D35" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E35" s="36"/>
-      <c r="F35" s="23"/>
+      <c r="E35" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F35" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G35" s="3"/>
       <c r="H35" s="6">
         <v>0</v>
@@ -3424,8 +6640,12 @@
       <c r="D36" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E36" s="36"/>
-      <c r="F36" s="23"/>
+      <c r="E36" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F36" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G36" s="3"/>
       <c r="H36" s="6">
         <v>0</v>
@@ -3462,7 +6682,7 @@
       <c r="D38" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E38" s="36" t="s">
+      <c r="E38" s="28" t="s">
         <v>125</v>
       </c>
       <c r="F38" s="23" t="s">
@@ -3481,10 +6701,10 @@
       <c r="D39" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E39" s="36" t="s">
-        <v>125</v>
-      </c>
-      <c r="F39" s="36" t="s">
+      <c r="E39" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F39" s="28" t="s">
         <v>125</v>
       </c>
       <c r="G39" s="3"/>
@@ -3498,10 +6718,10 @@
       <c r="D40" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E40" s="36" t="s">
-        <v>125</v>
-      </c>
-      <c r="F40" s="36" t="s">
+      <c r="E40" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F40" s="28" t="s">
         <v>125</v>
       </c>
       <c r="G40" s="3"/>
@@ -3515,10 +6735,10 @@
       <c r="D41" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E41" s="36" t="s">
-        <v>125</v>
-      </c>
-      <c r="F41" s="36" t="s">
+      <c r="E41" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F41" s="28" t="s">
         <v>125</v>
       </c>
       <c r="G41" s="3"/>
@@ -3532,10 +6752,10 @@
       <c r="D42" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E42" s="36" t="s">
-        <v>125</v>
-      </c>
-      <c r="F42" s="36" t="s">
+      <c r="E42" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F42" s="28" t="s">
         <v>125</v>
       </c>
       <c r="G42" s="3"/>
@@ -3549,10 +6769,10 @@
       <c r="D43" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E43" s="36" t="s">
-        <v>125</v>
-      </c>
-      <c r="F43" s="36" t="s">
+      <c r="E43" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F43" s="28" t="s">
         <v>125</v>
       </c>
       <c r="G43" s="3"/>
@@ -3566,10 +6786,10 @@
       <c r="D44" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E44" s="36" t="s">
-        <v>125</v>
-      </c>
-      <c r="F44" s="36" t="s">
+      <c r="E44" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F44" s="28" t="s">
         <v>125</v>
       </c>
       <c r="G44" s="3"/>
@@ -3583,10 +6803,10 @@
       <c r="D45" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E45" s="36" t="s">
-        <v>125</v>
-      </c>
-      <c r="F45" s="36" t="s">
+      <c r="E45" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F45" s="28" t="s">
         <v>125</v>
       </c>
       <c r="G45" s="3"/>
@@ -3609,7 +6829,7 @@
         <v>72</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H46" s="6">
         <v>2</v>
@@ -3624,7 +6844,9 @@
       <c r="E47" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="F47" s="23"/>
+      <c r="F47" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G47" s="3"/>
       <c r="H47" s="6">
         <v>10</v>
@@ -3639,7 +6861,9 @@
       <c r="E48" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="F48" s="23"/>
+      <c r="F48" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G48" s="3"/>
       <c r="H48" s="6">
         <v>0</v>
@@ -3654,7 +6878,9 @@
       <c r="E49" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="F49" s="23"/>
+      <c r="F49" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G49" s="3"/>
       <c r="H49" s="6">
         <v>5</v>
@@ -3669,7 +6895,9 @@
       <c r="E50" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="F50" s="23"/>
+      <c r="F50" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G50" s="3"/>
       <c r="H50" s="6">
         <v>5</v>
@@ -3684,7 +6912,9 @@
       <c r="E51" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="F51" s="23"/>
+      <c r="F51" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G51" s="3"/>
       <c r="H51" s="6">
         <v>1</v>
@@ -3699,7 +6929,9 @@
       <c r="E52" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="F52" s="23"/>
+      <c r="F52" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G52" s="3"/>
       <c r="H52" s="6">
         <v>1</v>
@@ -3714,7 +6946,9 @@
       <c r="E53" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="F53" s="23"/>
+      <c r="F53" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G53" s="3"/>
       <c r="H53" s="6">
         <v>1</v>
@@ -3728,10 +6962,14 @@
       <c r="D54" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E54" s="23"/>
-      <c r="F54" s="23"/>
+      <c r="E54" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F54" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G54" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H54" s="6">
         <v>1</v>
@@ -3743,8 +6981,12 @@
       <c r="D55" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E55" s="23"/>
-      <c r="F55" s="23"/>
+      <c r="E55" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F55" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G55" s="3"/>
       <c r="H55" s="6">
         <v>3</v>
@@ -3756,8 +6998,12 @@
       <c r="D56" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E56" s="23"/>
-      <c r="F56" s="23"/>
+      <c r="E56" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F56" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G56" s="3"/>
       <c r="H56" s="6">
         <v>0</v>
@@ -3769,8 +7015,12 @@
       <c r="D57" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E57" s="23"/>
-      <c r="F57" s="23"/>
+      <c r="E57" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F57" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G57" s="3"/>
       <c r="H57" s="6">
         <v>2</v>
@@ -3782,8 +7032,12 @@
       <c r="D58" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E58" s="23"/>
-      <c r="F58" s="23"/>
+      <c r="E58" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F58" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G58" s="3"/>
       <c r="H58" s="6">
         <v>2</v>
@@ -3795,8 +7049,12 @@
       <c r="D59" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E59" s="23"/>
-      <c r="F59" s="23"/>
+      <c r="E59" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F59" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G59" s="3"/>
       <c r="H59" s="6">
         <v>1</v>
@@ -3808,8 +7066,12 @@
       <c r="D60" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E60" s="23"/>
-      <c r="F60" s="23"/>
+      <c r="E60" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F60" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G60" s="3"/>
       <c r="H60" s="6">
         <v>1</v>
@@ -3821,8 +7083,12 @@
       <c r="D61" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E61" s="23"/>
-      <c r="F61" s="23"/>
+      <c r="E61" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F61" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G61" s="3"/>
       <c r="H61" s="6">
         <v>1</v>
@@ -3859,10 +7125,14 @@
       <c r="D63" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E63" s="23"/>
-      <c r="F63" s="23"/>
+      <c r="E63" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F63" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G63" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H63" s="6">
         <v>2</v>
@@ -3874,8 +7144,12 @@
       <c r="D64" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E64" s="23"/>
-      <c r="F64" s="23"/>
+      <c r="E64" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F64" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G64" s="3"/>
       <c r="H64" s="6">
         <v>5</v>
@@ -3887,8 +7161,12 @@
       <c r="D65" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E65" s="23"/>
-      <c r="F65" s="23"/>
+      <c r="E65" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F65" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G65" s="3"/>
       <c r="H65" s="6">
         <v>0</v>
@@ -3900,8 +7178,12 @@
       <c r="D66" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E66" s="23"/>
-      <c r="F66" s="23"/>
+      <c r="E66" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F66" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G66" s="3"/>
       <c r="H66" s="6">
         <v>3</v>
@@ -3913,8 +7195,12 @@
       <c r="D67" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E67" s="23"/>
-      <c r="F67" s="23"/>
+      <c r="E67" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F67" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G67" s="3"/>
       <c r="H67" s="6">
         <v>3</v>
@@ -3926,8 +7212,12 @@
       <c r="D68" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E68" s="23"/>
-      <c r="F68" s="23"/>
+      <c r="E68" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F68" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G68" s="3"/>
       <c r="H68" s="6">
         <v>1</v>
@@ -3939,8 +7229,12 @@
       <c r="D69" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E69" s="23"/>
-      <c r="F69" s="23"/>
+      <c r="E69" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F69" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G69" s="3"/>
       <c r="H69" s="6">
         <v>1</v>
@@ -3952,8 +7246,12 @@
       <c r="D70" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E70" s="23"/>
-      <c r="F70" s="23"/>
+      <c r="E70" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F70" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G70" s="3"/>
       <c r="H70" s="6">
         <v>1</v>
@@ -3967,10 +7265,14 @@
       <c r="D71" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E71" s="23"/>
-      <c r="F71" s="23"/>
+      <c r="E71" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F71" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G71" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H71" s="6">
         <v>1</v>
@@ -3982,8 +7284,12 @@
       <c r="D72" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E72" s="23"/>
-      <c r="F72" s="23"/>
+      <c r="E72" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F72" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G72" s="3"/>
       <c r="H72" s="6">
         <v>3</v>
@@ -3995,8 +7301,12 @@
       <c r="D73" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E73" s="23"/>
-      <c r="F73" s="23"/>
+      <c r="E73" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F73" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G73" s="3"/>
       <c r="H73" s="6">
         <v>0</v>
@@ -4008,8 +7318,12 @@
       <c r="D74" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E74" s="23"/>
-      <c r="F74" s="23"/>
+      <c r="E74" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F74" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G74" s="3"/>
       <c r="H74" s="6">
         <v>2</v>
@@ -4021,8 +7335,12 @@
       <c r="D75" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E75" s="23"/>
-      <c r="F75" s="23"/>
+      <c r="E75" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F75" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G75" s="3"/>
       <c r="H75" s="6">
         <v>2</v>
@@ -4034,8 +7352,12 @@
       <c r="D76" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E76" s="23"/>
-      <c r="F76" s="23"/>
+      <c r="E76" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F76" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G76" s="3"/>
       <c r="H76" s="6">
         <v>1</v>
@@ -4047,8 +7369,12 @@
       <c r="D77" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E77" s="23"/>
-      <c r="F77" s="23"/>
+      <c r="E77" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F77" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G77" s="3"/>
       <c r="H77" s="6">
         <v>1</v>
@@ -4060,8 +7386,12 @@
       <c r="D78" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E78" s="23"/>
-      <c r="F78" s="23"/>
+      <c r="E78" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F78" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G78" s="3"/>
       <c r="H78" s="6">
         <v>1</v>
@@ -4075,10 +7405,14 @@
       <c r="D79" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E79" s="23"/>
-      <c r="F79" s="23"/>
+      <c r="E79" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F79" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G79" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H79" s="6">
         <v>2</v>
@@ -4090,8 +7424,12 @@
       <c r="D80" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E80" s="23"/>
-      <c r="F80" s="23"/>
+      <c r="E80" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F80" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G80" s="3"/>
       <c r="H80" s="6">
         <v>5</v>
@@ -4103,8 +7441,12 @@
       <c r="D81" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E81" s="23"/>
-      <c r="F81" s="23"/>
+      <c r="E81" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F81" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G81" s="3"/>
       <c r="H81" s="6">
         <v>0</v>
@@ -4116,8 +7458,12 @@
       <c r="D82" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E82" s="23"/>
-      <c r="F82" s="23"/>
+      <c r="E82" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F82" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G82" s="3"/>
       <c r="H82" s="6">
         <v>3</v>
@@ -4129,8 +7475,12 @@
       <c r="D83" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E83" s="23"/>
-      <c r="F83" s="23"/>
+      <c r="E83" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F83" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G83" s="3"/>
       <c r="H83" s="6">
         <v>3</v>
@@ -4142,8 +7492,12 @@
       <c r="D84" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E84" s="23"/>
-      <c r="F84" s="23"/>
+      <c r="E84" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F84" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G84" s="3"/>
       <c r="H84" s="6">
         <v>1</v>
@@ -4155,8 +7509,12 @@
       <c r="D85" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E85" s="23"/>
-      <c r="F85" s="23"/>
+      <c r="E85" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F85" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G85" s="3"/>
       <c r="H85" s="6">
         <v>1</v>
@@ -4168,8 +7526,12 @@
       <c r="D86" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E86" s="23"/>
-      <c r="F86" s="23"/>
+      <c r="E86" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F86" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G86" s="3"/>
       <c r="H86" s="6">
         <v>1</v>
@@ -4183,10 +7545,14 @@
       <c r="D87" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E87" s="23"/>
-      <c r="F87" s="23"/>
+      <c r="E87" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F87" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G87" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H87" s="6">
         <v>1</v>
@@ -4198,8 +7564,12 @@
       <c r="D88" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E88" s="23"/>
-      <c r="F88" s="23"/>
+      <c r="E88" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F88" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G88" s="3"/>
       <c r="H88" s="6">
         <v>3</v>
@@ -4211,8 +7581,12 @@
       <c r="D89" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E89" s="23"/>
-      <c r="F89" s="23"/>
+      <c r="E89" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F89" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G89" s="3"/>
       <c r="H89" s="6">
         <v>0</v>
@@ -4224,8 +7598,12 @@
       <c r="D90" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E90" s="23"/>
-      <c r="F90" s="23"/>
+      <c r="E90" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F90" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G90" s="3"/>
       <c r="H90" s="6">
         <v>2</v>
@@ -4237,8 +7615,12 @@
       <c r="D91" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E91" s="23"/>
-      <c r="F91" s="23"/>
+      <c r="E91" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F91" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G91" s="3"/>
       <c r="H91" s="6">
         <v>2</v>
@@ -4250,8 +7632,12 @@
       <c r="D92" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E92" s="23"/>
-      <c r="F92" s="23"/>
+      <c r="E92" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F92" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G92" s="3"/>
       <c r="H92" s="6">
         <v>1</v>
@@ -4263,8 +7649,12 @@
       <c r="D93" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E93" s="23"/>
-      <c r="F93" s="23"/>
+      <c r="E93" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F93" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G93" s="3"/>
       <c r="H93" s="6">
         <v>1</v>
@@ -4276,8 +7666,12 @@
       <c r="D94" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E94" s="23"/>
-      <c r="F94" s="23"/>
+      <c r="E94" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F94" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G94" s="3"/>
       <c r="H94" s="6">
         <v>1</v>
@@ -4291,10 +7685,14 @@
       <c r="D95" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E95" s="23"/>
-      <c r="F95" s="23"/>
+      <c r="E95" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F95" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G95" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H95" s="6">
         <v>1</v>
@@ -4306,8 +7704,12 @@
       <c r="D96" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E96" s="23"/>
-      <c r="F96" s="23"/>
+      <c r="E96" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F96" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G96" s="3"/>
       <c r="H96" s="6">
         <v>3</v>
@@ -4319,8 +7721,12 @@
       <c r="D97" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E97" s="23"/>
-      <c r="F97" s="23"/>
+      <c r="E97" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F97" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G97" s="3"/>
       <c r="H97" s="6">
         <v>0</v>
@@ -4332,8 +7738,12 @@
       <c r="D98" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E98" s="23"/>
-      <c r="F98" s="23"/>
+      <c r="E98" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F98" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G98" s="3"/>
       <c r="H98" s="6">
         <v>2</v>
@@ -4345,8 +7755,12 @@
       <c r="D99" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E99" s="23"/>
-      <c r="F99" s="23"/>
+      <c r="E99" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F99" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G99" s="3"/>
       <c r="H99" s="6">
         <v>2</v>
@@ -4358,8 +7772,12 @@
       <c r="D100" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E100" s="23"/>
-      <c r="F100" s="23"/>
+      <c r="E100" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F100" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G100" s="3"/>
       <c r="H100" s="6">
         <v>1</v>
@@ -4371,8 +7789,12 @@
       <c r="D101" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E101" s="23"/>
-      <c r="F101" s="23"/>
+      <c r="E101" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F101" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G101" s="3"/>
       <c r="H101" s="6">
         <v>1</v>
@@ -4384,8 +7806,12 @@
       <c r="D102" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E102" s="23"/>
-      <c r="F102" s="23"/>
+      <c r="E102" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F102" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G102" s="3"/>
       <c r="H102" s="6">
         <v>1</v>
@@ -4399,10 +7825,14 @@
       <c r="D103" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E103" s="23"/>
-      <c r="F103" s="23"/>
+      <c r="E103" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F103" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G103" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H103" s="6">
         <v>1</v>
@@ -4414,8 +7844,12 @@
       <c r="D104" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E104" s="23"/>
-      <c r="F104" s="23"/>
+      <c r="E104" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F104" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G104" s="3"/>
       <c r="H104" s="6">
         <v>1</v>
@@ -4427,8 +7861,12 @@
       <c r="D105" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E105" s="23"/>
-      <c r="F105" s="23"/>
+      <c r="E105" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F105" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G105" s="3"/>
       <c r="H105" s="6">
         <v>0</v>
@@ -4440,8 +7878,12 @@
       <c r="D106" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E106" s="23"/>
-      <c r="F106" s="23"/>
+      <c r="E106" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F106" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G106" s="3"/>
       <c r="H106" s="6">
         <v>1</v>
@@ -4453,8 +7895,12 @@
       <c r="D107" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E107" s="23"/>
-      <c r="F107" s="23"/>
+      <c r="E107" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F107" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G107" s="3"/>
       <c r="H107" s="6">
         <v>1</v>
@@ -4466,8 +7912,12 @@
       <c r="D108" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E108" s="23"/>
-      <c r="F108" s="23"/>
+      <c r="E108" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F108" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G108" s="3"/>
       <c r="H108" s="6">
         <v>1</v>
@@ -4479,8 +7929,12 @@
       <c r="D109" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E109" s="23"/>
-      <c r="F109" s="23"/>
+      <c r="E109" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F109" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G109" s="3"/>
       <c r="H109" s="6">
         <v>1</v>
@@ -4492,8 +7946,12 @@
       <c r="D110" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E110" s="23"/>
-      <c r="F110" s="23"/>
+      <c r="E110" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F110" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G110" s="3"/>
       <c r="H110" s="6">
         <v>1</v>
@@ -4509,8 +7967,12 @@
       <c r="D111" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="E111" s="23"/>
-      <c r="F111" s="23"/>
+      <c r="E111" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F111" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G111" s="3" t="s">
         <v>126</v>
       </c>
@@ -4526,8 +7988,12 @@
       <c r="D112" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E112" s="23"/>
-      <c r="F112" s="23"/>
+      <c r="E112" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F112" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G112" s="3" t="s">
         <v>133</v>
       </c>
@@ -4540,8 +8006,12 @@
       <c r="D113" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E113" s="23"/>
-      <c r="F113" s="23"/>
+      <c r="E113" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F113" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G113" s="3"/>
       <c r="H113" s="6">
         <v>0</v>
@@ -4552,8 +8022,12 @@
       <c r="D114" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E114" s="23"/>
-      <c r="F114" s="23"/>
+      <c r="E114" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F114" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G114" s="3"/>
       <c r="H114" s="6">
         <v>0</v>
@@ -4564,8 +8038,12 @@
       <c r="D115" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E115" s="23"/>
-      <c r="F115" s="23"/>
+      <c r="E115" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F115" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G115" s="3"/>
       <c r="H115" s="6">
         <v>0</v>
@@ -4576,8 +8054,12 @@
       <c r="D116" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E116" s="23"/>
-      <c r="F116" s="23"/>
+      <c r="E116" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F116" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G116" s="3"/>
       <c r="H116" s="6">
         <v>0</v>
@@ -4588,8 +8070,12 @@
       <c r="D117" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E117" s="23"/>
-      <c r="F117" s="23"/>
+      <c r="E117" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F117" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G117" s="3"/>
       <c r="H117" s="6">
         <v>0</v>
@@ -4601,8 +8087,12 @@
       <c r="D118" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E118" s="23"/>
-      <c r="F118" s="23"/>
+      <c r="E118" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F118" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G118" s="3"/>
       <c r="H118" s="6">
         <v>0</v>
@@ -4614,8 +8104,12 @@
       <c r="D119" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E119" s="23"/>
-      <c r="F119" s="23"/>
+      <c r="E119" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F119" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G119" s="3"/>
       <c r="H119" s="6">
         <v>0</v>
@@ -4629,8 +8123,12 @@
       <c r="D120" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E120" s="23"/>
-      <c r="F120" s="23"/>
+      <c r="E120" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F120" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G120" s="3" t="s">
         <v>134</v>
       </c>
@@ -4644,8 +8142,12 @@
       <c r="D121" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E121" s="23"/>
-      <c r="F121" s="23"/>
+      <c r="E121" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F121" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G121" s="3"/>
       <c r="H121" s="6">
         <v>0</v>
@@ -4657,8 +8159,12 @@
       <c r="D122" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E122" s="23"/>
-      <c r="F122" s="23"/>
+      <c r="E122" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F122" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G122" s="3"/>
       <c r="H122" s="6">
         <v>0</v>
@@ -4670,8 +8176,12 @@
       <c r="D123" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E123" s="23"/>
-      <c r="F123" s="23"/>
+      <c r="E123" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F123" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G123" s="3"/>
       <c r="H123" s="6">
         <v>0</v>
@@ -4683,8 +8193,12 @@
       <c r="D124" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E124" s="23"/>
-      <c r="F124" s="23"/>
+      <c r="E124" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F124" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G124" s="3"/>
       <c r="H124" s="6">
         <v>0</v>
@@ -4696,8 +8210,12 @@
       <c r="D125" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E125" s="23"/>
-      <c r="F125" s="23"/>
+      <c r="E125" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F125" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G125" s="3"/>
       <c r="H125" s="6">
         <v>0</v>
@@ -4709,8 +8227,12 @@
       <c r="D126" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E126" s="23"/>
-      <c r="F126" s="23"/>
+      <c r="E126" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F126" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G126" s="3"/>
       <c r="H126" s="6">
         <v>0</v>
@@ -4722,8 +8244,12 @@
       <c r="D127" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E127" s="23"/>
-      <c r="F127" s="23"/>
+      <c r="E127" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F127" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G127" s="3"/>
       <c r="H127" s="6">
         <v>0</v>
@@ -4737,10 +8263,14 @@
       <c r="D128" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E128" s="23"/>
-      <c r="F128" s="23"/>
+      <c r="E128" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F128" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G128" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H128" s="6">
         <v>1</v>
@@ -4752,8 +8282,12 @@
       <c r="D129" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E129" s="23"/>
-      <c r="F129" s="23"/>
+      <c r="E129" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F129" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G129" s="3"/>
       <c r="H129" s="6">
         <v>10</v>
@@ -4765,8 +8299,12 @@
       <c r="D130" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E130" s="23"/>
-      <c r="F130" s="23"/>
+      <c r="E130" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F130" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G130" s="3"/>
       <c r="H130" s="6">
         <v>0</v>
@@ -4778,8 +8316,12 @@
       <c r="D131" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E131" s="23"/>
-      <c r="F131" s="23"/>
+      <c r="E131" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F131" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G131" s="3"/>
       <c r="H131" s="6">
         <v>5</v>
@@ -4791,8 +8333,12 @@
       <c r="D132" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E132" s="23"/>
-      <c r="F132" s="23"/>
+      <c r="E132" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F132" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G132" s="3"/>
       <c r="H132" s="6">
         <v>5</v>
@@ -4804,8 +8350,12 @@
       <c r="D133" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E133" s="23"/>
-      <c r="F133" s="23"/>
+      <c r="E133" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F133" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G133" s="3"/>
       <c r="H133" s="6">
         <v>1</v>
@@ -4817,8 +8367,12 @@
       <c r="D134" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E134" s="23"/>
-      <c r="F134" s="23"/>
+      <c r="E134" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F134" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G134" s="3"/>
       <c r="H134" s="6">
         <v>1</v>
@@ -4830,8 +8384,12 @@
       <c r="D135" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E135" s="23"/>
-      <c r="F135" s="23"/>
+      <c r="E135" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F135" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G135" s="3"/>
       <c r="H135" s="6">
         <v>1</v>
@@ -4845,10 +8403,14 @@
       <c r="D136" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E136" s="23"/>
-      <c r="F136" s="23"/>
+      <c r="E136" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F136" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G136" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H136" s="6">
         <v>1</v>
@@ -4860,8 +8422,12 @@
       <c r="D137" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E137" s="23"/>
-      <c r="F137" s="23"/>
+      <c r="E137" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F137" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G137" s="3"/>
       <c r="H137" s="6">
         <v>3</v>
@@ -4873,8 +8439,12 @@
       <c r="D138" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E138" s="23"/>
-      <c r="F138" s="23"/>
+      <c r="E138" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F138" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G138" s="3"/>
       <c r="H138" s="6">
         <v>0</v>
@@ -4886,8 +8456,12 @@
       <c r="D139" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E139" s="23"/>
-      <c r="F139" s="23"/>
+      <c r="E139" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F139" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G139" s="3"/>
       <c r="H139" s="6">
         <v>2</v>
@@ -4899,8 +8473,12 @@
       <c r="D140" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E140" s="23"/>
-      <c r="F140" s="23"/>
+      <c r="E140" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F140" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G140" s="3"/>
       <c r="H140" s="6">
         <v>2</v>
@@ -4912,8 +8490,12 @@
       <c r="D141" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E141" s="23"/>
-      <c r="F141" s="23"/>
+      <c r="E141" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F141" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G141" s="3"/>
       <c r="H141" s="6">
         <v>1</v>
@@ -4925,8 +8507,12 @@
       <c r="D142" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E142" s="23"/>
-      <c r="F142" s="23"/>
+      <c r="E142" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F142" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G142" s="3"/>
       <c r="H142" s="6">
         <v>1</v>
@@ -4938,8 +8524,12 @@
       <c r="D143" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E143" s="23"/>
-      <c r="F143" s="23"/>
+      <c r="E143" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F143" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G143" s="3"/>
       <c r="H143" s="6">
         <v>1</v>
@@ -4953,8 +8543,12 @@
       <c r="D144" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E144" s="23"/>
-      <c r="F144" s="23"/>
+      <c r="E144" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F144" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G144" s="3" t="s">
         <v>135</v>
       </c>
@@ -4968,8 +8562,12 @@
       <c r="D145" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E145" s="23"/>
-      <c r="F145" s="23"/>
+      <c r="E145" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F145" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G145" s="3"/>
       <c r="H145" s="6">
         <v>0</v>
@@ -4981,8 +8579,12 @@
       <c r="D146" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E146" s="23"/>
-      <c r="F146" s="23"/>
+      <c r="E146" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F146" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G146" s="3"/>
       <c r="H146" s="6">
         <v>0</v>
@@ -4994,8 +8596,12 @@
       <c r="D147" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E147" s="23"/>
-      <c r="F147" s="23"/>
+      <c r="E147" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F147" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G147" s="3"/>
       <c r="H147" s="6">
         <v>0</v>
@@ -5007,8 +8613,12 @@
       <c r="D148" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E148" s="23"/>
-      <c r="F148" s="23"/>
+      <c r="E148" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F148" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G148" s="3"/>
       <c r="H148" s="6">
         <v>0</v>
@@ -5020,8 +8630,12 @@
       <c r="D149" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E149" s="23"/>
-      <c r="F149" s="23"/>
+      <c r="E149" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F149" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G149" s="3"/>
       <c r="H149" s="6">
         <v>0</v>
@@ -5033,8 +8647,12 @@
       <c r="D150" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E150" s="23"/>
-      <c r="F150" s="23"/>
+      <c r="E150" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F150" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G150" s="3"/>
       <c r="H150" s="6">
         <v>0</v>
@@ -5046,8 +8664,12 @@
       <c r="D151" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E151" s="23"/>
-      <c r="F151" s="23"/>
+      <c r="E151" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F151" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G151" s="3"/>
       <c r="H151" s="6">
         <v>0</v>
@@ -5061,8 +8683,12 @@
       <c r="D152" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E152" s="23"/>
-      <c r="F152" s="23"/>
+      <c r="E152" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F152" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G152" s="3" t="s">
         <v>136</v>
       </c>
@@ -5075,8 +8701,12 @@
       <c r="D153" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E153" s="23"/>
-      <c r="F153" s="23"/>
+      <c r="E153" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F153" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G153" s="3"/>
       <c r="H153" s="6">
         <v>0</v>
@@ -5087,8 +8717,12 @@
       <c r="D154" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E154" s="23"/>
-      <c r="F154" s="23"/>
+      <c r="E154" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F154" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G154" s="3"/>
       <c r="H154" s="6">
         <v>0</v>
@@ -5099,8 +8733,12 @@
       <c r="D155" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E155" s="23"/>
-      <c r="F155" s="23"/>
+      <c r="E155" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F155" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G155" s="3"/>
       <c r="H155" s="6">
         <v>0</v>
@@ -5111,8 +8749,12 @@
       <c r="D156" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E156" s="23"/>
-      <c r="F156" s="23"/>
+      <c r="E156" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F156" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G156" s="3"/>
       <c r="H156" s="6">
         <v>0</v>
@@ -5123,8 +8765,12 @@
       <c r="D157" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E157" s="23"/>
-      <c r="F157" s="23"/>
+      <c r="E157" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F157" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G157" s="3"/>
       <c r="H157" s="6">
         <v>0</v>
@@ -5136,8 +8782,12 @@
       <c r="D158" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E158" s="23"/>
-      <c r="F158" s="23"/>
+      <c r="E158" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F158" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G158" s="3"/>
       <c r="H158" s="6">
         <v>0</v>
@@ -5148,8 +8798,12 @@
       <c r="D159" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E159" s="23"/>
-      <c r="F159" s="23"/>
+      <c r="E159" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F159" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G159" s="3"/>
       <c r="H159" s="6">
         <v>0</v>
@@ -5163,10 +8817,14 @@
       <c r="D160" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E160" s="23"/>
-      <c r="F160" s="23"/>
+      <c r="E160" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F160" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G160" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H160" s="6">
         <v>2</v>
@@ -5178,8 +8836,12 @@
       <c r="D161" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E161" s="23"/>
-      <c r="F161" s="23"/>
+      <c r="E161" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F161" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G161" s="3"/>
       <c r="H161" s="6">
         <v>5</v>
@@ -5191,8 +8853,12 @@
       <c r="D162" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E162" s="23"/>
-      <c r="F162" s="23"/>
+      <c r="E162" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F162" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G162" s="3"/>
       <c r="H162" s="6">
         <v>0</v>
@@ -5204,8 +8870,12 @@
       <c r="D163" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E163" s="23"/>
-      <c r="F163" s="23"/>
+      <c r="E163" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F163" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G163" s="3"/>
       <c r="H163" s="6">
         <v>3</v>
@@ -5217,8 +8887,12 @@
       <c r="D164" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E164" s="23"/>
-      <c r="F164" s="23"/>
+      <c r="E164" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F164" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G164" s="3"/>
       <c r="H164" s="6">
         <v>3</v>
@@ -5230,8 +8904,12 @@
       <c r="D165" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E165" s="23"/>
-      <c r="F165" s="23"/>
+      <c r="E165" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F165" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G165" s="3"/>
       <c r="H165" s="6">
         <v>1</v>
@@ -5243,8 +8921,12 @@
       <c r="D166" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E166" s="23"/>
-      <c r="F166" s="23"/>
+      <c r="E166" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F166" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G166" s="3"/>
       <c r="H166" s="6">
         <v>1</v>
@@ -5256,8 +8938,12 @@
       <c r="D167" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E167" s="23"/>
-      <c r="F167" s="23"/>
+      <c r="E167" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F167" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G167" s="3"/>
       <c r="H167" s="6">
         <v>1</v>
@@ -5271,10 +8957,14 @@
       <c r="D168" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E168" s="23"/>
-      <c r="F168" s="23"/>
+      <c r="E168" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F168" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G168" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H168" s="6">
         <v>1</v>
@@ -5285,8 +8975,12 @@
       <c r="D169" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E169" s="23"/>
-      <c r="F169" s="23"/>
+      <c r="E169" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F169" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G169" s="3"/>
       <c r="H169" s="6">
         <v>3</v>
@@ -5297,8 +8991,12 @@
       <c r="D170" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E170" s="23"/>
-      <c r="F170" s="23"/>
+      <c r="E170" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F170" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G170" s="3"/>
       <c r="H170" s="6">
         <v>0</v>
@@ -5309,8 +9007,12 @@
       <c r="D171" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E171" s="23"/>
-      <c r="F171" s="23"/>
+      <c r="E171" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F171" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G171" s="3"/>
       <c r="H171" s="6">
         <v>2</v>
@@ -5321,8 +9023,12 @@
       <c r="D172" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E172" s="23"/>
-      <c r="F172" s="23"/>
+      <c r="E172" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F172" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G172" s="3"/>
       <c r="H172" s="6">
         <v>2</v>
@@ -5333,8 +9039,12 @@
       <c r="D173" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E173" s="23"/>
-      <c r="F173" s="23"/>
+      <c r="E173" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F173" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G173" s="3"/>
       <c r="H173" s="6">
         <v>1</v>
@@ -5346,8 +9056,12 @@
       <c r="D174" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E174" s="23"/>
-      <c r="F174" s="23"/>
+      <c r="E174" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F174" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G174" s="3"/>
       <c r="H174" s="6">
         <v>1</v>
@@ -5358,8 +9072,12 @@
       <c r="D175" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E175" s="23"/>
-      <c r="F175" s="23"/>
+      <c r="E175" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F175" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G175" s="3"/>
       <c r="H175" s="6">
         <v>1</v>
@@ -5396,8 +9114,12 @@
       <c r="D177" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E177" s="23"/>
-      <c r="F177" s="23"/>
+      <c r="E177" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F177" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G177" s="3" t="s">
         <v>137</v>
       </c>
@@ -5410,8 +9132,12 @@
       <c r="D178" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E178" s="23"/>
-      <c r="F178" s="23"/>
+      <c r="E178" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F178" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G178" s="3"/>
       <c r="H178" s="6">
         <v>0</v>
@@ -5422,8 +9148,12 @@
       <c r="D179" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E179" s="23"/>
-      <c r="F179" s="23"/>
+      <c r="E179" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F179" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G179" s="3"/>
       <c r="H179" s="6">
         <v>0</v>
@@ -5434,8 +9164,12 @@
       <c r="D180" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E180" s="23"/>
-      <c r="F180" s="23"/>
+      <c r="E180" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F180" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G180" s="3"/>
       <c r="H180" s="6">
         <v>0</v>
@@ -5446,8 +9180,12 @@
       <c r="D181" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E181" s="23"/>
-      <c r="F181" s="23"/>
+      <c r="E181" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F181" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G181" s="3"/>
       <c r="H181" s="6">
         <v>0</v>
@@ -5458,8 +9196,12 @@
       <c r="D182" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E182" s="23"/>
-      <c r="F182" s="23"/>
+      <c r="E182" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F182" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G182" s="3"/>
       <c r="H182" s="6">
         <v>0</v>
@@ -5471,8 +9213,12 @@
       <c r="D183" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E183" s="23"/>
-      <c r="F183" s="23"/>
+      <c r="E183" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F183" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G183" s="3"/>
       <c r="H183" s="6">
         <v>0</v>
@@ -5483,8 +9229,12 @@
       <c r="D184" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E184" s="23"/>
-      <c r="F184" s="23"/>
+      <c r="E184" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F184" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G184" s="3"/>
       <c r="H184" s="6">
         <v>0</v>
@@ -5498,10 +9248,14 @@
       <c r="D185" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E185" s="23"/>
-      <c r="F185" s="23"/>
+      <c r="E185" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F185" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G185" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H185" s="6">
         <v>2</v>
@@ -5513,8 +9267,12 @@
       <c r="D186" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E186" s="23"/>
-      <c r="F186" s="23"/>
+      <c r="E186" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F186" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G186" s="3"/>
       <c r="H186" s="6">
         <v>5</v>
@@ -5526,8 +9284,12 @@
       <c r="D187" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E187" s="23"/>
-      <c r="F187" s="23"/>
+      <c r="E187" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F187" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G187" s="3"/>
       <c r="H187" s="6">
         <v>0</v>
@@ -5539,8 +9301,12 @@
       <c r="D188" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E188" s="23"/>
-      <c r="F188" s="23"/>
+      <c r="E188" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F188" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G188" s="3"/>
       <c r="H188" s="6">
         <v>3</v>
@@ -5552,8 +9318,12 @@
       <c r="D189" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E189" s="23"/>
-      <c r="F189" s="23"/>
+      <c r="E189" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F189" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G189" s="3"/>
       <c r="H189" s="6">
         <v>3</v>
@@ -5565,8 +9335,12 @@
       <c r="D190" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E190" s="23"/>
-      <c r="F190" s="23"/>
+      <c r="E190" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F190" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G190" s="3"/>
       <c r="H190" s="6">
         <v>1</v>
@@ -5578,8 +9352,12 @@
       <c r="D191" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E191" s="23"/>
-      <c r="F191" s="23"/>
+      <c r="E191" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F191" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G191" s="3"/>
       <c r="H191" s="6">
         <v>1</v>
@@ -5591,8 +9369,12 @@
       <c r="D192" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E192" s="23"/>
-      <c r="F192" s="23"/>
+      <c r="E192" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F192" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G192" s="3"/>
       <c r="H192" s="6">
         <v>1</v>
@@ -5606,8 +9388,12 @@
       <c r="D193" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E193" s="23"/>
-      <c r="F193" s="23"/>
+      <c r="E193" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F193" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G193" s="3" t="s">
         <v>140</v>
       </c>
@@ -5620,8 +9406,12 @@
       <c r="D194" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E194" s="23"/>
-      <c r="F194" s="23"/>
+      <c r="E194" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F194" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G194" s="3"/>
       <c r="H194" s="6">
         <v>0</v>
@@ -5632,8 +9422,12 @@
       <c r="D195" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E195" s="23"/>
-      <c r="F195" s="23"/>
+      <c r="E195" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F195" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G195" s="3"/>
       <c r="H195" s="6">
         <v>0</v>
@@ -5644,8 +9438,12 @@
       <c r="D196" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E196" s="23"/>
-      <c r="F196" s="23"/>
+      <c r="E196" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F196" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G196" s="3"/>
       <c r="H196" s="6">
         <v>0</v>
@@ -5656,8 +9454,12 @@
       <c r="D197" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E197" s="23"/>
-      <c r="F197" s="23"/>
+      <c r="E197" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F197" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G197" s="3"/>
       <c r="H197" s="6">
         <v>0</v>
@@ -5668,8 +9470,12 @@
       <c r="D198" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E198" s="23"/>
-      <c r="F198" s="23"/>
+      <c r="E198" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F198" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G198" s="3"/>
       <c r="H198" s="6">
         <v>0</v>
@@ -5681,8 +9487,12 @@
       <c r="D199" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E199" s="23"/>
-      <c r="F199" s="23"/>
+      <c r="E199" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F199" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G199" s="3"/>
       <c r="H199" s="6">
         <v>0</v>
@@ -5694,8 +9504,12 @@
       <c r="D200" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E200" s="23"/>
-      <c r="F200" s="23"/>
+      <c r="E200" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F200" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G200" s="3"/>
       <c r="H200" s="6">
         <v>0</v>
@@ -5709,8 +9523,12 @@
       <c r="D201" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E201" s="23"/>
-      <c r="F201" s="23"/>
+      <c r="E201" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F201" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G201" s="3" t="s">
         <v>138</v>
       </c>
@@ -5723,8 +9541,12 @@
       <c r="D202" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E202" s="23"/>
-      <c r="F202" s="23"/>
+      <c r="E202" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F202" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G202" s="3"/>
       <c r="H202" s="6">
         <v>0</v>
@@ -5735,8 +9557,12 @@
       <c r="D203" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E203" s="23"/>
-      <c r="F203" s="23"/>
+      <c r="E203" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F203" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G203" s="3"/>
       <c r="H203" s="6">
         <v>0</v>
@@ -5747,8 +9573,12 @@
       <c r="D204" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E204" s="23"/>
-      <c r="F204" s="23"/>
+      <c r="E204" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F204" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G204" s="3"/>
       <c r="H204" s="6">
         <v>0</v>
@@ -5759,8 +9589,12 @@
       <c r="D205" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E205" s="23"/>
-      <c r="F205" s="23"/>
+      <c r="E205" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F205" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G205" s="3"/>
       <c r="H205" s="6">
         <v>0</v>
@@ -5771,8 +9605,12 @@
       <c r="D206" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E206" s="23"/>
-      <c r="F206" s="23"/>
+      <c r="E206" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F206" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G206" s="3"/>
       <c r="H206" s="6">
         <v>0</v>
@@ -5784,8 +9622,12 @@
       <c r="D207" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E207" s="23"/>
-      <c r="F207" s="23"/>
+      <c r="E207" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F207" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G207" s="3"/>
       <c r="H207" s="6">
         <v>0</v>
@@ -5796,8 +9638,12 @@
       <c r="D208" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E208" s="23"/>
-      <c r="F208" s="23"/>
+      <c r="E208" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F208" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G208" s="3"/>
       <c r="H208" s="6">
         <v>0</v>
@@ -5813,8 +9659,12 @@
       <c r="D209" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="E209" s="23"/>
-      <c r="F209" s="23"/>
+      <c r="E209" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F209" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G209" s="3" t="s">
         <v>71</v>
       </c>
@@ -5830,8 +9680,12 @@
       <c r="D210" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E210" s="23"/>
-      <c r="F210" s="23"/>
+      <c r="E210" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F210" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G210" s="3" t="s">
         <v>137</v>
       </c>
@@ -5844,8 +9698,12 @@
       <c r="D211" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E211" s="23"/>
-      <c r="F211" s="23"/>
+      <c r="E211" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F211" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G211" s="3"/>
       <c r="H211" s="6">
         <v>0</v>
@@ -5856,8 +9714,12 @@
       <c r="D212" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E212" s="23"/>
-      <c r="F212" s="23"/>
+      <c r="E212" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F212" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G212" s="3"/>
       <c r="H212" s="6">
         <v>0</v>
@@ -5868,8 +9730,12 @@
       <c r="D213" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E213" s="23"/>
-      <c r="F213" s="23"/>
+      <c r="E213" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F213" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G213" s="3"/>
       <c r="H213" s="6">
         <v>0</v>
@@ -5880,8 +9746,12 @@
       <c r="D214" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E214" s="23"/>
-      <c r="F214" s="23"/>
+      <c r="E214" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F214" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G214" s="3"/>
       <c r="H214" s="6">
         <v>0</v>
@@ -5892,8 +9762,12 @@
       <c r="D215" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E215" s="23"/>
-      <c r="F215" s="23"/>
+      <c r="E215" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F215" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G215" s="3"/>
       <c r="H215" s="6">
         <v>0</v>
@@ -5905,8 +9779,12 @@
       <c r="D216" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E216" s="23"/>
-      <c r="F216" s="23"/>
+      <c r="E216" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F216" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G216" s="3"/>
       <c r="H216" s="6">
         <v>0</v>
@@ -5917,8 +9795,12 @@
       <c r="D217" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E217" s="23"/>
-      <c r="F217" s="23"/>
+      <c r="E217" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F217" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G217" s="3"/>
       <c r="H217" s="6">
         <v>0</v>
@@ -5932,10 +9814,14 @@
       <c r="D218" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E218" s="23"/>
-      <c r="F218" s="23"/>
+      <c r="E218" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F218" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G218" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H218" s="6">
         <v>3</v>
@@ -5947,8 +9833,12 @@
       <c r="D219" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E219" s="23"/>
-      <c r="F219" s="23"/>
+      <c r="E219" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F219" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G219" s="3"/>
       <c r="H219" s="6">
         <v>10</v>
@@ -5960,8 +9850,12 @@
       <c r="D220" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E220" s="23"/>
-      <c r="F220" s="23"/>
+      <c r="E220" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F220" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G220" s="3"/>
       <c r="H220" s="6">
         <v>0</v>
@@ -5973,8 +9867,12 @@
       <c r="D221" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E221" s="23"/>
-      <c r="F221" s="23"/>
+      <c r="E221" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F221" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G221" s="3"/>
       <c r="H221" s="6">
         <v>5</v>
@@ -5986,8 +9884,12 @@
       <c r="D222" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E222" s="23"/>
-      <c r="F222" s="23"/>
+      <c r="E222" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F222" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G222" s="3"/>
       <c r="H222" s="6">
         <v>5</v>
@@ -5999,8 +9901,12 @@
       <c r="D223" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E223" s="23"/>
-      <c r="F223" s="23"/>
+      <c r="E223" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F223" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G223" s="3"/>
       <c r="H223" s="6">
         <v>2</v>
@@ -6012,8 +9918,12 @@
       <c r="D224" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E224" s="23"/>
-      <c r="F224" s="23"/>
+      <c r="E224" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F224" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G224" s="3"/>
       <c r="H224" s="6">
         <v>1</v>
@@ -6025,8 +9935,12 @@
       <c r="D225" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E225" s="23"/>
-      <c r="F225" s="23"/>
+      <c r="E225" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F225" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G225" s="3"/>
       <c r="H225" s="6">
         <v>1</v>
@@ -6040,8 +9954,12 @@
       <c r="D226" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E226" s="23"/>
-      <c r="F226" s="23"/>
+      <c r="E226" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F226" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G226" s="3" t="s">
         <v>139</v>
       </c>
@@ -6054,8 +9972,12 @@
       <c r="D227" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E227" s="23"/>
-      <c r="F227" s="23"/>
+      <c r="E227" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F227" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G227" s="3"/>
       <c r="H227" s="6">
         <v>0</v>
@@ -6066,8 +9988,12 @@
       <c r="D228" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E228" s="23"/>
-      <c r="F228" s="23"/>
+      <c r="E228" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F228" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G228" s="3"/>
       <c r="H228" s="6">
         <v>0</v>
@@ -6078,8 +10004,12 @@
       <c r="D229" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E229" s="23"/>
-      <c r="F229" s="23"/>
+      <c r="E229" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F229" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G229" s="3"/>
       <c r="H229" s="6">
         <v>0</v>
@@ -6090,8 +10020,12 @@
       <c r="D230" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E230" s="23"/>
-      <c r="F230" s="23"/>
+      <c r="E230" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F230" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G230" s="3"/>
       <c r="H230" s="6">
         <v>0</v>
@@ -6102,8 +10036,12 @@
       <c r="D231" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E231" s="23"/>
-      <c r="F231" s="23"/>
+      <c r="E231" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F231" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G231" s="3"/>
       <c r="H231" s="6">
         <v>0</v>
@@ -6115,8 +10053,12 @@
       <c r="D232" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E232" s="23"/>
-      <c r="F232" s="23"/>
+      <c r="E232" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F232" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G232" s="3"/>
       <c r="H232" s="6">
         <v>0</v>
@@ -6128,8 +10070,12 @@
       <c r="D233" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E233" s="23"/>
-      <c r="F233" s="23"/>
+      <c r="E233" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F233" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G233" s="3"/>
       <c r="H233" s="6">
         <v>0</v>
@@ -6143,8 +10089,12 @@
       <c r="D234" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E234" s="23"/>
-      <c r="F234" s="23"/>
+      <c r="E234" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F234" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G234" s="3" t="s">
         <v>121</v>
       </c>
@@ -6157,8 +10107,12 @@
       <c r="D235" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E235" s="23"/>
-      <c r="F235" s="23"/>
+      <c r="E235" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F235" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G235" s="3"/>
       <c r="H235" s="6">
         <v>0</v>
@@ -6169,8 +10123,12 @@
       <c r="D236" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E236" s="23"/>
-      <c r="F236" s="23"/>
+      <c r="E236" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F236" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G236" s="3"/>
       <c r="H236" s="6">
         <v>0</v>
@@ -6181,8 +10139,12 @@
       <c r="D237" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E237" s="23"/>
-      <c r="F237" s="23"/>
+      <c r="E237" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F237" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G237" s="3"/>
       <c r="H237" s="6">
         <v>0</v>
@@ -6193,8 +10155,12 @@
       <c r="D238" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E238" s="23"/>
-      <c r="F238" s="23"/>
+      <c r="E238" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F238" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G238" s="3"/>
       <c r="H238" s="6">
         <v>0</v>
@@ -6205,8 +10171,12 @@
       <c r="D239" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E239" s="23"/>
-      <c r="F239" s="23"/>
+      <c r="E239" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F239" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G239" s="3"/>
       <c r="H239" s="6">
         <v>0</v>
@@ -6218,8 +10188,12 @@
       <c r="D240" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E240" s="23"/>
-      <c r="F240" s="23"/>
+      <c r="E240" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F240" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G240" s="3"/>
       <c r="H240" s="6">
         <v>0</v>
@@ -6231,8 +10205,12 @@
       <c r="D241" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E241" s="23"/>
-      <c r="F241" s="23"/>
+      <c r="E241" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F241" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G241" s="3"/>
       <c r="H241" s="6">
         <v>0</v>
@@ -6246,8 +10224,12 @@
       <c r="D242" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E242" s="23"/>
-      <c r="F242" s="23"/>
+      <c r="E242" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F242" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G242" s="3" t="s">
         <v>140</v>
       </c>
@@ -6260,8 +10242,12 @@
       <c r="D243" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E243" s="23"/>
-      <c r="F243" s="23"/>
+      <c r="E243" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F243" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G243" s="3"/>
       <c r="H243" s="6">
         <v>0</v>
@@ -6272,8 +10258,12 @@
       <c r="D244" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E244" s="23"/>
-      <c r="F244" s="23"/>
+      <c r="E244" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F244" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G244" s="3"/>
       <c r="H244" s="6">
         <v>0</v>
@@ -6284,8 +10274,12 @@
       <c r="D245" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E245" s="23"/>
-      <c r="F245" s="23"/>
+      <c r="E245" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F245" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G245" s="3"/>
       <c r="H245" s="6">
         <v>0</v>
@@ -6296,8 +10290,12 @@
       <c r="D246" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E246" s="23"/>
-      <c r="F246" s="23"/>
+      <c r="E246" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F246" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G246" s="3"/>
       <c r="H246" s="6">
         <v>0</v>
@@ -6308,8 +10306,12 @@
       <c r="D247" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E247" s="23"/>
-      <c r="F247" s="23"/>
+      <c r="E247" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F247" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G247" s="3"/>
       <c r="H247" s="6">
         <v>0</v>
@@ -6321,8 +10323,12 @@
       <c r="D248" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E248" s="23"/>
-      <c r="F248" s="23"/>
+      <c r="E248" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F248" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G248" s="3"/>
       <c r="H248" s="6">
         <v>0</v>
@@ -6334,8 +10340,12 @@
       <c r="D249" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E249" s="23"/>
-      <c r="F249" s="23"/>
+      <c r="E249" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F249" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G249" s="3"/>
       <c r="H249" s="6">
         <v>0</v>
@@ -6349,8 +10359,12 @@
       <c r="D250" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E250" s="23"/>
-      <c r="F250" s="23"/>
+      <c r="E250" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F250" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G250" s="3" t="s">
         <v>138</v>
       </c>
@@ -6363,8 +10377,12 @@
       <c r="D251" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E251" s="23"/>
-      <c r="F251" s="23"/>
+      <c r="E251" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F251" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G251" s="3"/>
       <c r="H251" s="6">
         <v>0</v>
@@ -6375,8 +10393,12 @@
       <c r="D252" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E252" s="23"/>
-      <c r="F252" s="23"/>
+      <c r="E252" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F252" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G252" s="3"/>
       <c r="H252" s="6">
         <v>0</v>
@@ -6387,8 +10409,12 @@
       <c r="D253" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E253" s="23"/>
-      <c r="F253" s="23"/>
+      <c r="E253" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F253" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G253" s="3"/>
       <c r="H253" s="6">
         <v>0</v>
@@ -6399,8 +10425,12 @@
       <c r="D254" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E254" s="23"/>
-      <c r="F254" s="23"/>
+      <c r="E254" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F254" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G254" s="3"/>
       <c r="H254" s="6">
         <v>0</v>
@@ -6411,8 +10441,12 @@
       <c r="D255" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E255" s="23"/>
-      <c r="F255" s="23"/>
+      <c r="E255" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F255" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G255" s="3"/>
       <c r="H255" s="6">
         <v>0</v>
@@ -6424,8 +10458,12 @@
       <c r="D256" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E256" s="23"/>
-      <c r="F256" s="23"/>
+      <c r="E256" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F256" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G256" s="3"/>
       <c r="H256" s="6">
         <v>0</v>
@@ -6436,8 +10474,12 @@
       <c r="D257" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E257" s="23"/>
-      <c r="F257" s="23"/>
+      <c r="E257" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F257" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G257" s="3"/>
       <c r="H257" s="6">
         <v>0</v>
@@ -6453,8 +10495,12 @@
       <c r="D258" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="E258" s="23"/>
-      <c r="F258" s="23"/>
+      <c r="E258" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F258" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G258" s="3" t="s">
         <v>117</v>
       </c>
@@ -6470,10 +10516,14 @@
       <c r="D259" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E259" s="23"/>
-      <c r="F259" s="23"/>
+      <c r="E259" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F259" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G259" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H259" s="6">
         <v>2</v>
@@ -6484,8 +10534,12 @@
       <c r="D260" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E260" s="23"/>
-      <c r="F260" s="23"/>
+      <c r="E260" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F260" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="H260" s="6">
         <v>10</v>
       </c>
@@ -6495,8 +10549,12 @@
       <c r="D261" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E261" s="23"/>
-      <c r="F261" s="23"/>
+      <c r="E261" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F261" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G261" s="3"/>
       <c r="H261" s="6">
         <v>0</v>
@@ -6507,8 +10565,12 @@
       <c r="D262" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E262" s="23"/>
-      <c r="F262" s="23"/>
+      <c r="E262" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F262" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G262" s="3"/>
       <c r="H262" s="6">
         <v>5</v>
@@ -6519,8 +10581,12 @@
       <c r="D263" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E263" s="23"/>
-      <c r="F263" s="23"/>
+      <c r="E263" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F263" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G263" s="3"/>
       <c r="H263" s="6">
         <v>5</v>
@@ -6531,8 +10597,12 @@
       <c r="D264" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E264" s="23"/>
-      <c r="F264" s="23"/>
+      <c r="E264" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F264" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G264" s="3"/>
       <c r="H264" s="6">
         <v>3</v>
@@ -6544,8 +10614,12 @@
       <c r="D265" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E265" s="23"/>
-      <c r="F265" s="23"/>
+      <c r="E265" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F265" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G265" s="3"/>
       <c r="H265" s="6">
         <v>1</v>
@@ -6556,8 +10630,12 @@
       <c r="D266" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E266" s="23"/>
-      <c r="F266" s="23"/>
+      <c r="E266" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F266" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G266" s="3"/>
       <c r="H266" s="6">
         <v>1</v>
@@ -6571,10 +10649,14 @@
       <c r="D267" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E267" s="23"/>
-      <c r="F267" s="23"/>
+      <c r="E267" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F267" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G267" s="3" t="s">
-        <v>141</v>
+        <v>174</v>
       </c>
       <c r="H267" s="6">
         <v>2</v>
@@ -6586,8 +10668,12 @@
       <c r="D268" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E268" s="23"/>
-      <c r="F268" s="23"/>
+      <c r="E268" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F268" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G268" s="3"/>
       <c r="H268" s="6">
         <v>5</v>
@@ -6599,8 +10685,12 @@
       <c r="D269" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E269" s="23"/>
-      <c r="F269" s="23"/>
+      <c r="E269" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F269" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G269" s="3"/>
       <c r="H269" s="6">
         <v>0</v>
@@ -6612,8 +10702,12 @@
       <c r="D270" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E270" s="23"/>
-      <c r="F270" s="23"/>
+      <c r="E270" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F270" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G270" s="3"/>
       <c r="H270" s="6">
         <v>3</v>
@@ -6625,8 +10719,12 @@
       <c r="D271" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E271" s="23"/>
-      <c r="F271" s="23"/>
+      <c r="E271" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F271" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G271" s="3"/>
       <c r="H271" s="6">
         <v>3</v>
@@ -6638,8 +10736,12 @@
       <c r="D272" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E272" s="23"/>
-      <c r="F272" s="23"/>
+      <c r="E272" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F272" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G272" s="3"/>
       <c r="H272" s="6">
         <v>1</v>
@@ -6651,8 +10753,12 @@
       <c r="D273" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E273" s="23"/>
-      <c r="F273" s="23"/>
+      <c r="E273" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F273" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G273" s="3"/>
       <c r="H273" s="6">
         <v>1</v>
@@ -6664,8 +10770,12 @@
       <c r="D274" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E274" s="23"/>
-      <c r="F274" s="23"/>
+      <c r="E274" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F274" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G274" s="3"/>
       <c r="H274" s="6">
         <v>1</v>
@@ -6679,10 +10789,14 @@
       <c r="D275" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E275" s="23"/>
-      <c r="F275" s="23"/>
+      <c r="E275" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F275" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G275" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H275" s="6">
         <v>1</v>
@@ -6694,8 +10808,12 @@
       <c r="D276" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E276" s="23"/>
-      <c r="F276" s="23"/>
+      <c r="E276" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F276" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G276" s="3"/>
       <c r="H276" s="6">
         <v>0</v>
@@ -6707,8 +10825,12 @@
       <c r="D277" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E277" s="23"/>
-      <c r="F277" s="23"/>
+      <c r="E277" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F277" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G277" s="3"/>
       <c r="H277" s="6">
         <v>0</v>
@@ -6720,8 +10842,12 @@
       <c r="D278" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E278" s="23"/>
-      <c r="F278" s="23"/>
+      <c r="E278" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F278" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G278" s="3"/>
       <c r="H278" s="6">
         <v>0</v>
@@ -6733,8 +10859,12 @@
       <c r="D279" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E279" s="23"/>
-      <c r="F279" s="23"/>
+      <c r="E279" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F279" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G279" s="3"/>
       <c r="H279" s="6">
         <v>0</v>
@@ -6746,8 +10876,12 @@
       <c r="D280" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E280" s="23"/>
-      <c r="F280" s="23"/>
+      <c r="E280" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F280" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G280" s="3"/>
       <c r="H280" s="6">
         <v>0</v>
@@ -6759,8 +10893,12 @@
       <c r="D281" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E281" s="23"/>
-      <c r="F281" s="23"/>
+      <c r="E281" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F281" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G281" s="3"/>
       <c r="H281" s="6">
         <v>0</v>
@@ -6772,8 +10910,12 @@
       <c r="D282" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E282" s="23"/>
-      <c r="F282" s="23"/>
+      <c r="E282" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F282" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G282" s="3"/>
       <c r="H282" s="6">
         <v>0</v>
@@ -6787,10 +10929,14 @@
       <c r="D283" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E283" s="23"/>
-      <c r="F283" s="23"/>
+      <c r="E283" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F283" s="39" t="s">
+        <v>72</v>
+      </c>
       <c r="G283" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H283" s="6">
         <v>1</v>
@@ -6801,8 +10947,12 @@
       <c r="D284" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E284" s="23"/>
-      <c r="F284" s="23"/>
+      <c r="E284" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F284" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="H284" s="6">
         <v>0</v>
       </c>
@@ -6812,8 +10962,12 @@
       <c r="D285" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E285" s="23"/>
-      <c r="F285" s="23"/>
+      <c r="E285" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F285" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G285" s="3"/>
       <c r="H285" s="6">
         <v>0</v>
@@ -6824,8 +10978,12 @@
       <c r="D286" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E286" s="23"/>
-      <c r="F286" s="23"/>
+      <c r="E286" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F286" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G286" s="3"/>
       <c r="H286" s="6">
         <v>0</v>
@@ -6836,8 +10994,12 @@
       <c r="D287" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E287" s="23"/>
-      <c r="F287" s="23"/>
+      <c r="E287" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F287" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G287" s="3"/>
       <c r="H287" s="6">
         <v>0</v>
@@ -6848,8 +11010,12 @@
       <c r="D288" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E288" s="23"/>
-      <c r="F288" s="23"/>
+      <c r="E288" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F288" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G288" s="3"/>
       <c r="H288" s="6">
         <v>0</v>
@@ -6861,8 +11027,12 @@
       <c r="D289" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E289" s="23"/>
-      <c r="F289" s="23"/>
+      <c r="E289" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F289" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G289" s="3"/>
       <c r="H289" s="6">
         <v>0</v>
@@ -6874,8 +11044,12 @@
       <c r="D290" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E290" s="23"/>
-      <c r="F290" s="23"/>
+      <c r="E290" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F290" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G290" s="3"/>
       <c r="H290" s="6">
         <v>0</v>
@@ -6889,8 +11063,12 @@
       <c r="D291" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E291" s="23"/>
-      <c r="F291" s="23"/>
+      <c r="E291" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F291" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G291" s="3" t="s">
         <v>128</v>
       </c>
@@ -6903,8 +11081,12 @@
       <c r="D292" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E292" s="23"/>
-      <c r="F292" s="23"/>
+      <c r="E292" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F292" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="H292" s="6">
         <v>0</v>
       </c>
@@ -6914,8 +11096,12 @@
       <c r="D293" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E293" s="23"/>
-      <c r="F293" s="23"/>
+      <c r="E293" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F293" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G293" s="3"/>
       <c r="H293" s="6">
         <v>0</v>
@@ -6926,8 +11112,12 @@
       <c r="D294" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E294" s="23"/>
-      <c r="F294" s="23"/>
+      <c r="E294" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F294" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G294" s="3"/>
       <c r="H294" s="6">
         <v>0</v>
@@ -6938,8 +11128,12 @@
       <c r="D295" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E295" s="23"/>
-      <c r="F295" s="23"/>
+      <c r="E295" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F295" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G295" s="3"/>
       <c r="H295" s="6">
         <v>0</v>
@@ -6950,8 +11144,12 @@
       <c r="D296" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E296" s="23"/>
-      <c r="F296" s="23"/>
+      <c r="E296" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F296" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G296" s="3"/>
       <c r="H296" s="6">
         <v>0</v>
@@ -6963,8 +11161,12 @@
       <c r="D297" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E297" s="23"/>
-      <c r="F297" s="23"/>
+      <c r="E297" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F297" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G297" s="3"/>
       <c r="H297" s="6">
         <v>0</v>
@@ -6975,8 +11177,12 @@
       <c r="D298" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E298" s="23"/>
-      <c r="F298" s="23"/>
+      <c r="E298" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F298" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G298" s="3"/>
       <c r="H298" s="6">
         <v>0</v>
@@ -6992,7 +11198,9 @@
       <c r="D299" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="E299" s="23"/>
+      <c r="E299" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="F299" s="23" t="s">
         <v>72</v>
       </c>
@@ -7011,8 +11219,12 @@
       <c r="D300" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E300" s="23"/>
-      <c r="F300" s="23"/>
+      <c r="E300" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F300" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G300" s="3" t="s">
         <v>137</v>
       </c>
@@ -7025,8 +11237,12 @@
       <c r="D301" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E301" s="23"/>
-      <c r="F301" s="23"/>
+      <c r="E301" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F301" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G301" s="3"/>
       <c r="H301" s="6">
         <v>0</v>
@@ -7037,8 +11253,12 @@
       <c r="D302" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E302" s="23"/>
-      <c r="F302" s="23"/>
+      <c r="E302" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F302" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G302" s="3"/>
       <c r="H302" s="6">
         <v>0</v>
@@ -7049,8 +11269,12 @@
       <c r="D303" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E303" s="23"/>
-      <c r="F303" s="23"/>
+      <c r="E303" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F303" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G303" s="3"/>
       <c r="H303" s="6">
         <v>0</v>
@@ -7061,8 +11285,12 @@
       <c r="D304" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E304" s="23"/>
-      <c r="F304" s="23"/>
+      <c r="E304" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F304" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G304" s="3"/>
       <c r="H304" s="6">
         <v>0</v>
@@ -7073,8 +11301,12 @@
       <c r="D305" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E305" s="23"/>
-      <c r="F305" s="23"/>
+      <c r="E305" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F305" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G305" s="3"/>
       <c r="H305" s="6">
         <v>0</v>
@@ -7086,8 +11318,12 @@
       <c r="D306" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E306" s="23"/>
-      <c r="F306" s="23"/>
+      <c r="E306" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F306" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G306" s="3"/>
       <c r="H306" s="6">
         <v>0</v>
@@ -7098,8 +11334,12 @@
       <c r="D307" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E307" s="23"/>
-      <c r="F307" s="23"/>
+      <c r="E307" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F307" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G307" s="3"/>
       <c r="H307" s="6">
         <v>0</v>
@@ -7116,9 +11356,11 @@
       <c r="E308" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="F308" s="23"/>
+      <c r="F308" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G308" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H308" s="6">
         <v>3</v>
@@ -7130,8 +11372,12 @@
       <c r="D309" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E309" s="23"/>
-      <c r="F309" s="23"/>
+      <c r="E309" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F309" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G309" s="3"/>
       <c r="H309" s="6">
         <v>10</v>
@@ -7143,8 +11389,12 @@
       <c r="D310" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E310" s="23"/>
-      <c r="F310" s="23"/>
+      <c r="E310" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F310" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G310" s="3"/>
       <c r="H310" s="6">
         <v>0</v>
@@ -7156,8 +11406,12 @@
       <c r="D311" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E311" s="23"/>
-      <c r="F311" s="23"/>
+      <c r="E311" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F311" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G311" s="3"/>
       <c r="H311" s="6">
         <v>5</v>
@@ -7169,8 +11423,12 @@
       <c r="D312" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E312" s="23"/>
-      <c r="F312" s="23"/>
+      <c r="E312" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F312" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G312" s="3"/>
       <c r="H312" s="6">
         <v>5</v>
@@ -7182,8 +11440,12 @@
       <c r="D313" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E313" s="23"/>
-      <c r="F313" s="23"/>
+      <c r="E313" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F313" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G313" s="3"/>
       <c r="H313" s="6">
         <v>2</v>
@@ -7195,8 +11457,12 @@
       <c r="D314" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E314" s="23"/>
-      <c r="F314" s="23"/>
+      <c r="E314" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F314" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G314" s="3"/>
       <c r="H314" s="6">
         <v>1</v>
@@ -7208,8 +11474,12 @@
       <c r="D315" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E315" s="23"/>
-      <c r="F315" s="23"/>
+      <c r="E315" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F315" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G315" s="3"/>
       <c r="H315" s="6">
         <v>1</v>
@@ -7226,7 +11496,9 @@
       <c r="E316" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="F316" s="23"/>
+      <c r="F316" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G316" s="3" t="s">
         <v>139</v>
       </c>
@@ -7239,8 +11511,12 @@
       <c r="D317" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E317" s="23"/>
-      <c r="F317" s="23"/>
+      <c r="E317" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F317" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G317" s="3"/>
       <c r="H317" s="6">
         <v>0</v>
@@ -7251,8 +11527,12 @@
       <c r="D318" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E318" s="23"/>
-      <c r="F318" s="23"/>
+      <c r="E318" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F318" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G318" s="3"/>
       <c r="H318" s="6">
         <v>0</v>
@@ -7263,8 +11543,12 @@
       <c r="D319" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E319" s="23"/>
-      <c r="F319" s="23"/>
+      <c r="E319" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F319" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G319" s="3"/>
       <c r="H319" s="6">
         <v>0</v>
@@ -7275,8 +11559,12 @@
       <c r="D320" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E320" s="23"/>
-      <c r="F320" s="23"/>
+      <c r="E320" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F320" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G320" s="3"/>
       <c r="H320" s="6">
         <v>0</v>
@@ -7287,8 +11575,12 @@
       <c r="D321" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E321" s="23"/>
-      <c r="F321" s="23"/>
+      <c r="E321" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F321" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G321" s="3"/>
       <c r="H321" s="6">
         <v>0</v>
@@ -7300,8 +11592,12 @@
       <c r="D322" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E322" s="23"/>
-      <c r="F322" s="23"/>
+      <c r="E322" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F322" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G322" s="3"/>
       <c r="H322" s="6">
         <v>0</v>
@@ -7313,8 +11609,12 @@
       <c r="D323" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E323" s="23"/>
-      <c r="F323" s="23"/>
+      <c r="E323" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F323" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G323" s="3"/>
       <c r="H323" s="6">
         <v>0</v>
@@ -7328,8 +11628,12 @@
       <c r="D324" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E324" s="23"/>
-      <c r="F324" s="23"/>
+      <c r="E324" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F324" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G324" s="3" t="s">
         <v>121</v>
       </c>
@@ -7342,8 +11646,12 @@
       <c r="D325" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E325" s="23"/>
-      <c r="F325" s="23"/>
+      <c r="E325" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F325" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G325" s="3"/>
       <c r="H325" s="6">
         <v>0</v>
@@ -7354,8 +11662,12 @@
       <c r="D326" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E326" s="23"/>
-      <c r="F326" s="23"/>
+      <c r="E326" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F326" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G326" s="3"/>
       <c r="H326" s="6">
         <v>0</v>
@@ -7366,8 +11678,12 @@
       <c r="D327" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E327" s="23"/>
-      <c r="F327" s="23"/>
+      <c r="E327" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F327" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G327" s="3"/>
       <c r="H327" s="6">
         <v>0</v>
@@ -7378,8 +11694,12 @@
       <c r="D328" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E328" s="23"/>
-      <c r="F328" s="23"/>
+      <c r="E328" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F328" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G328" s="3"/>
       <c r="H328" s="6">
         <v>0</v>
@@ -7390,8 +11710,12 @@
       <c r="D329" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E329" s="23"/>
-      <c r="F329" s="23"/>
+      <c r="E329" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F329" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G329" s="3"/>
       <c r="H329" s="6">
         <v>0</v>
@@ -7403,8 +11727,12 @@
       <c r="D330" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E330" s="23"/>
-      <c r="F330" s="23"/>
+      <c r="E330" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F330" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G330" s="3"/>
       <c r="H330" s="6">
         <v>0</v>
@@ -7416,8 +11744,12 @@
       <c r="D331" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E331" s="23"/>
-      <c r="F331" s="23"/>
+      <c r="E331" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F331" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G331" s="3"/>
       <c r="H331" s="6">
         <v>0</v>
@@ -7431,13 +11763,17 @@
       <c r="D332" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E332" s="23"/>
-      <c r="F332" s="23"/>
+      <c r="E332" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F332" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G332" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H332" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="333" spans="2:8" x14ac:dyDescent="0.45">
@@ -7445,8 +11781,12 @@
       <c r="D333" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E333" s="23"/>
-      <c r="F333" s="23"/>
+      <c r="E333" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F333" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G333" s="3"/>
       <c r="H333" s="6">
         <v>0</v>
@@ -7457,8 +11797,12 @@
       <c r="D334" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E334" s="23"/>
-      <c r="F334" s="23"/>
+      <c r="E334" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F334" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G334" s="3"/>
       <c r="H334" s="6">
         <v>0</v>
@@ -7469,8 +11813,12 @@
       <c r="D335" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E335" s="23"/>
-      <c r="F335" s="23"/>
+      <c r="E335" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F335" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G335" s="3"/>
       <c r="H335" s="6">
         <v>0</v>
@@ -7481,8 +11829,12 @@
       <c r="D336" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E336" s="23"/>
-      <c r="F336" s="23"/>
+      <c r="E336" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F336" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G336" s="3"/>
       <c r="H336" s="6">
         <v>0</v>
@@ -7493,8 +11845,12 @@
       <c r="D337" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E337" s="23"/>
-      <c r="F337" s="23"/>
+      <c r="E337" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F337" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G337" s="3"/>
       <c r="H337" s="6">
         <v>0</v>
@@ -7506,8 +11862,12 @@
       <c r="D338" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E338" s="23"/>
-      <c r="F338" s="23"/>
+      <c r="E338" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F338" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G338" s="3"/>
       <c r="H338" s="6">
         <v>0</v>
@@ -7518,8 +11878,12 @@
       <c r="D339" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E339" s="23"/>
-      <c r="F339" s="23"/>
+      <c r="E339" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F339" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G339" s="3"/>
       <c r="H339" s="6">
         <v>0</v>
@@ -7536,9 +11900,11 @@
       <c r="E340" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="F340" s="23"/>
+      <c r="F340" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G340" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H340" s="6">
         <v>5</v>
@@ -7550,8 +11916,12 @@
       <c r="D341" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E341" s="23"/>
-      <c r="F341" s="23"/>
+      <c r="E341" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F341" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G341" s="3"/>
       <c r="H341" s="6">
         <v>0</v>
@@ -7563,8 +11933,12 @@
       <c r="D342" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E342" s="23"/>
-      <c r="F342" s="23"/>
+      <c r="E342" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F342" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G342" s="3"/>
       <c r="H342" s="6">
         <v>0</v>
@@ -7576,8 +11950,12 @@
       <c r="D343" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E343" s="23"/>
-      <c r="F343" s="23"/>
+      <c r="E343" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F343" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G343" s="3"/>
       <c r="H343" s="6">
         <v>0</v>
@@ -7589,8 +11967,12 @@
       <c r="D344" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E344" s="23"/>
-      <c r="F344" s="23"/>
+      <c r="E344" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F344" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G344" s="3"/>
       <c r="H344" s="6">
         <v>0</v>
@@ -7602,8 +11984,12 @@
       <c r="D345" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E345" s="23"/>
-      <c r="F345" s="23"/>
+      <c r="E345" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F345" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G345" s="3"/>
       <c r="H345" s="6">
         <v>0</v>
@@ -7615,8 +12001,12 @@
       <c r="D346" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E346" s="23"/>
-      <c r="F346" s="23"/>
+      <c r="E346" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F346" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G346" s="3"/>
       <c r="H346" s="6">
         <v>0</v>
@@ -7628,8 +12018,12 @@
       <c r="D347" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E347" s="23"/>
-      <c r="F347" s="23"/>
+      <c r="E347" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F347" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G347" s="3"/>
       <c r="H347" s="6">
         <v>0</v>
@@ -7666,8 +12060,12 @@
       <c r="D349" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E349" s="23"/>
-      <c r="F349" s="23"/>
+      <c r="E349" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F349" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G349" s="3" t="s">
         <v>137</v>
       </c>
@@ -7680,8 +12078,12 @@
       <c r="D350" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E350" s="23"/>
-      <c r="F350" s="23"/>
+      <c r="E350" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F350" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G350" s="3"/>
       <c r="H350" s="6">
         <v>0</v>
@@ -7692,8 +12094,12 @@
       <c r="D351" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E351" s="23"/>
-      <c r="F351" s="23"/>
+      <c r="E351" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F351" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G351" s="3"/>
       <c r="H351" s="6">
         <v>0</v>
@@ -7704,8 +12110,12 @@
       <c r="D352" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E352" s="23"/>
-      <c r="F352" s="23"/>
+      <c r="E352" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F352" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G352" s="3"/>
       <c r="H352" s="6">
         <v>0</v>
@@ -7716,8 +12126,12 @@
       <c r="D353" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E353" s="23"/>
-      <c r="F353" s="23"/>
+      <c r="E353" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F353" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G353" s="3"/>
       <c r="H353" s="6">
         <v>0</v>
@@ -7728,8 +12142,12 @@
       <c r="D354" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E354" s="23"/>
-      <c r="F354" s="23"/>
+      <c r="E354" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F354" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G354" s="3"/>
       <c r="H354" s="6">
         <v>0</v>
@@ -7741,8 +12159,12 @@
       <c r="D355" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E355" s="23"/>
-      <c r="F355" s="23"/>
+      <c r="E355" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F355" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G355" s="3"/>
       <c r="H355" s="6">
         <v>0</v>
@@ -7753,8 +12175,12 @@
       <c r="D356" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E356" s="23"/>
-      <c r="F356" s="23"/>
+      <c r="E356" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F356" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G356" s="3"/>
       <c r="H356" s="6">
         <v>0</v>
@@ -7771,9 +12197,11 @@
       <c r="E357" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="F357" s="23"/>
+      <c r="F357" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G357" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H357" s="6">
         <v>3</v>
@@ -7785,8 +12213,12 @@
       <c r="D358" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E358" s="23"/>
-      <c r="F358" s="23"/>
+      <c r="E358" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F358" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G358" s="3"/>
       <c r="H358" s="6">
         <v>10</v>
@@ -7798,8 +12230,12 @@
       <c r="D359" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E359" s="23"/>
-      <c r="F359" s="23"/>
+      <c r="E359" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F359" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G359" s="3"/>
       <c r="H359" s="6">
         <v>0</v>
@@ -7811,8 +12247,12 @@
       <c r="D360" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E360" s="23"/>
-      <c r="F360" s="23"/>
+      <c r="E360" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F360" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G360" s="3"/>
       <c r="H360" s="6">
         <v>5</v>
@@ -7824,8 +12264,12 @@
       <c r="D361" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E361" s="23"/>
-      <c r="F361" s="23"/>
+      <c r="E361" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F361" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G361" s="3"/>
       <c r="H361" s="6">
         <v>5</v>
@@ -7837,8 +12281,12 @@
       <c r="D362" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E362" s="23"/>
-      <c r="F362" s="23"/>
+      <c r="E362" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F362" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G362" s="3"/>
       <c r="H362" s="6">
         <v>2</v>
@@ -7850,8 +12298,12 @@
       <c r="D363" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E363" s="23"/>
-      <c r="F363" s="23"/>
+      <c r="E363" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F363" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G363" s="3"/>
       <c r="H363" s="6">
         <v>1</v>
@@ -7863,8 +12315,12 @@
       <c r="D364" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E364" s="23"/>
-      <c r="F364" s="23"/>
+      <c r="E364" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F364" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G364" s="3"/>
       <c r="H364" s="6">
         <v>1</v>
@@ -7881,7 +12337,9 @@
       <c r="E365" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="F365" s="23"/>
+      <c r="F365" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G365" s="3" t="s">
         <v>139</v>
       </c>
@@ -7894,8 +12352,12 @@
       <c r="D366" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E366" s="23"/>
-      <c r="F366" s="23"/>
+      <c r="E366" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F366" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G366" s="3"/>
       <c r="H366" s="6">
         <v>0</v>
@@ -7906,8 +12368,12 @@
       <c r="D367" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E367" s="23"/>
-      <c r="F367" s="23"/>
+      <c r="E367" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F367" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G367" s="3"/>
       <c r="H367" s="6">
         <v>0</v>
@@ -7918,8 +12384,12 @@
       <c r="D368" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E368" s="23"/>
-      <c r="F368" s="23"/>
+      <c r="E368" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F368" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G368" s="3"/>
       <c r="H368" s="6">
         <v>0</v>
@@ -7930,8 +12400,12 @@
       <c r="D369" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E369" s="23"/>
-      <c r="F369" s="23"/>
+      <c r="E369" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F369" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G369" s="3"/>
       <c r="H369" s="6">
         <v>0</v>
@@ -7942,8 +12416,12 @@
       <c r="D370" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E370" s="23"/>
-      <c r="F370" s="23"/>
+      <c r="E370" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F370" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G370" s="3"/>
       <c r="H370" s="6">
         <v>0</v>
@@ -7955,8 +12433,12 @@
       <c r="D371" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E371" s="23"/>
-      <c r="F371" s="23"/>
+      <c r="E371" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F371" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G371" s="3"/>
       <c r="H371" s="6">
         <v>0</v>
@@ -7968,8 +12450,12 @@
       <c r="D372" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E372" s="23"/>
-      <c r="F372" s="23"/>
+      <c r="E372" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F372" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G372" s="3"/>
       <c r="H372" s="6">
         <v>0</v>
@@ -7983,13 +12469,17 @@
       <c r="D373" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E373" s="23"/>
-      <c r="F373" s="23"/>
+      <c r="E373" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F373" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G373" s="3" t="s">
         <v>121</v>
       </c>
       <c r="H373" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="374" spans="2:8" x14ac:dyDescent="0.45">
@@ -7997,8 +12487,12 @@
       <c r="D374" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E374" s="23"/>
-      <c r="F374" s="23"/>
+      <c r="E374" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F374" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G374" s="3"/>
       <c r="H374" s="6">
         <v>0</v>
@@ -8009,8 +12503,12 @@
       <c r="D375" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E375" s="23"/>
-      <c r="F375" s="23"/>
+      <c r="E375" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F375" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G375" s="3"/>
       <c r="H375" s="6">
         <v>0</v>
@@ -8021,8 +12519,12 @@
       <c r="D376" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E376" s="23"/>
-      <c r="F376" s="23"/>
+      <c r="E376" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F376" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G376" s="3"/>
       <c r="H376" s="6">
         <v>0</v>
@@ -8033,8 +12535,12 @@
       <c r="D377" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E377" s="23"/>
-      <c r="F377" s="23"/>
+      <c r="E377" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F377" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G377" s="3"/>
       <c r="H377" s="6">
         <v>0</v>
@@ -8045,8 +12551,12 @@
       <c r="D378" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E378" s="23"/>
-      <c r="F378" s="23"/>
+      <c r="E378" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F378" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G378" s="3"/>
       <c r="H378" s="6">
         <v>0</v>
@@ -8058,8 +12568,12 @@
       <c r="D379" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E379" s="23"/>
-      <c r="F379" s="23"/>
+      <c r="E379" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F379" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G379" s="3"/>
       <c r="H379" s="6">
         <v>0</v>
@@ -8071,8 +12585,12 @@
       <c r="D380" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E380" s="23"/>
-      <c r="F380" s="23"/>
+      <c r="E380" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F380" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G380" s="3"/>
       <c r="H380" s="6">
         <v>0</v>
@@ -8086,13 +12604,17 @@
       <c r="D381" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E381" s="23"/>
-      <c r="F381" s="23"/>
+      <c r="E381" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F381" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G381" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H381" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="382" spans="2:8" x14ac:dyDescent="0.45">
@@ -8100,8 +12622,12 @@
       <c r="D382" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E382" s="23"/>
-      <c r="F382" s="23"/>
+      <c r="E382" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F382" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G382" s="3"/>
       <c r="H382" s="6">
         <v>0</v>
@@ -8112,8 +12638,12 @@
       <c r="D383" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E383" s="23"/>
-      <c r="F383" s="23"/>
+      <c r="E383" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F383" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G383" s="3"/>
       <c r="H383" s="6">
         <v>0</v>
@@ -8124,8 +12654,12 @@
       <c r="D384" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E384" s="23"/>
-      <c r="F384" s="23"/>
+      <c r="E384" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F384" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G384" s="3"/>
       <c r="H384" s="6">
         <v>0</v>
@@ -8136,8 +12670,12 @@
       <c r="D385" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E385" s="23"/>
-      <c r="F385" s="23"/>
+      <c r="E385" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F385" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G385" s="3"/>
       <c r="H385" s="6">
         <v>0</v>
@@ -8148,8 +12686,12 @@
       <c r="D386" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E386" s="23"/>
-      <c r="F386" s="23"/>
+      <c r="E386" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F386" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G386" s="3"/>
       <c r="H386" s="6">
         <v>0</v>
@@ -8161,8 +12703,12 @@
       <c r="D387" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E387" s="23"/>
-      <c r="F387" s="23"/>
+      <c r="E387" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F387" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G387" s="3"/>
       <c r="H387" s="6">
         <v>0</v>
@@ -8173,8 +12719,12 @@
       <c r="D388" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E388" s="23"/>
-      <c r="F388" s="23"/>
+      <c r="E388" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F388" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G388" s="3"/>
       <c r="H388" s="6">
         <v>0</v>
@@ -8191,9 +12741,11 @@
       <c r="E389" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="F389" s="23"/>
+      <c r="F389" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="G389" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H389" s="6">
         <v>5</v>
@@ -8205,8 +12757,12 @@
       <c r="D390" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E390" s="23"/>
-      <c r="F390" s="23"/>
+      <c r="E390" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F390" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G390" s="3"/>
       <c r="H390" s="6">
         <v>0</v>
@@ -8218,8 +12774,12 @@
       <c r="D391" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E391" s="23"/>
-      <c r="F391" s="23"/>
+      <c r="E391" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F391" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G391" s="3"/>
       <c r="H391" s="6">
         <v>0</v>
@@ -8231,8 +12791,12 @@
       <c r="D392" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E392" s="23"/>
-      <c r="F392" s="23"/>
+      <c r="E392" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F392" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G392" s="3"/>
       <c r="H392" s="6">
         <v>0</v>
@@ -8244,8 +12808,12 @@
       <c r="D393" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E393" s="23"/>
-      <c r="F393" s="23"/>
+      <c r="E393" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F393" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G393" s="3"/>
       <c r="H393" s="6">
         <v>0</v>
@@ -8257,8 +12825,12 @@
       <c r="D394" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E394" s="23"/>
-      <c r="F394" s="23"/>
+      <c r="E394" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F394" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G394" s="3"/>
       <c r="H394" s="6">
         <v>0</v>
@@ -8270,8 +12842,12 @@
       <c r="D395" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E395" s="23"/>
-      <c r="F395" s="23"/>
+      <c r="E395" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F395" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G395" s="3"/>
       <c r="H395" s="6">
         <v>0</v>
@@ -8283,8 +12859,12 @@
       <c r="D396" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E396" s="23"/>
-      <c r="F396" s="23"/>
+      <c r="E396" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F396" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="G396" s="3"/>
       <c r="H396" s="6">
         <v>0</v>
@@ -8293,13 +12873,13 @@
     <row r="397" spans="2:8" x14ac:dyDescent="0.45">
       <c r="H397" s="7">
         <f>SUM(H3:H396)</f>
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="398" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="H398" s="37">
+      <c r="H398" s="29">
         <f>ROUNDUP(H397*1.3,0)</f>
-        <v>440</v>
+        <v>444</v>
       </c>
     </row>
   </sheetData>
@@ -8310,19 +12890,19 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{8F217F8F-0424-4D09-8EF1-76A058388FDB}">
           <x14:formula1>
-            <xm:f>Sheet1!$E$4:$E$10</xm:f>
+            <xm:f>項目表!$E$4:$E$10</xm:f>
           </x14:formula1>
           <xm:sqref>D259:D298 D300:D347 D112:D175 D63:D110 D177:D208 D38:D61 D4:D36 D349:D396 D210:D257</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{3C1A2A9C-A006-4E67-9C3E-9EABE379EDE1}">
           <x14:formula1>
-            <xm:f>Sheet1!$E$3:$E$10</xm:f>
+            <xm:f>項目表!$E$3:$E$10</xm:f>
           </x14:formula1>
           <xm:sqref>D299 D111 D176 D209 D258 D348 D62</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{0C8521CF-0CAB-467C-BD0E-C1BF122F2C71}">
           <x14:formula1>
-            <xm:f>Sheet1!$E$3:$E$11</xm:f>
+            <xm:f>項目表!$E$3:$E$11</xm:f>
           </x14:formula1>
           <xm:sqref>D37 D3</xm:sqref>
         </x14:dataValidation>
@@ -8332,7 +12912,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82D13BD5-9ECF-45BC-A450-6172FCD0B19D}">
   <dimension ref="B2:F24"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
@@ -8347,10 +12927,10 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B2" s="35" t="s">
+      <c r="B2" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="35"/>
+      <c r="C2" s="33"/>
       <c r="D2" s="5" t="s">
         <v>0</v>
       </c>
@@ -8373,7 +12953,7 @@
       </c>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B4" s="29" t="s">
+      <c r="B4" s="30" t="s">
         <v>30</v>
       </c>
       <c r="C4" s="2" t="s">
@@ -8387,7 +12967,7 @@
       </c>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B5" s="30"/>
+      <c r="B5" s="31"/>
       <c r="C5" s="2" t="s">
         <v>29</v>
       </c>
@@ -8399,7 +12979,7 @@
       </c>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B6" s="31"/>
+      <c r="B6" s="32"/>
       <c r="C6" s="3" t="s">
         <v>21</v>
       </c>
@@ -8411,7 +12991,7 @@
       </c>
     </row>
     <row r="7" spans="2:6" ht="72" x14ac:dyDescent="0.45">
-      <c r="B7" s="27" t="s">
+      <c r="B7" s="34" t="s">
         <v>4</v>
       </c>
       <c r="C7" s="3" t="s">
@@ -8425,7 +13005,7 @@
       </c>
     </row>
     <row r="8" spans="2:6" ht="180" x14ac:dyDescent="0.45">
-      <c r="B8" s="27"/>
+      <c r="B8" s="34"/>
       <c r="C8" s="3" t="s">
         <v>22</v>
       </c>
@@ -8459,16 +13039,16 @@
       </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B10" s="29" t="s">
+      <c r="B10" s="30" t="s">
         <v>15</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="32" t="s">
+      <c r="D10" s="36" t="s">
         <v>42</v>
       </c>
-      <c r="E10" s="29">
+      <c r="E10" s="30">
         <f>240/8</f>
         <v>30</v>
       </c>
@@ -8477,23 +13057,23 @@
       </c>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B11" s="30"/>
+      <c r="B11" s="31"/>
       <c r="C11" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D11" s="33"/>
-      <c r="E11" s="30"/>
+      <c r="D11" s="37"/>
+      <c r="E11" s="31"/>
     </row>
     <row r="12" spans="2:6" ht="44.4" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B12" s="31"/>
+      <c r="B12" s="32"/>
       <c r="C12" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D12" s="34"/>
-      <c r="E12" s="31"/>
+      <c r="D12" s="38"/>
+      <c r="E12" s="32"/>
     </row>
     <row r="13" spans="2:6" ht="72" x14ac:dyDescent="0.45">
-      <c r="B13" s="29" t="s">
+      <c r="B13" s="30" t="s">
         <v>12</v>
       </c>
       <c r="C13" s="2" t="s">
@@ -8507,7 +13087,7 @@
       </c>
     </row>
     <row r="14" spans="2:6" ht="36" x14ac:dyDescent="0.45">
-      <c r="B14" s="31"/>
+      <c r="B14" s="32"/>
       <c r="C14" s="2" t="s">
         <v>11</v>
       </c>
@@ -8519,7 +13099,7 @@
       </c>
     </row>
     <row r="15" spans="2:6" ht="342" x14ac:dyDescent="0.45">
-      <c r="B15" s="29" t="s">
+      <c r="B15" s="30" t="s">
         <v>8</v>
       </c>
       <c r="C15" s="2" t="s">
@@ -8537,7 +13117,7 @@
       </c>
     </row>
     <row r="16" spans="2:6" ht="342" x14ac:dyDescent="0.45">
-      <c r="B16" s="30"/>
+      <c r="B16" s="31"/>
       <c r="C16" s="2" t="s">
         <v>3</v>
       </c>
@@ -8553,7 +13133,7 @@
       </c>
     </row>
     <row r="17" spans="2:6" ht="342" x14ac:dyDescent="0.45">
-      <c r="B17" s="30"/>
+      <c r="B17" s="31"/>
       <c r="C17" s="2" t="s">
         <v>14</v>
       </c>
@@ -8569,7 +13149,7 @@
       </c>
     </row>
     <row r="18" spans="2:6" ht="54" x14ac:dyDescent="0.45">
-      <c r="B18" s="30"/>
+      <c r="B18" s="31"/>
       <c r="C18" s="2" t="s">
         <v>17</v>
       </c>
@@ -8585,7 +13165,7 @@
       </c>
     </row>
     <row r="19" spans="2:6" ht="270" x14ac:dyDescent="0.45">
-      <c r="B19" s="31"/>
+      <c r="B19" s="32"/>
       <c r="C19" s="2" t="s">
         <v>19</v>
       </c>
@@ -8601,13 +13181,13 @@
       </c>
     </row>
     <row r="20" spans="2:6" ht="36" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B20" s="27" t="s">
+      <c r="B20" s="34" t="s">
         <v>20</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D20" s="28" t="s">
+      <c r="D20" s="35" t="s">
         <v>26</v>
       </c>
       <c r="E20" s="2">
@@ -8615,11 +13195,11 @@
       </c>
     </row>
     <row r="21" spans="2:6" ht="36" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B21" s="27"/>
+      <c r="B21" s="34"/>
       <c r="C21" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D21" s="28"/>
+      <c r="D21" s="35"/>
       <c r="E21" s="2">
         <v>5</v>
       </c>
@@ -8648,23 +13228,23 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="B10:B12"/>
+    <mergeCell ref="D10:D12"/>
+    <mergeCell ref="B15:B19"/>
     <mergeCell ref="E10:E12"/>
     <mergeCell ref="B13:B14"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B4:B6"/>
     <mergeCell ref="B7:B8"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="B10:B12"/>
-    <mergeCell ref="D10:D12"/>
-    <mergeCell ref="B15:B19"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B14BFA20-2618-4448-84AE-35D356F77BBD}">
   <dimension ref="C2:G11"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>

--- a/見積もり/NTTDU様-案件管理-概算見積もり_最新.xlsx
+++ b/見積もり/NTTDU様-案件管理-概算見積もり_最新.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ishid\Desktop\project_management\見積もり\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\project_management\見積もり\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6760448-E5F0-4FD3-AC13-E37414981CEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{031F6DE0-0AF5-449C-8493-CB431E8F45DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{15EF4DE1-B99D-4880-9633-29B1123E0732}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1476" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1476" uniqueCount="179">
   <si>
     <t>備考</t>
     <rPh sb="0" eb="2">
@@ -1004,32 +1004,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>以下の流れを確認する。
-マテリアルの管理～マテリアルの作成～マテリアルの確認～マテリアルのデプロイ～マテリアルのデプロイ後の確認</t>
-    <rPh sb="0" eb="2">
-      <t>イカ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>ナガ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>カクニン</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>カンリ</t>
-    </rPh>
-    <rPh sb="27" eb="29">
-      <t>サクセイ</t>
-    </rPh>
-    <rPh sb="60" eb="61">
-      <t>ゴ</t>
-    </rPh>
-    <rPh sb="62" eb="64">
-      <t>カクニン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>マテリアルのデプロイ後の確認</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -2425,6 +2399,132 @@
     </rPh>
     <rPh sb="77" eb="79">
       <t>タイオウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>以下の流れを検討する。
+# 検討対象
+・ユーザー（年度別）の作成
+・ユーザー（年度別）のクラスへの割り当て
+# 作成ツール/システム
+　なし（※ギブリー様と相談）/ 簡易的なもの</t>
+    <rPh sb="0" eb="2">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ナガ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ケントウ</t>
+    </rPh>
+    <rPh sb="49" eb="50">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="51" eb="52">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>以下の流れを検討する。
+# 検討対象
+・ユーザー（年度別）の確認
+・ユーザー（年度別）のクラスへの割り当ての確認
+# 作成ツール/システム
+　なし（※ギブリー様と相談）/ 簡易的なもの</t>
+    <rPh sb="0" eb="2">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ナガ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ケントウ</t>
+    </rPh>
+    <rPh sb="54" eb="56">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>以下の流れを検討する。
+# 検討対象
+・ユーザー（年度別）の確認
+・ユーザー（年度別）のスペースへの割り当ての確認
+# 作成ツール/システム
+　簡易的なもの</t>
+    <rPh sb="0" eb="2">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ナガ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ケントウ</t>
+    </rPh>
+    <rPh sb="55" eb="57">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>以下の流れを検討する。
+# 検討対象
+・ユーザー（年度別）の作成
+・ユーザー（年度別）のスペースへの割り当て
+# 作成ツール/システム
+　簡易的なもの</t>
+    <rPh sb="0" eb="2">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ナガ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ケントウ</t>
+    </rPh>
+    <rPh sb="50" eb="51">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="52" eb="53">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>以下の流れを確認する。
+マテリアルの管理～マテリアルの作成～マテリアルの確認～マテリアルのデプロイ～マテリアルのデプロイ後の確認
+※マテリアル＝テキスト・演習・動画・章テスト・修了判定テスト・アンケート</t>
+    <rPh sb="0" eb="2">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ナガ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>カンリ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="60" eb="61">
+      <t>ゴ</t>
+    </rPh>
+    <rPh sb="62" eb="64">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="77" eb="79">
+      <t>エンシュウ</t>
+    </rPh>
+    <rPh sb="80" eb="82">
+      <t>ドウガ</t>
+    </rPh>
+    <rPh sb="88" eb="92">
+      <t>シュウリョウハンテイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2700,6 +2800,21 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -2708,15 +2823,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -2727,14 +2833,8 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3074,11 +3174,11 @@
       </c>
     </row>
     <row r="3" spans="2:4" ht="54" x14ac:dyDescent="0.45">
-      <c r="B3" s="41" t="s">
-        <v>122</v>
+      <c r="B3" s="32" t="s">
+        <v>121</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D3" s="6">
         <f>SUM('新入社員研修（詳細）'!H3:H36)</f>
@@ -3088,16 +3188,16 @@
     <row r="4" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
       <c r="B4" s="18"/>
       <c r="C4" s="27" t="s">
-        <v>130</v>
-      </c>
-      <c r="D4" s="40">
+        <v>129</v>
+      </c>
+      <c r="D4" s="31">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
       <c r="B5" s="18"/>
       <c r="C5" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D5" s="6">
         <v>2</v>
@@ -3155,7 +3255,7 @@
     <row r="13" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
       <c r="B13" s="18"/>
       <c r="C13" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D13" s="6">
         <v>1</v>
@@ -3213,7 +3313,7 @@
     <row r="21" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
       <c r="B21" s="18"/>
       <c r="C21" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D21" s="6">
         <v>0</v>
@@ -3271,7 +3371,7 @@
     <row r="29" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
       <c r="B29" s="18"/>
       <c r="C29" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D29" s="6">
         <v>1</v>
@@ -3327,11 +3427,11 @@
       </c>
     </row>
     <row r="37" spans="2:4" ht="36" x14ac:dyDescent="0.45">
-      <c r="B37" s="41" t="s">
-        <v>123</v>
+      <c r="B37" s="32" t="s">
+        <v>122</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D37" s="6">
         <f>SUM('新入社員研修（詳細）'!H37:H61)</f>
@@ -3341,9 +3441,9 @@
     <row r="38" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
       <c r="B38" s="18"/>
       <c r="C38" s="27" t="s">
-        <v>132</v>
-      </c>
-      <c r="D38" s="40">
+        <v>131</v>
+      </c>
+      <c r="D38" s="31">
         <v>1</v>
       </c>
     </row>
@@ -3399,7 +3499,7 @@
     <row r="46" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
       <c r="B46" s="18"/>
       <c r="C46" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D46" s="6">
         <v>2</v>
@@ -3457,7 +3557,7 @@
     <row r="54" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
       <c r="B54" s="18"/>
       <c r="C54" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D54" s="6">
         <v>1</v>
@@ -3513,23 +3613,23 @@
       </c>
     </row>
     <row r="62" spans="2:4" ht="72" x14ac:dyDescent="0.45">
-      <c r="B62" s="41" t="s">
-        <v>101</v>
+      <c r="B62" s="32" t="s">
+        <v>100</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D62" s="6">
         <f>SUM('新入社員研修（詳細）'!H62:H110)</f>
-        <v>72</v>
+        <v>84</v>
       </c>
     </row>
     <row r="63" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
       <c r="B63" s="18"/>
       <c r="C63" s="27" t="s">
-        <v>160</v>
-      </c>
-      <c r="D63" s="40">
+        <v>159</v>
+      </c>
+      <c r="D63" s="31">
         <v>2</v>
       </c>
     </row>
@@ -3585,7 +3685,7 @@
     <row r="71" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
       <c r="B71" s="18"/>
       <c r="C71" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D71" s="6">
         <v>1</v>
@@ -3643,7 +3743,7 @@
     <row r="79" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
       <c r="B79" s="18"/>
       <c r="C79" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D79" s="6">
         <v>2</v>
@@ -3701,7 +3801,7 @@
     <row r="87" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
       <c r="B87" s="18"/>
       <c r="C87" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D87" s="6">
         <v>1</v>
@@ -3759,7 +3859,7 @@
     <row r="95" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
       <c r="B95" s="18"/>
       <c r="C95" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D95" s="6">
         <v>1</v>
@@ -3817,7 +3917,7 @@
     <row r="103" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
       <c r="B103" s="18"/>
       <c r="C103" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D103" s="6">
         <v>1</v>
@@ -3873,23 +3973,23 @@
       </c>
     </row>
     <row r="111" spans="2:4" ht="90" x14ac:dyDescent="0.45">
-      <c r="B111" s="41" t="s">
-        <v>102</v>
+      <c r="B111" s="32" t="s">
+        <v>101</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D111" s="6">
         <f>SUM('新入社員研修（詳細）'!H111:H175)</f>
-        <v>68</v>
+        <v>74</v>
       </c>
     </row>
     <row r="112" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
       <c r="B112" s="18"/>
       <c r="C112" s="27" t="s">
-        <v>133</v>
-      </c>
-      <c r="D112" s="40">
+        <v>132</v>
+      </c>
+      <c r="D112" s="31">
         <v>1</v>
       </c>
     </row>
@@ -3945,7 +4045,7 @@
     <row r="120" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
       <c r="B120" s="18"/>
       <c r="C120" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D120" s="6">
         <v>1</v>
@@ -4003,7 +4103,7 @@
     <row r="128" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
       <c r="B128" s="18"/>
       <c r="C128" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D128" s="6">
         <v>1</v>
@@ -4061,7 +4161,7 @@
     <row r="136" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
       <c r="B136" s="18"/>
       <c r="C136" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D136" s="6">
         <v>1</v>
@@ -4119,7 +4219,7 @@
     <row r="144" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
       <c r="B144" s="18"/>
       <c r="C144" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D144" s="6">
         <v>1</v>
@@ -4177,7 +4277,7 @@
     <row r="152" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
       <c r="B152" s="18"/>
       <c r="C152" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D152" s="6">
         <v>1</v>
@@ -4235,7 +4335,7 @@
     <row r="160" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
       <c r="B160" s="18"/>
       <c r="C160" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D160" s="6">
         <v>2</v>
@@ -4293,7 +4393,7 @@
     <row r="168" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
       <c r="B168" s="18"/>
       <c r="C168" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D168" s="6">
         <v>1</v>
@@ -4353,7 +4453,7 @@
         <v>52</v>
       </c>
       <c r="C176" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D176" s="6">
         <f>SUM('新入社員研修（詳細）'!H176:H208)</f>
@@ -4363,9 +4463,9 @@
     <row r="177" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
       <c r="B177" s="12"/>
       <c r="C177" s="27" t="s">
-        <v>137</v>
-      </c>
-      <c r="D177" s="40">
+        <v>136</v>
+      </c>
+      <c r="D177" s="31">
         <v>0</v>
       </c>
     </row>
@@ -4421,7 +4521,7 @@
     <row r="185" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
       <c r="B185" s="12"/>
       <c r="C185" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D185" s="6">
         <v>2</v>
@@ -4479,7 +4579,7 @@
     <row r="193" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
       <c r="B193" s="12"/>
       <c r="C193" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D193" s="6">
         <v>1</v>
@@ -4537,7 +4637,7 @@
     <row r="201" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
       <c r="B201" s="18"/>
       <c r="C201" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D201" s="6">
         <v>0</v>
@@ -4597,7 +4697,7 @@
         <v>53</v>
       </c>
       <c r="C209" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D209" s="6">
         <f>SUM('新入社員研修（詳細）'!H209:H257)</f>
@@ -4607,9 +4707,9 @@
     <row r="210" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
       <c r="B210" s="12"/>
       <c r="C210" s="27" t="s">
-        <v>137</v>
-      </c>
-      <c r="D210" s="40">
+        <v>136</v>
+      </c>
+      <c r="D210" s="31">
         <v>0</v>
       </c>
     </row>
@@ -4665,7 +4765,7 @@
     <row r="218" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
       <c r="B218" s="12"/>
       <c r="C218" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D218" s="6">
         <v>3</v>
@@ -4723,7 +4823,7 @@
     <row r="226" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
       <c r="B226" s="12"/>
       <c r="C226" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D226" s="6">
         <v>0</v>
@@ -4781,7 +4881,7 @@
     <row r="234" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="B234" s="18"/>
       <c r="C234" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D234" s="6">
         <v>0</v>
@@ -4839,7 +4939,7 @@
     <row r="242" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
       <c r="B242" s="18"/>
       <c r="C242" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D242" s="6">
         <v>1</v>
@@ -4897,7 +4997,7 @@
     <row r="250" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
       <c r="B250" s="18"/>
       <c r="C250" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D250" s="6">
         <v>0</v>
@@ -4957,7 +5057,7 @@
         <v>54</v>
       </c>
       <c r="C258" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D258" s="6">
         <f>SUM('新入社員研修（詳細）'!H258:H298)</f>
@@ -4967,9 +5067,9 @@
     <row r="259" spans="2:4" ht="108" hidden="1" x14ac:dyDescent="0.45">
       <c r="B259" s="12"/>
       <c r="C259" s="27" t="s">
-        <v>157</v>
-      </c>
-      <c r="D259" s="40">
+        <v>156</v>
+      </c>
+      <c r="D259" s="31">
         <v>2</v>
       </c>
     </row>
@@ -5024,7 +5124,7 @@
     <row r="267" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
       <c r="B267" s="12"/>
       <c r="C267" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D267" s="6">
         <v>2</v>
@@ -5082,7 +5182,7 @@
     <row r="275" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
       <c r="B275" s="18"/>
       <c r="C275" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D275" s="6">
         <v>1</v>
@@ -5140,7 +5240,7 @@
     <row r="283" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
       <c r="B283" s="18"/>
       <c r="C283" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D283" s="6">
         <v>1</v>
@@ -5197,7 +5297,7 @@
     <row r="291" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="B291" s="18"/>
       <c r="C291" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D291" s="6">
         <v>0</v>
@@ -5256,19 +5356,19 @@
         <v>55</v>
       </c>
       <c r="C299" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D299" s="6">
         <f>SUM('新入社員研修（詳細）'!H299:H347)</f>
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="300" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
       <c r="B300" s="12"/>
       <c r="C300" s="27" t="s">
-        <v>137</v>
-      </c>
-      <c r="D300" s="40">
+        <v>136</v>
+      </c>
+      <c r="D300" s="31">
         <v>0</v>
       </c>
     </row>
@@ -5324,7 +5424,7 @@
     <row r="308" spans="2:4" ht="108" hidden="1" x14ac:dyDescent="0.45">
       <c r="B308" s="12"/>
       <c r="C308" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D308" s="6">
         <v>3</v>
@@ -5382,7 +5482,7 @@
     <row r="316" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
       <c r="B316" s="12"/>
       <c r="C316" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D316" s="6">
         <v>1</v>
@@ -5440,7 +5540,7 @@
     <row r="324" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="B324" s="12"/>
       <c r="C324" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D324" s="6">
         <v>0</v>
@@ -5498,7 +5598,7 @@
     <row r="332" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
       <c r="B332" s="12"/>
       <c r="C332" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D332" s="6">
         <v>1</v>
@@ -5556,7 +5656,7 @@
     <row r="340" spans="2:4" ht="126" hidden="1" x14ac:dyDescent="0.45">
       <c r="B340" s="12"/>
       <c r="C340" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D340" s="6">
         <v>5</v>
@@ -5612,23 +5712,23 @@
       </c>
     </row>
     <row r="348" spans="2:4" ht="36" x14ac:dyDescent="0.45">
-      <c r="B348" s="41" t="s">
+      <c r="B348" s="32" t="s">
         <v>19</v>
       </c>
       <c r="C348" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D348" s="6">
         <f>SUM('新入社員研修（詳細）'!H348:H396)</f>
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="349" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
       <c r="B349" s="18"/>
       <c r="C349" s="27" t="s">
-        <v>137</v>
-      </c>
-      <c r="D349" s="40">
+        <v>136</v>
+      </c>
+      <c r="D349" s="31">
         <v>0</v>
       </c>
     </row>
@@ -5684,7 +5784,7 @@
     <row r="357" spans="2:4" ht="108" hidden="1" x14ac:dyDescent="0.45">
       <c r="B357" s="18"/>
       <c r="C357" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D357" s="6">
         <v>3</v>
@@ -5742,7 +5842,7 @@
     <row r="365" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
       <c r="B365" s="18"/>
       <c r="C365" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D365" s="6">
         <v>1</v>
@@ -5800,7 +5900,7 @@
     <row r="373" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="B373" s="18"/>
       <c r="C373" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D373" s="6">
         <v>1</v>
@@ -5858,7 +5958,7 @@
     <row r="381" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
       <c r="B381" s="18"/>
       <c r="C381" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D381" s="6">
         <v>1</v>
@@ -5916,7 +6016,7 @@
     <row r="389" spans="2:4" ht="126" hidden="1" x14ac:dyDescent="0.45">
       <c r="B389" s="18"/>
       <c r="C389" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D389" s="6">
         <v>5</v>
@@ -5974,25 +6074,25 @@
     <row r="397" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="D397" s="7">
         <f>SUM(D3:D396)</f>
-        <v>680</v>
+        <v>694</v>
       </c>
     </row>
     <row r="398" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="D398" s="29">
         <f>ROUNDUP(D397*1.3,0)</f>
-        <v>884</v>
+        <v>903</v>
       </c>
     </row>
     <row r="399" spans="2:4" x14ac:dyDescent="0.45">
       <c r="D399" s="7">
         <f>'新入社員研修（詳細）'!H397</f>
-        <v>341</v>
+        <v>355</v>
       </c>
     </row>
     <row r="400" spans="2:4" x14ac:dyDescent="0.45">
       <c r="D400" s="29">
         <f>'新入社員研修（詳細）'!H398</f>
-        <v>444</v>
+        <v>462</v>
       </c>
     </row>
   </sheetData>
@@ -6029,7 +6129,7 @@
         <v>49</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D2" s="14" t="s">
         <v>56</v>
@@ -6038,7 +6138,7 @@
         <v>66</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G2" s="5" t="s">
         <v>0</v>
@@ -6047,9 +6147,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="2:8" ht="54" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:8" ht="72" x14ac:dyDescent="0.45">
       <c r="B3" s="17" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>73</v>
@@ -6064,7 +6164,7 @@
         <v>72</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>90</v>
+        <v>178</v>
       </c>
       <c r="H3" s="6">
         <v>0</v>
@@ -6079,13 +6179,13 @@
         <v>67</v>
       </c>
       <c r="E4" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F4" s="23" t="s">
         <v>72</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H4" s="6">
         <v>1</v>
@@ -6100,13 +6200,13 @@
         <v>67</v>
       </c>
       <c r="E5" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F5" s="23" t="s">
         <v>72</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H5" s="6">
         <v>2</v>
@@ -6119,10 +6219,10 @@
         <v>57</v>
       </c>
       <c r="E6" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F6" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="6">
@@ -6136,10 +6236,10 @@
         <v>58</v>
       </c>
       <c r="E7" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F7" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="6">
@@ -6153,10 +6253,10 @@
         <v>59</v>
       </c>
       <c r="E8" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F8" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="6">
@@ -6170,10 +6270,10 @@
         <v>77</v>
       </c>
       <c r="E9" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F9" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="6">
@@ -6187,10 +6287,10 @@
         <v>80</v>
       </c>
       <c r="E10" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F10" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="6">
@@ -6204,10 +6304,10 @@
         <v>83</v>
       </c>
       <c r="E11" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F11" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="6">
@@ -6221,10 +6321,10 @@
         <v>60</v>
       </c>
       <c r="E12" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F12" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G12" s="3"/>
       <c r="H12" s="6">
@@ -6246,7 +6346,7 @@
         <v>72</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H13" s="6">
         <v>1</v>
@@ -6259,10 +6359,10 @@
         <v>57</v>
       </c>
       <c r="E14" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F14" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G14" s="3"/>
       <c r="H14" s="6">
@@ -6276,10 +6376,10 @@
         <v>58</v>
       </c>
       <c r="E15" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F15" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G15" s="3"/>
       <c r="H15" s="6">
@@ -6293,10 +6393,10 @@
         <v>59</v>
       </c>
       <c r="E16" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F16" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G16" s="3"/>
       <c r="H16" s="6">
@@ -6310,10 +6410,10 @@
         <v>77</v>
       </c>
       <c r="E17" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F17" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G17" s="3"/>
       <c r="H17" s="6">
@@ -6327,10 +6427,10 @@
         <v>80</v>
       </c>
       <c r="E18" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F18" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G18" s="3"/>
       <c r="H18" s="6">
@@ -6344,10 +6444,10 @@
         <v>83</v>
       </c>
       <c r="E19" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F19" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G19" s="3"/>
       <c r="H19" s="6">
@@ -6361,10 +6461,10 @@
         <v>60</v>
       </c>
       <c r="E20" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F20" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G20" s="3"/>
       <c r="H20" s="6">
@@ -6380,13 +6480,13 @@
         <v>67</v>
       </c>
       <c r="E21" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F21" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H21" s="6">
         <v>0</v>
@@ -6399,10 +6499,10 @@
         <v>57</v>
       </c>
       <c r="E22" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F22" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G22" s="3"/>
       <c r="H22" s="6">
@@ -6416,10 +6516,10 @@
         <v>58</v>
       </c>
       <c r="E23" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F23" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G23" s="3"/>
       <c r="H23" s="6">
@@ -6433,10 +6533,10 @@
         <v>59</v>
       </c>
       <c r="E24" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F24" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G24" s="3"/>
       <c r="H24" s="6">
@@ -6450,10 +6550,10 @@
         <v>77</v>
       </c>
       <c r="E25" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F25" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G25" s="3"/>
       <c r="H25" s="6">
@@ -6467,10 +6567,10 @@
         <v>80</v>
       </c>
       <c r="E26" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F26" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G26" s="3"/>
       <c r="H26" s="6">
@@ -6484,10 +6584,10 @@
         <v>83</v>
       </c>
       <c r="E27" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F27" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G27" s="3"/>
       <c r="H27" s="6">
@@ -6501,10 +6601,10 @@
         <v>60</v>
       </c>
       <c r="E28" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F28" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G28" s="3"/>
       <c r="H28" s="6">
@@ -6514,19 +6614,19 @@
     <row r="29" spans="2:8" ht="90" x14ac:dyDescent="0.45">
       <c r="B29" s="18"/>
       <c r="C29" s="17" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>67</v>
       </c>
       <c r="E29" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F29" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H29" s="6">
         <v>1</v>
@@ -6539,10 +6639,10 @@
         <v>57</v>
       </c>
       <c r="E30" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F30" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G30" s="3"/>
       <c r="H30" s="6">
@@ -6556,10 +6656,10 @@
         <v>58</v>
       </c>
       <c r="E31" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F31" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G31" s="3"/>
       <c r="H31" s="6">
@@ -6573,10 +6673,10 @@
         <v>59</v>
       </c>
       <c r="E32" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F32" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G32" s="3"/>
       <c r="H32" s="6">
@@ -6590,10 +6690,10 @@
         <v>77</v>
       </c>
       <c r="E33" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F33" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G33" s="3"/>
       <c r="H33" s="6">
@@ -6607,10 +6707,10 @@
         <v>80</v>
       </c>
       <c r="E34" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F34" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G34" s="3"/>
       <c r="H34" s="6">
@@ -6624,10 +6724,10 @@
         <v>83</v>
       </c>
       <c r="E35" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F35" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G35" s="3"/>
       <c r="H35" s="6">
@@ -6641,10 +6741,10 @@
         <v>60</v>
       </c>
       <c r="E36" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F36" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G36" s="3"/>
       <c r="H36" s="6">
@@ -6653,7 +6753,7 @@
     </row>
     <row r="37" spans="2:8" ht="36" x14ac:dyDescent="0.45">
       <c r="B37" s="17" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>73</v>
@@ -6668,7 +6768,7 @@
         <v>72</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H37" s="6">
         <v>0</v>
@@ -6677,19 +6777,19 @@
     <row r="38" spans="2:8" ht="90" x14ac:dyDescent="0.45">
       <c r="B38" s="18"/>
       <c r="C38" s="17" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>67</v>
       </c>
       <c r="E38" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F38" s="23" t="s">
         <v>72</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H38" s="6">
         <v>1</v>
@@ -6702,10 +6802,10 @@
         <v>57</v>
       </c>
       <c r="E39" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F39" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G39" s="3"/>
       <c r="H39" s="6">
@@ -6719,10 +6819,10 @@
         <v>58</v>
       </c>
       <c r="E40" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F40" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G40" s="3"/>
       <c r="H40" s="6">
@@ -6736,10 +6836,10 @@
         <v>59</v>
       </c>
       <c r="E41" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F41" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G41" s="3"/>
       <c r="H41" s="6">
@@ -6753,10 +6853,10 @@
         <v>77</v>
       </c>
       <c r="E42" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F42" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G42" s="3"/>
       <c r="H42" s="6">
@@ -6770,10 +6870,10 @@
         <v>80</v>
       </c>
       <c r="E43" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F43" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G43" s="3"/>
       <c r="H43" s="6">
@@ -6787,10 +6887,10 @@
         <v>83</v>
       </c>
       <c r="E44" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F44" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G44" s="3"/>
       <c r="H44" s="6">
@@ -6804,10 +6904,10 @@
         <v>60</v>
       </c>
       <c r="E45" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F45" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G45" s="3"/>
       <c r="H45" s="6">
@@ -6817,7 +6917,7 @@
     <row r="46" spans="2:8" ht="90" x14ac:dyDescent="0.45">
       <c r="B46" s="18"/>
       <c r="C46" s="17" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>67</v>
@@ -6829,7 +6929,7 @@
         <v>72</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H46" s="6">
         <v>2</v>
@@ -6957,7 +7057,7 @@
     <row r="54" spans="2:8" ht="90" x14ac:dyDescent="0.45">
       <c r="B54" s="18"/>
       <c r="C54" s="17" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>67</v>
@@ -6969,7 +7069,7 @@
         <v>72</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H54" s="6">
         <v>1</v>
@@ -7096,7 +7196,7 @@
     </row>
     <row r="62" spans="2:8" ht="72" x14ac:dyDescent="0.45">
       <c r="B62" s="17" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>73</v>
@@ -7111,7 +7211,7 @@
         <v>72</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H62" s="6">
         <v>0</v>
@@ -7120,7 +7220,7 @@
     <row r="63" spans="2:8" ht="90" x14ac:dyDescent="0.45">
       <c r="B63" s="18"/>
       <c r="C63" s="11" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>67</v>
@@ -7132,7 +7232,7 @@
         <v>72</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H63" s="6">
         <v>2</v>
@@ -7272,7 +7372,7 @@
         <v>72</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H71" s="6">
         <v>1</v>
@@ -7400,7 +7500,7 @@
     <row r="79" spans="2:8" ht="90" x14ac:dyDescent="0.45">
       <c r="B79" s="18"/>
       <c r="C79" s="11" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>67</v>
@@ -7412,7 +7512,7 @@
         <v>72</v>
       </c>
       <c r="G79" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H79" s="6">
         <v>2</v>
@@ -7432,7 +7532,7 @@
       </c>
       <c r="G80" s="3"/>
       <c r="H80" s="6">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="81" spans="2:8" x14ac:dyDescent="0.45">
@@ -7466,7 +7566,7 @@
       </c>
       <c r="G82" s="3"/>
       <c r="H82" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="83" spans="2:8" x14ac:dyDescent="0.45">
@@ -7483,7 +7583,7 @@
       </c>
       <c r="G83" s="3"/>
       <c r="H83" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="84" spans="2:8" x14ac:dyDescent="0.45">
@@ -7500,7 +7600,7 @@
       </c>
       <c r="G84" s="3"/>
       <c r="H84" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85" spans="2:8" x14ac:dyDescent="0.45">
@@ -7540,7 +7640,7 @@
     <row r="87" spans="2:8" ht="90" x14ac:dyDescent="0.45">
       <c r="B87" s="18"/>
       <c r="C87" s="11" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>67</v>
@@ -7552,7 +7652,7 @@
         <v>72</v>
       </c>
       <c r="G87" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H87" s="6">
         <v>1</v>
@@ -7677,10 +7777,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="2:8" ht="90" x14ac:dyDescent="0.45">
+    <row r="95" spans="2:8" ht="108" x14ac:dyDescent="0.45">
       <c r="B95" s="18"/>
       <c r="C95" s="11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>67</v>
@@ -7692,7 +7792,7 @@
         <v>72</v>
       </c>
       <c r="G95" s="3" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="H95" s="6">
         <v>1</v>
@@ -7712,7 +7812,7 @@
       </c>
       <c r="G96" s="3"/>
       <c r="H96" s="6">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="97" spans="2:8" x14ac:dyDescent="0.45">
@@ -7746,7 +7846,7 @@
       </c>
       <c r="G98" s="3"/>
       <c r="H98" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="99" spans="2:8" x14ac:dyDescent="0.45">
@@ -7763,7 +7863,7 @@
       </c>
       <c r="G99" s="3"/>
       <c r="H99" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="100" spans="2:8" x14ac:dyDescent="0.45">
@@ -7817,10 +7917,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="2:8" ht="90" x14ac:dyDescent="0.45">
+    <row r="103" spans="2:8" ht="108" x14ac:dyDescent="0.45">
       <c r="B103" s="18"/>
       <c r="C103" s="11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>67</v>
@@ -7832,7 +7932,7 @@
         <v>72</v>
       </c>
       <c r="G103" s="3" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="H103" s="6">
         <v>1</v>
@@ -7852,7 +7952,7 @@
       </c>
       <c r="G104" s="3"/>
       <c r="H104" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="105" spans="2:8" x14ac:dyDescent="0.45">
@@ -7886,7 +7986,7 @@
       </c>
       <c r="G106" s="3"/>
       <c r="H106" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="107" spans="2:8" x14ac:dyDescent="0.45">
@@ -7903,7 +8003,7 @@
       </c>
       <c r="G107" s="3"/>
       <c r="H107" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="108" spans="2:8" x14ac:dyDescent="0.45">
@@ -7959,7 +8059,7 @@
     </row>
     <row r="111" spans="2:8" ht="90" x14ac:dyDescent="0.45">
       <c r="B111" s="17" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>73</v>
@@ -7974,7 +8074,7 @@
         <v>72</v>
       </c>
       <c r="G111" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H111" s="6">
         <v>2</v>
@@ -7983,19 +8083,19 @@
     <row r="112" spans="2:8" ht="90" x14ac:dyDescent="0.45">
       <c r="B112" s="18"/>
       <c r="C112" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>67</v>
       </c>
       <c r="E112" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F112" s="23" t="s">
         <v>72</v>
       </c>
       <c r="G112" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H112" s="6">
         <v>1</v>
@@ -8007,10 +8107,10 @@
         <v>57</v>
       </c>
       <c r="E113" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F113" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G113" s="3"/>
       <c r="H113" s="6">
@@ -8023,10 +8123,10 @@
         <v>58</v>
       </c>
       <c r="E114" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F114" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G114" s="3"/>
       <c r="H114" s="6">
@@ -8039,10 +8139,10 @@
         <v>59</v>
       </c>
       <c r="E115" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F115" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G115" s="3"/>
       <c r="H115" s="6">
@@ -8055,10 +8155,10 @@
         <v>77</v>
       </c>
       <c r="E116" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F116" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G116" s="3"/>
       <c r="H116" s="6">
@@ -8071,10 +8171,10 @@
         <v>80</v>
       </c>
       <c r="E117" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F117" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G117" s="3"/>
       <c r="H117" s="6">
@@ -8088,10 +8188,10 @@
         <v>83</v>
       </c>
       <c r="E118" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F118" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G118" s="3"/>
       <c r="H118" s="6">
@@ -8105,10 +8205,10 @@
         <v>60</v>
       </c>
       <c r="E119" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F119" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G119" s="3"/>
       <c r="H119" s="6">
@@ -8118,19 +8218,19 @@
     <row r="120" spans="2:8" ht="90" x14ac:dyDescent="0.45">
       <c r="B120" s="18"/>
       <c r="C120" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>67</v>
       </c>
       <c r="E120" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F120" s="23" t="s">
         <v>72</v>
       </c>
       <c r="G120" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H120" s="6">
         <v>1</v>
@@ -8143,10 +8243,10 @@
         <v>57</v>
       </c>
       <c r="E121" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F121" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G121" s="3"/>
       <c r="H121" s="6">
@@ -8160,10 +8260,10 @@
         <v>58</v>
       </c>
       <c r="E122" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F122" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G122" s="3"/>
       <c r="H122" s="6">
@@ -8177,10 +8277,10 @@
         <v>59</v>
       </c>
       <c r="E123" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F123" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G123" s="3"/>
       <c r="H123" s="6">
@@ -8194,10 +8294,10 @@
         <v>77</v>
       </c>
       <c r="E124" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F124" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G124" s="3"/>
       <c r="H124" s="6">
@@ -8211,10 +8311,10 @@
         <v>80</v>
       </c>
       <c r="E125" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F125" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G125" s="3"/>
       <c r="H125" s="6">
@@ -8228,10 +8328,10 @@
         <v>83</v>
       </c>
       <c r="E126" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F126" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G126" s="3"/>
       <c r="H126" s="6">
@@ -8245,10 +8345,10 @@
         <v>60</v>
       </c>
       <c r="E127" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F127" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G127" s="3"/>
       <c r="H127" s="6">
@@ -8258,7 +8358,7 @@
     <row r="128" spans="2:8" ht="90" x14ac:dyDescent="0.45">
       <c r="B128" s="18"/>
       <c r="C128" s="20" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D128" s="2" t="s">
         <v>67</v>
@@ -8270,7 +8370,7 @@
         <v>72</v>
       </c>
       <c r="G128" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H128" s="6">
         <v>1</v>
@@ -8398,7 +8498,7 @@
     <row r="136" spans="2:8" ht="90" x14ac:dyDescent="0.45">
       <c r="B136" s="18"/>
       <c r="C136" s="20" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D136" s="2" t="s">
         <v>67</v>
@@ -8410,7 +8510,7 @@
         <v>72</v>
       </c>
       <c r="G136" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H136" s="6">
         <v>1</v>
@@ -8538,19 +8638,19 @@
     <row r="144" spans="2:8" ht="90" x14ac:dyDescent="0.45">
       <c r="B144" s="18"/>
       <c r="C144" s="20" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D144" s="2" t="s">
         <v>67</v>
       </c>
       <c r="E144" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F144" s="23" t="s">
         <v>72</v>
       </c>
       <c r="G144" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H144" s="6">
         <v>1</v>
@@ -8563,10 +8663,10 @@
         <v>57</v>
       </c>
       <c r="E145" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F145" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G145" s="3"/>
       <c r="H145" s="6">
@@ -8580,10 +8680,10 @@
         <v>58</v>
       </c>
       <c r="E146" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F146" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G146" s="3"/>
       <c r="H146" s="6">
@@ -8597,10 +8697,10 @@
         <v>59</v>
       </c>
       <c r="E147" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F147" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G147" s="3"/>
       <c r="H147" s="6">
@@ -8614,10 +8714,10 @@
         <v>77</v>
       </c>
       <c r="E148" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F148" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G148" s="3"/>
       <c r="H148" s="6">
@@ -8631,10 +8731,10 @@
         <v>80</v>
       </c>
       <c r="E149" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F149" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G149" s="3"/>
       <c r="H149" s="6">
@@ -8648,10 +8748,10 @@
         <v>83</v>
       </c>
       <c r="E150" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F150" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G150" s="3"/>
       <c r="H150" s="6">
@@ -8665,10 +8765,10 @@
         <v>60</v>
       </c>
       <c r="E151" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F151" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G151" s="3"/>
       <c r="H151" s="6">
@@ -8678,19 +8778,19 @@
     <row r="152" spans="2:8" ht="90" x14ac:dyDescent="0.45">
       <c r="B152" s="18"/>
       <c r="C152" s="20" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D152" s="2" t="s">
         <v>67</v>
       </c>
       <c r="E152" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F152" s="23" t="s">
         <v>72</v>
       </c>
       <c r="G152" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H152" s="6">
         <v>1</v>
@@ -8702,10 +8802,10 @@
         <v>57</v>
       </c>
       <c r="E153" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F153" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G153" s="3"/>
       <c r="H153" s="6">
@@ -8718,10 +8818,10 @@
         <v>58</v>
       </c>
       <c r="E154" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F154" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G154" s="3"/>
       <c r="H154" s="6">
@@ -8734,10 +8834,10 @@
         <v>59</v>
       </c>
       <c r="E155" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F155" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G155" s="3"/>
       <c r="H155" s="6">
@@ -8750,10 +8850,10 @@
         <v>77</v>
       </c>
       <c r="E156" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F156" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G156" s="3"/>
       <c r="H156" s="6">
@@ -8766,10 +8866,10 @@
         <v>80</v>
       </c>
       <c r="E157" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F157" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G157" s="3"/>
       <c r="H157" s="6">
@@ -8783,10 +8883,10 @@
         <v>83</v>
       </c>
       <c r="E158" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F158" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G158" s="3"/>
       <c r="H158" s="6">
@@ -8799,20 +8899,20 @@
         <v>60</v>
       </c>
       <c r="E159" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F159" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G159" s="3"/>
       <c r="H159" s="6">
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="2:8" ht="90" x14ac:dyDescent="0.45">
+    <row r="160" spans="2:8" ht="108" x14ac:dyDescent="0.45">
       <c r="B160" s="18"/>
       <c r="C160" s="20" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D160" s="2" t="s">
         <v>67</v>
@@ -8824,7 +8924,7 @@
         <v>72</v>
       </c>
       <c r="G160" s="3" t="s">
-        <v>153</v>
+        <v>177</v>
       </c>
       <c r="H160" s="6">
         <v>2</v>
@@ -8844,7 +8944,7 @@
       </c>
       <c r="G161" s="3"/>
       <c r="H161" s="6">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="162" spans="2:8" x14ac:dyDescent="0.45">
@@ -8878,7 +8978,7 @@
       </c>
       <c r="G163" s="3"/>
       <c r="H163" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="164" spans="2:8" x14ac:dyDescent="0.45">
@@ -8895,7 +8995,7 @@
       </c>
       <c r="G164" s="3"/>
       <c r="H164" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="165" spans="2:8" x14ac:dyDescent="0.45">
@@ -8949,10 +9049,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="168" spans="2:8" ht="90" x14ac:dyDescent="0.45">
+    <row r="168" spans="2:8" ht="108" x14ac:dyDescent="0.45">
       <c r="B168" s="18"/>
       <c r="C168" s="20" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D168" s="2" t="s">
         <v>67</v>
@@ -8964,7 +9064,7 @@
         <v>72</v>
       </c>
       <c r="G168" s="3" t="s">
-        <v>154</v>
+        <v>176</v>
       </c>
       <c r="H168" s="6">
         <v>1</v>
@@ -8983,7 +9083,7 @@
       </c>
       <c r="G169" s="3"/>
       <c r="H169" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="170" spans="2:8" x14ac:dyDescent="0.45">
@@ -9015,7 +9115,7 @@
       </c>
       <c r="G171" s="3"/>
       <c r="H171" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="172" spans="2:8" x14ac:dyDescent="0.45">
@@ -9031,7 +9131,7 @@
       </c>
       <c r="G172" s="3"/>
       <c r="H172" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="173" spans="2:8" x14ac:dyDescent="0.45">
@@ -9109,19 +9209,19 @@
     <row r="177" spans="2:8" ht="90" x14ac:dyDescent="0.45">
       <c r="B177" s="12"/>
       <c r="C177" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D177" s="2" t="s">
         <v>67</v>
       </c>
       <c r="E177" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F177" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G177" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H177" s="6">
         <v>0</v>
@@ -9133,10 +9233,10 @@
         <v>57</v>
       </c>
       <c r="E178" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F178" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G178" s="3"/>
       <c r="H178" s="6">
@@ -9149,10 +9249,10 @@
         <v>58</v>
       </c>
       <c r="E179" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F179" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G179" s="3"/>
       <c r="H179" s="6">
@@ -9165,10 +9265,10 @@
         <v>59</v>
       </c>
       <c r="E180" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F180" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G180" s="3"/>
       <c r="H180" s="6">
@@ -9181,10 +9281,10 @@
         <v>77</v>
       </c>
       <c r="E181" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F181" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G181" s="3"/>
       <c r="H181" s="6">
@@ -9197,10 +9297,10 @@
         <v>80</v>
       </c>
       <c r="E182" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F182" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G182" s="3"/>
       <c r="H182" s="6">
@@ -9214,10 +9314,10 @@
         <v>83</v>
       </c>
       <c r="E183" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F183" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G183" s="3"/>
       <c r="H183" s="6">
@@ -9230,10 +9330,10 @@
         <v>60</v>
       </c>
       <c r="E184" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F184" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G184" s="3"/>
       <c r="H184" s="6">
@@ -9243,7 +9343,7 @@
     <row r="185" spans="2:8" ht="90" x14ac:dyDescent="0.45">
       <c r="B185" s="12"/>
       <c r="C185" s="20" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D185" s="2" t="s">
         <v>67</v>
@@ -9255,7 +9355,7 @@
         <v>72</v>
       </c>
       <c r="G185" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H185" s="6">
         <v>2</v>
@@ -9383,7 +9483,7 @@
     <row r="193" spans="2:8" ht="90" x14ac:dyDescent="0.45">
       <c r="B193" s="12"/>
       <c r="C193" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D193" s="2" t="s">
         <v>67</v>
@@ -9395,7 +9495,7 @@
         <v>72</v>
       </c>
       <c r="G193" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H193" s="6">
         <v>1</v>
@@ -9407,10 +9507,10 @@
         <v>57</v>
       </c>
       <c r="E194" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F194" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G194" s="3"/>
       <c r="H194" s="6">
@@ -9423,10 +9523,10 @@
         <v>58</v>
       </c>
       <c r="E195" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F195" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G195" s="3"/>
       <c r="H195" s="6">
@@ -9439,10 +9539,10 @@
         <v>59</v>
       </c>
       <c r="E196" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F196" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G196" s="3"/>
       <c r="H196" s="6">
@@ -9455,10 +9555,10 @@
         <v>77</v>
       </c>
       <c r="E197" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F197" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G197" s="3"/>
       <c r="H197" s="6">
@@ -9471,10 +9571,10 @@
         <v>80</v>
       </c>
       <c r="E198" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F198" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G198" s="3"/>
       <c r="H198" s="6">
@@ -9488,10 +9588,10 @@
         <v>83</v>
       </c>
       <c r="E199" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F199" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G199" s="3"/>
       <c r="H199" s="6">
@@ -9505,10 +9605,10 @@
         <v>60</v>
       </c>
       <c r="E200" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F200" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G200" s="3"/>
       <c r="H200" s="6">
@@ -9518,19 +9618,19 @@
     <row r="201" spans="2:8" ht="90" x14ac:dyDescent="0.45">
       <c r="B201" s="18"/>
       <c r="C201" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D201" s="2" t="s">
         <v>67</v>
       </c>
       <c r="E201" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F201" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G201" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H201" s="6">
         <v>0</v>
@@ -9542,10 +9642,10 @@
         <v>57</v>
       </c>
       <c r="E202" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F202" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G202" s="3"/>
       <c r="H202" s="6">
@@ -9558,10 +9658,10 @@
         <v>58</v>
       </c>
       <c r="E203" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F203" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G203" s="3"/>
       <c r="H203" s="6">
@@ -9574,10 +9674,10 @@
         <v>59</v>
       </c>
       <c r="E204" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F204" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G204" s="3"/>
       <c r="H204" s="6">
@@ -9590,10 +9690,10 @@
         <v>77</v>
       </c>
       <c r="E205" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F205" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G205" s="3"/>
       <c r="H205" s="6">
@@ -9606,10 +9706,10 @@
         <v>80</v>
       </c>
       <c r="E206" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F206" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G206" s="3"/>
       <c r="H206" s="6">
@@ -9623,10 +9723,10 @@
         <v>83</v>
       </c>
       <c r="E207" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F207" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G207" s="3"/>
       <c r="H207" s="6">
@@ -9639,10 +9739,10 @@
         <v>60</v>
       </c>
       <c r="E208" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F208" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G208" s="3"/>
       <c r="H208" s="6">
@@ -9675,19 +9775,19 @@
     <row r="210" spans="2:8" ht="90" x14ac:dyDescent="0.45">
       <c r="B210" s="12"/>
       <c r="C210" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D210" s="2" t="s">
         <v>67</v>
       </c>
       <c r="E210" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F210" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G210" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H210" s="6">
         <v>0</v>
@@ -9699,10 +9799,10 @@
         <v>57</v>
       </c>
       <c r="E211" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F211" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G211" s="3"/>
       <c r="H211" s="6">
@@ -9715,10 +9815,10 @@
         <v>58</v>
       </c>
       <c r="E212" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F212" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G212" s="3"/>
       <c r="H212" s="6">
@@ -9731,10 +9831,10 @@
         <v>59</v>
       </c>
       <c r="E213" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F213" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G213" s="3"/>
       <c r="H213" s="6">
@@ -9747,10 +9847,10 @@
         <v>77</v>
       </c>
       <c r="E214" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F214" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G214" s="3"/>
       <c r="H214" s="6">
@@ -9763,10 +9863,10 @@
         <v>80</v>
       </c>
       <c r="E215" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F215" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G215" s="3"/>
       <c r="H215" s="6">
@@ -9780,10 +9880,10 @@
         <v>83</v>
       </c>
       <c r="E216" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F216" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G216" s="3"/>
       <c r="H216" s="6">
@@ -9796,10 +9896,10 @@
         <v>60</v>
       </c>
       <c r="E217" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F217" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G217" s="3"/>
       <c r="H217" s="6">
@@ -9809,7 +9909,7 @@
     <row r="218" spans="2:8" ht="90" x14ac:dyDescent="0.45">
       <c r="B218" s="12"/>
       <c r="C218" s="20" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D218" s="2" t="s">
         <v>67</v>
@@ -9821,7 +9921,7 @@
         <v>72</v>
       </c>
       <c r="G218" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H218" s="6">
         <v>3</v>
@@ -9949,7 +10049,7 @@
     <row r="226" spans="2:8" ht="90" x14ac:dyDescent="0.45">
       <c r="B226" s="12"/>
       <c r="C226" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D226" s="2" t="s">
         <v>67</v>
@@ -9961,7 +10061,7 @@
         <v>72</v>
       </c>
       <c r="G226" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H226" s="6">
         <v>0</v>
@@ -9973,10 +10073,10 @@
         <v>57</v>
       </c>
       <c r="E227" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F227" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G227" s="3"/>
       <c r="H227" s="6">
@@ -9989,10 +10089,10 @@
         <v>58</v>
       </c>
       <c r="E228" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F228" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G228" s="3"/>
       <c r="H228" s="6">
@@ -10005,10 +10105,10 @@
         <v>59</v>
       </c>
       <c r="E229" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F229" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G229" s="3"/>
       <c r="H229" s="6">
@@ -10021,10 +10121,10 @@
         <v>77</v>
       </c>
       <c r="E230" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F230" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G230" s="3"/>
       <c r="H230" s="6">
@@ -10037,10 +10137,10 @@
         <v>80</v>
       </c>
       <c r="E231" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F231" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G231" s="3"/>
       <c r="H231" s="6">
@@ -10054,10 +10154,10 @@
         <v>83</v>
       </c>
       <c r="E232" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F232" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G232" s="3"/>
       <c r="H232" s="6">
@@ -10071,10 +10171,10 @@
         <v>60</v>
       </c>
       <c r="E233" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F233" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G233" s="3"/>
       <c r="H233" s="6">
@@ -10084,19 +10184,19 @@
     <row r="234" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B234" s="18"/>
       <c r="C234" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D234" s="2" t="s">
         <v>67</v>
       </c>
       <c r="E234" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F234" s="23" t="s">
         <v>72</v>
       </c>
       <c r="G234" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H234" s="6">
         <v>0</v>
@@ -10108,10 +10208,10 @@
         <v>57</v>
       </c>
       <c r="E235" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F235" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G235" s="3"/>
       <c r="H235" s="6">
@@ -10124,10 +10224,10 @@
         <v>58</v>
       </c>
       <c r="E236" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F236" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G236" s="3"/>
       <c r="H236" s="6">
@@ -10140,10 +10240,10 @@
         <v>59</v>
       </c>
       <c r="E237" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F237" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G237" s="3"/>
       <c r="H237" s="6">
@@ -10156,10 +10256,10 @@
         <v>77</v>
       </c>
       <c r="E238" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F238" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G238" s="3"/>
       <c r="H238" s="6">
@@ -10172,10 +10272,10 @@
         <v>80</v>
       </c>
       <c r="E239" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F239" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G239" s="3"/>
       <c r="H239" s="6">
@@ -10189,10 +10289,10 @@
         <v>83</v>
       </c>
       <c r="E240" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F240" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G240" s="3"/>
       <c r="H240" s="6">
@@ -10206,10 +10306,10 @@
         <v>60</v>
       </c>
       <c r="E241" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F241" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G241" s="3"/>
       <c r="H241" s="6">
@@ -10219,7 +10319,7 @@
     <row r="242" spans="2:8" ht="90" x14ac:dyDescent="0.45">
       <c r="B242" s="18"/>
       <c r="C242" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D242" s="2" t="s">
         <v>67</v>
@@ -10231,7 +10331,7 @@
         <v>72</v>
       </c>
       <c r="G242" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H242" s="6">
         <v>1</v>
@@ -10243,10 +10343,10 @@
         <v>57</v>
       </c>
       <c r="E243" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F243" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G243" s="3"/>
       <c r="H243" s="6">
@@ -10259,10 +10359,10 @@
         <v>58</v>
       </c>
       <c r="E244" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F244" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G244" s="3"/>
       <c r="H244" s="6">
@@ -10275,10 +10375,10 @@
         <v>59</v>
       </c>
       <c r="E245" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F245" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G245" s="3"/>
       <c r="H245" s="6">
@@ -10291,10 +10391,10 @@
         <v>77</v>
       </c>
       <c r="E246" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F246" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G246" s="3"/>
       <c r="H246" s="6">
@@ -10307,10 +10407,10 @@
         <v>80</v>
       </c>
       <c r="E247" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F247" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G247" s="3"/>
       <c r="H247" s="6">
@@ -10324,10 +10424,10 @@
         <v>83</v>
       </c>
       <c r="E248" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F248" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G248" s="3"/>
       <c r="H248" s="6">
@@ -10341,10 +10441,10 @@
         <v>60</v>
       </c>
       <c r="E249" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F249" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G249" s="3"/>
       <c r="H249" s="6">
@@ -10354,19 +10454,19 @@
     <row r="250" spans="2:8" ht="90" x14ac:dyDescent="0.45">
       <c r="B250" s="18"/>
       <c r="C250" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D250" s="2" t="s">
         <v>67</v>
       </c>
       <c r="E250" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F250" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G250" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H250" s="6">
         <v>0</v>
@@ -10378,10 +10478,10 @@
         <v>57</v>
       </c>
       <c r="E251" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F251" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G251" s="3"/>
       <c r="H251" s="6">
@@ -10394,10 +10494,10 @@
         <v>58</v>
       </c>
       <c r="E252" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F252" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G252" s="3"/>
       <c r="H252" s="6">
@@ -10410,10 +10510,10 @@
         <v>59</v>
       </c>
       <c r="E253" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F253" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G253" s="3"/>
       <c r="H253" s="6">
@@ -10426,10 +10526,10 @@
         <v>77</v>
       </c>
       <c r="E254" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F254" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G254" s="3"/>
       <c r="H254" s="6">
@@ -10442,10 +10542,10 @@
         <v>80</v>
       </c>
       <c r="E255" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F255" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G255" s="3"/>
       <c r="H255" s="6">
@@ -10459,10 +10559,10 @@
         <v>83</v>
       </c>
       <c r="E256" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F256" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G256" s="3"/>
       <c r="H256" s="6">
@@ -10475,10 +10575,10 @@
         <v>60</v>
       </c>
       <c r="E257" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F257" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G257" s="3"/>
       <c r="H257" s="6">
@@ -10502,7 +10602,7 @@
         <v>72</v>
       </c>
       <c r="G258" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H258" s="6">
         <v>0</v>
@@ -10511,7 +10611,7 @@
     <row r="259" spans="2:8" ht="108" x14ac:dyDescent="0.45">
       <c r="B259" s="12"/>
       <c r="C259" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D259" s="2" t="s">
         <v>67</v>
@@ -10523,7 +10623,7 @@
         <v>72</v>
       </c>
       <c r="G259" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H259" s="6">
         <v>2</v>
@@ -10644,7 +10744,7 @@
     <row r="267" spans="2:8" ht="90" x14ac:dyDescent="0.45">
       <c r="B267" s="12"/>
       <c r="C267" s="20" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D267" s="2" t="s">
         <v>67</v>
@@ -10656,7 +10756,7 @@
         <v>72</v>
       </c>
       <c r="G267" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H267" s="6">
         <v>2</v>
@@ -10784,7 +10884,7 @@
     <row r="275" spans="2:8" ht="90" x14ac:dyDescent="0.45">
       <c r="B275" s="18"/>
       <c r="C275" s="20" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D275" s="2" t="s">
         <v>67</v>
@@ -10796,7 +10896,7 @@
         <v>72</v>
       </c>
       <c r="G275" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H275" s="6">
         <v>1</v>
@@ -10809,10 +10909,10 @@
         <v>57</v>
       </c>
       <c r="E276" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F276" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G276" s="3"/>
       <c r="H276" s="6">
@@ -10826,10 +10926,10 @@
         <v>58</v>
       </c>
       <c r="E277" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F277" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G277" s="3"/>
       <c r="H277" s="6">
@@ -10843,10 +10943,10 @@
         <v>59</v>
       </c>
       <c r="E278" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F278" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G278" s="3"/>
       <c r="H278" s="6">
@@ -10860,10 +10960,10 @@
         <v>77</v>
       </c>
       <c r="E279" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F279" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G279" s="3"/>
       <c r="H279" s="6">
@@ -10877,10 +10977,10 @@
         <v>80</v>
       </c>
       <c r="E280" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F280" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G280" s="3"/>
       <c r="H280" s="6">
@@ -10894,10 +10994,10 @@
         <v>83</v>
       </c>
       <c r="E281" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F281" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G281" s="3"/>
       <c r="H281" s="6">
@@ -10911,10 +11011,10 @@
         <v>60</v>
       </c>
       <c r="E282" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F282" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G282" s="3"/>
       <c r="H282" s="6">
@@ -10924,19 +11024,19 @@
     <row r="283" spans="2:8" ht="90" x14ac:dyDescent="0.45">
       <c r="B283" s="18"/>
       <c r="C283" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D283" s="2" t="s">
         <v>67</v>
       </c>
       <c r="E283" s="28" t="s">
-        <v>125</v>
-      </c>
-      <c r="F283" s="39" t="s">
+        <v>124</v>
+      </c>
+      <c r="F283" s="30" t="s">
         <v>72</v>
       </c>
       <c r="G283" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H283" s="6">
         <v>1</v>
@@ -10948,10 +11048,10 @@
         <v>57</v>
       </c>
       <c r="E284" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F284" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H284" s="6">
         <v>0</v>
@@ -10963,10 +11063,10 @@
         <v>58</v>
       </c>
       <c r="E285" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F285" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G285" s="3"/>
       <c r="H285" s="6">
@@ -10979,10 +11079,10 @@
         <v>59</v>
       </c>
       <c r="E286" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F286" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G286" s="3"/>
       <c r="H286" s="6">
@@ -10995,10 +11095,10 @@
         <v>77</v>
       </c>
       <c r="E287" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F287" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G287" s="3"/>
       <c r="H287" s="6">
@@ -11011,10 +11111,10 @@
         <v>80</v>
       </c>
       <c r="E288" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F288" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G288" s="3"/>
       <c r="H288" s="6">
@@ -11028,10 +11128,10 @@
         <v>83</v>
       </c>
       <c r="E289" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F289" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G289" s="3"/>
       <c r="H289" s="6">
@@ -11045,10 +11145,10 @@
         <v>60</v>
       </c>
       <c r="E290" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F290" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G290" s="3"/>
       <c r="H290" s="6">
@@ -11058,19 +11158,19 @@
     <row r="291" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B291" s="18"/>
       <c r="C291" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D291" s="2" t="s">
         <v>67</v>
       </c>
       <c r="E291" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F291" s="23" t="s">
         <v>72</v>
       </c>
       <c r="G291" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H291" s="6">
         <v>0</v>
@@ -11082,10 +11182,10 @@
         <v>57</v>
       </c>
       <c r="E292" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F292" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H292" s="6">
         <v>0</v>
@@ -11097,10 +11197,10 @@
         <v>58</v>
       </c>
       <c r="E293" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F293" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G293" s="3"/>
       <c r="H293" s="6">
@@ -11113,10 +11213,10 @@
         <v>59</v>
       </c>
       <c r="E294" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F294" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G294" s="3"/>
       <c r="H294" s="6">
@@ -11129,10 +11229,10 @@
         <v>77</v>
       </c>
       <c r="E295" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F295" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G295" s="3"/>
       <c r="H295" s="6">
@@ -11145,10 +11245,10 @@
         <v>80</v>
       </c>
       <c r="E296" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F296" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G296" s="3"/>
       <c r="H296" s="6">
@@ -11162,10 +11262,10 @@
         <v>83</v>
       </c>
       <c r="E297" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F297" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G297" s="3"/>
       <c r="H297" s="6">
@@ -11178,10 +11278,10 @@
         <v>60</v>
       </c>
       <c r="E298" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F298" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G298" s="3"/>
       <c r="H298" s="6">
@@ -11214,19 +11314,19 @@
     <row r="300" spans="2:8" ht="90" x14ac:dyDescent="0.45">
       <c r="B300" s="12"/>
       <c r="C300" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D300" s="2" t="s">
         <v>67</v>
       </c>
       <c r="E300" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F300" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G300" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H300" s="6">
         <v>0</v>
@@ -11238,10 +11338,10 @@
         <v>57</v>
       </c>
       <c r="E301" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F301" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G301" s="3"/>
       <c r="H301" s="6">
@@ -11254,10 +11354,10 @@
         <v>58</v>
       </c>
       <c r="E302" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F302" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G302" s="3"/>
       <c r="H302" s="6">
@@ -11270,10 +11370,10 @@
         <v>59</v>
       </c>
       <c r="E303" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F303" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G303" s="3"/>
       <c r="H303" s="6">
@@ -11286,10 +11386,10 @@
         <v>77</v>
       </c>
       <c r="E304" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F304" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G304" s="3"/>
       <c r="H304" s="6">
@@ -11302,10 +11402,10 @@
         <v>80</v>
       </c>
       <c r="E305" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F305" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G305" s="3"/>
       <c r="H305" s="6">
@@ -11319,10 +11419,10 @@
         <v>83</v>
       </c>
       <c r="E306" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F306" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G306" s="3"/>
       <c r="H306" s="6">
@@ -11335,10 +11435,10 @@
         <v>60</v>
       </c>
       <c r="E307" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F307" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G307" s="3"/>
       <c r="H307" s="6">
@@ -11348,7 +11448,7 @@
     <row r="308" spans="2:8" ht="108" x14ac:dyDescent="0.45">
       <c r="B308" s="12"/>
       <c r="C308" s="20" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D308" s="2" t="s">
         <v>67</v>
@@ -11360,7 +11460,7 @@
         <v>72</v>
       </c>
       <c r="G308" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H308" s="6">
         <v>3</v>
@@ -11488,7 +11588,7 @@
     <row r="316" spans="2:8" ht="90" x14ac:dyDescent="0.45">
       <c r="B316" s="12"/>
       <c r="C316" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D316" s="2" t="s">
         <v>67</v>
@@ -11500,7 +11600,7 @@
         <v>72</v>
       </c>
       <c r="G316" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H316" s="6">
         <v>1</v>
@@ -11512,10 +11612,10 @@
         <v>57</v>
       </c>
       <c r="E317" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F317" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G317" s="3"/>
       <c r="H317" s="6">
@@ -11528,10 +11628,10 @@
         <v>58</v>
       </c>
       <c r="E318" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F318" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G318" s="3"/>
       <c r="H318" s="6">
@@ -11544,10 +11644,10 @@
         <v>59</v>
       </c>
       <c r="E319" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F319" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G319" s="3"/>
       <c r="H319" s="6">
@@ -11560,10 +11660,10 @@
         <v>77</v>
       </c>
       <c r="E320" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F320" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G320" s="3"/>
       <c r="H320" s="6">
@@ -11576,10 +11676,10 @@
         <v>80</v>
       </c>
       <c r="E321" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F321" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G321" s="3"/>
       <c r="H321" s="6">
@@ -11593,10 +11693,10 @@
         <v>83</v>
       </c>
       <c r="E322" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F322" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G322" s="3"/>
       <c r="H322" s="6">
@@ -11610,10 +11710,10 @@
         <v>60</v>
       </c>
       <c r="E323" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F323" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G323" s="3"/>
       <c r="H323" s="6">
@@ -11623,19 +11723,19 @@
     <row r="324" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B324" s="12"/>
       <c r="C324" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D324" s="2" t="s">
         <v>67</v>
       </c>
       <c r="E324" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F324" s="23" t="s">
         <v>72</v>
       </c>
       <c r="G324" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H324" s="6">
         <v>0</v>
@@ -11647,10 +11747,10 @@
         <v>57</v>
       </c>
       <c r="E325" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F325" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G325" s="3"/>
       <c r="H325" s="6">
@@ -11663,10 +11763,10 @@
         <v>58</v>
       </c>
       <c r="E326" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F326" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G326" s="3"/>
       <c r="H326" s="6">
@@ -11679,10 +11779,10 @@
         <v>59</v>
       </c>
       <c r="E327" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F327" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G327" s="3"/>
       <c r="H327" s="6">
@@ -11695,10 +11795,10 @@
         <v>77</v>
       </c>
       <c r="E328" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F328" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G328" s="3"/>
       <c r="H328" s="6">
@@ -11711,10 +11811,10 @@
         <v>80</v>
       </c>
       <c r="E329" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F329" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G329" s="3"/>
       <c r="H329" s="6">
@@ -11728,10 +11828,10 @@
         <v>83</v>
       </c>
       <c r="E330" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F330" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G330" s="3"/>
       <c r="H330" s="6">
@@ -11745,10 +11845,10 @@
         <v>60</v>
       </c>
       <c r="E331" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F331" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G331" s="3"/>
       <c r="H331" s="6">
@@ -11758,7 +11858,7 @@
     <row r="332" spans="2:8" ht="90" x14ac:dyDescent="0.45">
       <c r="B332" s="12"/>
       <c r="C332" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D332" s="2" t="s">
         <v>67</v>
@@ -11770,7 +11870,7 @@
         <v>72</v>
       </c>
       <c r="G332" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H332" s="6">
         <v>1</v>
@@ -11782,10 +11882,10 @@
         <v>57</v>
       </c>
       <c r="E333" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F333" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G333" s="3"/>
       <c r="H333" s="6">
@@ -11798,10 +11898,10 @@
         <v>58</v>
       </c>
       <c r="E334" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F334" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G334" s="3"/>
       <c r="H334" s="6">
@@ -11814,10 +11914,10 @@
         <v>59</v>
       </c>
       <c r="E335" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F335" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G335" s="3"/>
       <c r="H335" s="6">
@@ -11830,10 +11930,10 @@
         <v>77</v>
       </c>
       <c r="E336" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F336" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G336" s="3"/>
       <c r="H336" s="6">
@@ -11846,10 +11946,10 @@
         <v>80</v>
       </c>
       <c r="E337" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F337" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G337" s="3"/>
       <c r="H337" s="6">
@@ -11863,10 +11963,10 @@
         <v>83</v>
       </c>
       <c r="E338" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F338" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G338" s="3"/>
       <c r="H338" s="6">
@@ -11879,10 +11979,10 @@
         <v>60</v>
       </c>
       <c r="E339" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F339" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G339" s="3"/>
       <c r="H339" s="6">
@@ -11892,7 +11992,7 @@
     <row r="340" spans="2:8" ht="126" x14ac:dyDescent="0.45">
       <c r="B340" s="12"/>
       <c r="C340" s="20" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D340" s="2" t="s">
         <v>67</v>
@@ -11904,10 +12004,10 @@
         <v>72</v>
       </c>
       <c r="G340" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H340" s="6">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="341" spans="2:8" x14ac:dyDescent="0.45">
@@ -11917,10 +12017,10 @@
         <v>57</v>
       </c>
       <c r="E341" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F341" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G341" s="3"/>
       <c r="H341" s="6">
@@ -11934,10 +12034,10 @@
         <v>58</v>
       </c>
       <c r="E342" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F342" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G342" s="3"/>
       <c r="H342" s="6">
@@ -11951,10 +12051,10 @@
         <v>59</v>
       </c>
       <c r="E343" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F343" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G343" s="3"/>
       <c r="H343" s="6">
@@ -11968,10 +12068,10 @@
         <v>77</v>
       </c>
       <c r="E344" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F344" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G344" s="3"/>
       <c r="H344" s="6">
@@ -11985,10 +12085,10 @@
         <v>80</v>
       </c>
       <c r="E345" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F345" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G345" s="3"/>
       <c r="H345" s="6">
@@ -12002,10 +12102,10 @@
         <v>83</v>
       </c>
       <c r="E346" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F346" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G346" s="3"/>
       <c r="H346" s="6">
@@ -12019,10 +12119,10 @@
         <v>60</v>
       </c>
       <c r="E347" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F347" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G347" s="3"/>
       <c r="H347" s="6">
@@ -12055,19 +12155,19 @@
     <row r="349" spans="2:8" ht="90" x14ac:dyDescent="0.45">
       <c r="B349" s="18"/>
       <c r="C349" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D349" s="2" t="s">
         <v>67</v>
       </c>
       <c r="E349" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F349" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G349" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H349" s="6">
         <v>0</v>
@@ -12079,10 +12179,10 @@
         <v>57</v>
       </c>
       <c r="E350" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F350" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G350" s="3"/>
       <c r="H350" s="6">
@@ -12095,10 +12195,10 @@
         <v>58</v>
       </c>
       <c r="E351" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F351" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G351" s="3"/>
       <c r="H351" s="6">
@@ -12111,10 +12211,10 @@
         <v>59</v>
       </c>
       <c r="E352" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F352" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G352" s="3"/>
       <c r="H352" s="6">
@@ -12127,10 +12227,10 @@
         <v>77</v>
       </c>
       <c r="E353" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F353" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G353" s="3"/>
       <c r="H353" s="6">
@@ -12143,10 +12243,10 @@
         <v>80</v>
       </c>
       <c r="E354" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F354" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G354" s="3"/>
       <c r="H354" s="6">
@@ -12160,10 +12260,10 @@
         <v>83</v>
       </c>
       <c r="E355" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F355" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G355" s="3"/>
       <c r="H355" s="6">
@@ -12176,10 +12276,10 @@
         <v>60</v>
       </c>
       <c r="E356" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F356" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G356" s="3"/>
       <c r="H356" s="6">
@@ -12189,7 +12289,7 @@
     <row r="357" spans="2:8" ht="108" x14ac:dyDescent="0.45">
       <c r="B357" s="18"/>
       <c r="C357" s="20" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D357" s="2" t="s">
         <v>67</v>
@@ -12201,7 +12301,7 @@
         <v>72</v>
       </c>
       <c r="G357" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H357" s="6">
         <v>3</v>
@@ -12329,7 +12429,7 @@
     <row r="365" spans="2:8" ht="90" x14ac:dyDescent="0.45">
       <c r="B365" s="18"/>
       <c r="C365" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D365" s="2" t="s">
         <v>67</v>
@@ -12341,7 +12441,7 @@
         <v>72</v>
       </c>
       <c r="G365" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H365" s="6">
         <v>1</v>
@@ -12353,10 +12453,10 @@
         <v>57</v>
       </c>
       <c r="E366" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F366" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G366" s="3"/>
       <c r="H366" s="6">
@@ -12369,10 +12469,10 @@
         <v>58</v>
       </c>
       <c r="E367" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F367" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G367" s="3"/>
       <c r="H367" s="6">
@@ -12385,10 +12485,10 @@
         <v>59</v>
       </c>
       <c r="E368" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F368" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G368" s="3"/>
       <c r="H368" s="6">
@@ -12401,10 +12501,10 @@
         <v>77</v>
       </c>
       <c r="E369" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F369" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G369" s="3"/>
       <c r="H369" s="6">
@@ -12417,10 +12517,10 @@
         <v>80</v>
       </c>
       <c r="E370" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F370" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G370" s="3"/>
       <c r="H370" s="6">
@@ -12434,10 +12534,10 @@
         <v>83</v>
       </c>
       <c r="E371" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F371" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G371" s="3"/>
       <c r="H371" s="6">
@@ -12451,10 +12551,10 @@
         <v>60</v>
       </c>
       <c r="E372" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F372" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G372" s="3"/>
       <c r="H372" s="6">
@@ -12464,19 +12564,19 @@
     <row r="373" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B373" s="18"/>
       <c r="C373" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D373" s="2" t="s">
         <v>67</v>
       </c>
       <c r="E373" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F373" s="23" t="s">
         <v>72</v>
       </c>
       <c r="G373" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H373" s="6">
         <v>1</v>
@@ -12488,10 +12588,10 @@
         <v>57</v>
       </c>
       <c r="E374" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F374" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G374" s="3"/>
       <c r="H374" s="6">
@@ -12504,10 +12604,10 @@
         <v>58</v>
       </c>
       <c r="E375" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F375" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G375" s="3"/>
       <c r="H375" s="6">
@@ -12520,10 +12620,10 @@
         <v>59</v>
       </c>
       <c r="E376" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F376" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G376" s="3"/>
       <c r="H376" s="6">
@@ -12536,10 +12636,10 @@
         <v>77</v>
       </c>
       <c r="E377" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F377" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G377" s="3"/>
       <c r="H377" s="6">
@@ -12552,10 +12652,10 @@
         <v>80</v>
       </c>
       <c r="E378" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F378" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G378" s="3"/>
       <c r="H378" s="6">
@@ -12569,10 +12669,10 @@
         <v>83</v>
       </c>
       <c r="E379" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F379" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G379" s="3"/>
       <c r="H379" s="6">
@@ -12586,10 +12686,10 @@
         <v>60</v>
       </c>
       <c r="E380" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F380" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G380" s="3"/>
       <c r="H380" s="6">
@@ -12599,7 +12699,7 @@
     <row r="381" spans="2:8" ht="90" x14ac:dyDescent="0.45">
       <c r="B381" s="18"/>
       <c r="C381" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D381" s="2" t="s">
         <v>67</v>
@@ -12611,7 +12711,7 @@
         <v>72</v>
       </c>
       <c r="G381" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H381" s="6">
         <v>1</v>
@@ -12623,10 +12723,10 @@
         <v>57</v>
       </c>
       <c r="E382" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F382" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G382" s="3"/>
       <c r="H382" s="6">
@@ -12639,10 +12739,10 @@
         <v>58</v>
       </c>
       <c r="E383" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F383" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G383" s="3"/>
       <c r="H383" s="6">
@@ -12655,10 +12755,10 @@
         <v>59</v>
       </c>
       <c r="E384" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F384" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G384" s="3"/>
       <c r="H384" s="6">
@@ -12671,10 +12771,10 @@
         <v>77</v>
       </c>
       <c r="E385" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F385" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G385" s="3"/>
       <c r="H385" s="6">
@@ -12687,10 +12787,10 @@
         <v>80</v>
       </c>
       <c r="E386" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F386" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G386" s="3"/>
       <c r="H386" s="6">
@@ -12704,10 +12804,10 @@
         <v>83</v>
       </c>
       <c r="E387" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F387" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G387" s="3"/>
       <c r="H387" s="6">
@@ -12720,10 +12820,10 @@
         <v>60</v>
       </c>
       <c r="E388" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F388" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G388" s="3"/>
       <c r="H388" s="6">
@@ -12733,7 +12833,7 @@
     <row r="389" spans="2:8" ht="126" x14ac:dyDescent="0.45">
       <c r="B389" s="18"/>
       <c r="C389" s="20" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D389" s="2" t="s">
         <v>67</v>
@@ -12745,10 +12845,10 @@
         <v>72</v>
       </c>
       <c r="G389" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H389" s="6">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="390" spans="2:8" x14ac:dyDescent="0.45">
@@ -12758,10 +12858,10 @@
         <v>57</v>
       </c>
       <c r="E390" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F390" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G390" s="3"/>
       <c r="H390" s="6">
@@ -12775,10 +12875,10 @@
         <v>58</v>
       </c>
       <c r="E391" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F391" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G391" s="3"/>
       <c r="H391" s="6">
@@ -12792,10 +12892,10 @@
         <v>59</v>
       </c>
       <c r="E392" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F392" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G392" s="3"/>
       <c r="H392" s="6">
@@ -12809,10 +12909,10 @@
         <v>77</v>
       </c>
       <c r="E393" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F393" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G393" s="3"/>
       <c r="H393" s="6">
@@ -12826,10 +12926,10 @@
         <v>80</v>
       </c>
       <c r="E394" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F394" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G394" s="3"/>
       <c r="H394" s="6">
@@ -12843,10 +12943,10 @@
         <v>83</v>
       </c>
       <c r="E395" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F395" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G395" s="3"/>
       <c r="H395" s="6">
@@ -12860,10 +12960,10 @@
         <v>60</v>
       </c>
       <c r="E396" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F396" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G396" s="3"/>
       <c r="H396" s="6">
@@ -12873,13 +12973,13 @@
     <row r="397" spans="2:8" x14ac:dyDescent="0.45">
       <c r="H397" s="7">
         <f>SUM(H3:H396)</f>
-        <v>341</v>
+        <v>355</v>
       </c>
     </row>
     <row r="398" spans="2:8" x14ac:dyDescent="0.45">
       <c r="H398" s="29">
         <f>ROUNDUP(H397*1.3,0)</f>
-        <v>444</v>
+        <v>462</v>
       </c>
     </row>
   </sheetData>
@@ -12927,10 +13027,10 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B2" s="33" t="s">
+      <c r="B2" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="33"/>
+      <c r="C2" s="41"/>
       <c r="D2" s="5" t="s">
         <v>0</v>
       </c>
@@ -12953,7 +13053,7 @@
       </c>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B4" s="30" t="s">
+      <c r="B4" s="35" t="s">
         <v>30</v>
       </c>
       <c r="C4" s="2" t="s">
@@ -12967,7 +13067,7 @@
       </c>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B5" s="31"/>
+      <c r="B5" s="36"/>
       <c r="C5" s="2" t="s">
         <v>29</v>
       </c>
@@ -12979,7 +13079,7 @@
       </c>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B6" s="32"/>
+      <c r="B6" s="37"/>
       <c r="C6" s="3" t="s">
         <v>21</v>
       </c>
@@ -12991,7 +13091,7 @@
       </c>
     </row>
     <row r="7" spans="2:6" ht="72" x14ac:dyDescent="0.45">
-      <c r="B7" s="34" t="s">
+      <c r="B7" s="33" t="s">
         <v>4</v>
       </c>
       <c r="C7" s="3" t="s">
@@ -13005,7 +13105,7 @@
       </c>
     </row>
     <row r="8" spans="2:6" ht="180" x14ac:dyDescent="0.45">
-      <c r="B8" s="34"/>
+      <c r="B8" s="33"/>
       <c r="C8" s="3" t="s">
         <v>22</v>
       </c>
@@ -13039,16 +13139,16 @@
       </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B10" s="30" t="s">
+      <c r="B10" s="35" t="s">
         <v>15</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="36" t="s">
+      <c r="D10" s="38" t="s">
         <v>42</v>
       </c>
-      <c r="E10" s="30">
+      <c r="E10" s="35">
         <f>240/8</f>
         <v>30</v>
       </c>
@@ -13057,23 +13157,23 @@
       </c>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B11" s="31"/>
+      <c r="B11" s="36"/>
       <c r="C11" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D11" s="37"/>
-      <c r="E11" s="31"/>
+      <c r="D11" s="39"/>
+      <c r="E11" s="36"/>
     </row>
     <row r="12" spans="2:6" ht="44.4" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B12" s="32"/>
+      <c r="B12" s="37"/>
       <c r="C12" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D12" s="38"/>
-      <c r="E12" s="32"/>
+      <c r="D12" s="40"/>
+      <c r="E12" s="37"/>
     </row>
     <row r="13" spans="2:6" ht="72" x14ac:dyDescent="0.45">
-      <c r="B13" s="30" t="s">
+      <c r="B13" s="35" t="s">
         <v>12</v>
       </c>
       <c r="C13" s="2" t="s">
@@ -13087,7 +13187,7 @@
       </c>
     </row>
     <row r="14" spans="2:6" ht="36" x14ac:dyDescent="0.45">
-      <c r="B14" s="32"/>
+      <c r="B14" s="37"/>
       <c r="C14" s="2" t="s">
         <v>11</v>
       </c>
@@ -13099,7 +13199,7 @@
       </c>
     </row>
     <row r="15" spans="2:6" ht="342" x14ac:dyDescent="0.45">
-      <c r="B15" s="30" t="s">
+      <c r="B15" s="35" t="s">
         <v>8</v>
       </c>
       <c r="C15" s="2" t="s">
@@ -13117,7 +13217,7 @@
       </c>
     </row>
     <row r="16" spans="2:6" ht="342" x14ac:dyDescent="0.45">
-      <c r="B16" s="31"/>
+      <c r="B16" s="36"/>
       <c r="C16" s="2" t="s">
         <v>3</v>
       </c>
@@ -13133,7 +13233,7 @@
       </c>
     </row>
     <row r="17" spans="2:6" ht="342" x14ac:dyDescent="0.45">
-      <c r="B17" s="31"/>
+      <c r="B17" s="36"/>
       <c r="C17" s="2" t="s">
         <v>14</v>
       </c>
@@ -13149,7 +13249,7 @@
       </c>
     </row>
     <row r="18" spans="2:6" ht="54" x14ac:dyDescent="0.45">
-      <c r="B18" s="31"/>
+      <c r="B18" s="36"/>
       <c r="C18" s="2" t="s">
         <v>17</v>
       </c>
@@ -13165,7 +13265,7 @@
       </c>
     </row>
     <row r="19" spans="2:6" ht="270" x14ac:dyDescent="0.45">
-      <c r="B19" s="32"/>
+      <c r="B19" s="37"/>
       <c r="C19" s="2" t="s">
         <v>19</v>
       </c>
@@ -13181,13 +13281,13 @@
       </c>
     </row>
     <row r="20" spans="2:6" ht="36" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B20" s="34" t="s">
+      <c r="B20" s="33" t="s">
         <v>20</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D20" s="35" t="s">
+      <c r="D20" s="34" t="s">
         <v>26</v>
       </c>
       <c r="E20" s="2">
@@ -13195,11 +13295,11 @@
       </c>
     </row>
     <row r="21" spans="2:6" ht="36" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B21" s="34"/>
+      <c r="B21" s="33"/>
       <c r="C21" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D21" s="35"/>
+      <c r="D21" s="34"/>
       <c r="E21" s="2">
         <v>5</v>
       </c>
@@ -13228,16 +13328,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="E10:E12"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="B7:B8"/>
     <mergeCell ref="B20:B21"/>
     <mergeCell ref="D20:D21"/>
     <mergeCell ref="B10:B12"/>
     <mergeCell ref="D10:D12"/>
     <mergeCell ref="B15:B19"/>
-    <mergeCell ref="E10:E12"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B4:B6"/>
-    <mergeCell ref="B7:B8"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/見積もり/NTTDU様-案件管理-概算見積もり_最新.xlsx
+++ b/見積もり/NTTDU様-案件管理-概算見積もり_最新.xlsx
@@ -8,18 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\project_management\見積もり\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{031F6DE0-0AF5-449C-8493-CB431E8F45DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6E6B19E-B73D-462F-A3FD-6093CF8483CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{15EF4DE1-B99D-4880-9633-29B1123E0732}"/>
   </bookViews>
   <sheets>
-    <sheet name="新入社員研修" sheetId="8" r:id="rId1"/>
+    <sheet name="新入社員研修" sheetId="9" r:id="rId1"/>
     <sheet name="新入社員研修（詳細）" sheetId="4" r:id="rId2"/>
     <sheet name="案件企画・講師アサイン" sheetId="2" r:id="rId3"/>
     <sheet name="項目表" sheetId="5" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">新入社員研修!$B$2:$D$398</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">新入社員研修!$B$2:$H$22</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1476" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1467" uniqueCount="177">
   <si>
     <t>備考</t>
     <rPh sb="0" eb="2">
@@ -1907,40 +1907,6 @@
   <si>
     <t>以下の流れを検討する。
 # 検討対象
-・ユーザー（年度別）の作成
-# 作成ツール/システム
-　簡易的なもの</t>
-    <rPh sb="0" eb="2">
-      <t>イカ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>ナガ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>ケントウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>以下の流れを検討する。
-# 検討対象
-・ユーザー（年度別）の確認
-# 作成ツール/システム
-　簡易的なもの</t>
-    <rPh sb="0" eb="2">
-      <t>イカ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>ナガ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>ケントウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>以下の流れを検討する。
-# 検討対象
 ・集計方法の簡易化
 # 作成ツール/システム
 　簡易的なもの（ツール改善）</t>
@@ -2188,40 +2154,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>以下の流れを検討する。
-# 検討対象
-・ユーザー（年度別）の作成
-# 作成ツール/システム
-　なし（※ギブリー様と相談）/ 簡易的なもの</t>
-    <rPh sb="0" eb="2">
-      <t>イカ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>ナガ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>ケントウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>以下の流れを検討する。
-# 検討対象
-・ユーザー（年度別）の確認
-# 作成ツール/システム
-　なし（※ギブリー様と相談）/ 簡易的なもの</t>
-    <rPh sb="0" eb="2">
-      <t>イカ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>ナガ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>ケントウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>以下の流れを確認し、改善する。
 マテリアルの管理～マテリアルの作成～マテリアルの確認～マテリアルのデプロイ～マテリアルのデプロイ後の確認</t>
     <rPh sb="0" eb="2">
@@ -2525,6 +2457,29 @@
     </rPh>
     <rPh sb="88" eb="92">
       <t>シュウリョウハンテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>要件定義以外</t>
+    <rPh sb="0" eb="4">
+      <t>ヨウケンテイギ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>イガイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>要件定義を抜いたもの</t>
+    <rPh sb="0" eb="2">
+      <t>ヨウケン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>テイギ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ヌ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2709,7 +2664,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2791,9 +2746,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -2802,18 +2754,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -2824,6 +2764,15 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -2833,8 +2782,11 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3149,2962 +3101,396 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43519A57-0157-4E94-A8ED-B58B74152C39}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="B2:D400"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65F66F02-6446-4992-B24D-AB250ADF6165}">
+  <dimension ref="B2:I22"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.796875" style="1"/>
     <col min="2" max="2" width="19" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="78.296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.3984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.8984375" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="8.796875" style="1"/>
+    <col min="3" max="4" width="6.796875" style="16" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="78.296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.296875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12.3984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.59765625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="15.69921875" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B2" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="C2" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="24" t="s">
+      <c r="C2" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="G2" s="24" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="2:4" ht="54" x14ac:dyDescent="0.45">
-      <c r="B3" s="32" t="s">
+    <row r="3" spans="2:7" ht="54" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B3" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="39" t="s">
+        <v>72</v>
+      </c>
+      <c r="D3" s="39" t="s">
+        <v>72</v>
+      </c>
+      <c r="E3" s="39" t="s">
+        <v>161</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="G3" s="6">
+        <f>SUMIF('新入社員研修（詳細）'!D3:D36,"要件定義",'新入社員研修（詳細）'!H3:H36)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B4" s="9"/>
+      <c r="C4" s="40"/>
+      <c r="D4" s="40"/>
+      <c r="E4" s="40"/>
+      <c r="F4" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="G4" s="6">
+        <f>SUMIF('新入社員研修（詳細）'!D3:D36,"&lt;&gt;要件定義",'新入社員研修（詳細）'!H3:H36)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" ht="36" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B5" s="30" t="s">
+        <v>122</v>
+      </c>
+      <c r="C5" s="39" t="s">
+        <v>72</v>
+      </c>
+      <c r="D5" s="39" t="s">
+        <v>72</v>
+      </c>
+      <c r="E5" s="39" t="s">
+        <v>162</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="G5" s="6">
+        <f>SUMIF('新入社員研修（詳細）'!D37:D61,"要件定義",'新入社員研修（詳細）'!H37:H61)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B6" s="32"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="G6" s="6">
+        <f>SUMIF('新入社員研修（詳細）'!D37:D61,"&lt;&gt;要件定義",'新入社員研修（詳細）'!H37:H61)</f>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" ht="72" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B7" s="30" t="s">
+        <v>100</v>
+      </c>
+      <c r="C7" s="39" t="s">
+        <v>72</v>
+      </c>
+      <c r="D7" s="39" t="s">
+        <v>72</v>
+      </c>
+      <c r="E7" s="39" t="s">
+        <v>163</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="G7" s="6">
+        <f>SUMIF('新入社員研修（詳細）'!D62:D110,"要件定義",'新入社員研修（詳細）'!H62:H110)</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B8" s="32"/>
+      <c r="C8" s="40"/>
+      <c r="D8" s="40"/>
+      <c r="E8" s="40"/>
+      <c r="F8" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="G8" s="6">
+        <f>SUMIF('新入社員研修（詳細）'!D62:D110,"&lt;&gt;要件定義",'新入社員研修（詳細）'!H62:H110)</f>
+        <v>76</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" ht="90" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B9" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="C9" s="39" t="s">
+        <v>72</v>
+      </c>
+      <c r="D9" s="39" t="s">
+        <v>72</v>
+      </c>
+      <c r="E9" s="39" t="s">
+        <v>164</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="G9" s="6">
+        <f>SUMIF('新入社員研修（詳細）'!D111:D175,"要件定義",'新入社員研修（詳細）'!H111:H175)</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B10" s="32"/>
+      <c r="C10" s="40"/>
+      <c r="D10" s="40"/>
+      <c r="E10" s="40"/>
+      <c r="F10" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="G10" s="6">
+        <f>SUMIF('新入社員研修（詳細）'!D111:D175,"&lt;&gt;要件定義",'新入社員研修（詳細）'!H111:H175)</f>
+        <v>65</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" ht="36" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B11" s="30" t="s">
+        <v>52</v>
+      </c>
+      <c r="C11" s="39" t="s">
+        <v>72</v>
+      </c>
+      <c r="D11" s="39" t="s">
+        <v>72</v>
+      </c>
+      <c r="E11" s="39" t="s">
         <v>165</v>
       </c>
-      <c r="D3" s="6">
-        <f>SUM('新入社員研修（詳細）'!H3:H36)</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B4" s="18"/>
-      <c r="C4" s="27" t="s">
-        <v>129</v>
-      </c>
-      <c r="D4" s="31">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B5" s="18"/>
-      <c r="C5" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="D5" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B6" s="18"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B7" s="18"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B8" s="18"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B9" s="18"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B10" s="18"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B11" s="18"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B12" s="18"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B13" s="18"/>
-      <c r="C13" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="D13" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B14" s="18"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B15" s="18"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B16" s="18"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B17" s="18"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B18" s="18"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B19" s="18"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B20" s="18"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B21" s="18"/>
-      <c r="C21" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="D21" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B22" s="18"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B23" s="18"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B24" s="18"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B25" s="18"/>
-      <c r="C25" s="3"/>
-      <c r="D25" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B26" s="18"/>
-      <c r="C26" s="3"/>
-      <c r="D26" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B27" s="18"/>
-      <c r="C27" s="3"/>
-      <c r="D27" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B28" s="18"/>
-      <c r="C28" s="3"/>
-      <c r="D28" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B29" s="18"/>
-      <c r="C29" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="D29" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B30" s="18"/>
-      <c r="C30" s="3"/>
-      <c r="D30" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B31" s="18"/>
-      <c r="C31" s="3"/>
-      <c r="D31" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B32" s="18"/>
-      <c r="C32" s="3"/>
-      <c r="D32" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B33" s="18"/>
-      <c r="C33" s="3"/>
-      <c r="D33" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B34" s="18"/>
-      <c r="C34" s="3"/>
-      <c r="D34" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B35" s="18"/>
-      <c r="C35" s="3"/>
-      <c r="D35" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B36" s="18"/>
-      <c r="C36" s="3"/>
-      <c r="D36" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="2:4" ht="36" x14ac:dyDescent="0.45">
-      <c r="B37" s="32" t="s">
-        <v>122</v>
-      </c>
-      <c r="C37" s="3" t="s">
+      <c r="F11" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="G11" s="6">
+        <f>SUMIF('新入社員研修（詳細）'!D176:D208,"要件定義",'新入社員研修（詳細）'!H176:H208)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B12" s="32"/>
+      <c r="C12" s="40"/>
+      <c r="D12" s="40"/>
+      <c r="E12" s="40"/>
+      <c r="F12" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="G12" s="6">
+        <f>SUMIF('新入社員研修（詳細）'!D176:D208,"&lt;&gt;要件定義",'新入社員研修（詳細）'!H176:H208)</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" ht="36" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B13" s="30" t="s">
+        <v>53</v>
+      </c>
+      <c r="C13" s="39" t="s">
+        <v>72</v>
+      </c>
+      <c r="D13" s="39" t="s">
+        <v>72</v>
+      </c>
+      <c r="E13" s="39" t="s">
         <v>166</v>
       </c>
-      <c r="D37" s="6">
-        <f>SUM('新入社員研修（詳細）'!H37:H61)</f>
-        <v>37</v>
-      </c>
-    </row>
-    <row r="38" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B38" s="18"/>
-      <c r="C38" s="27" t="s">
-        <v>131</v>
-      </c>
-      <c r="D38" s="31">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B39" s="18"/>
-      <c r="C39" s="3"/>
-      <c r="D39" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B40" s="18"/>
-      <c r="C40" s="3"/>
-      <c r="D40" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B41" s="18"/>
-      <c r="C41" s="3"/>
-      <c r="D41" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B42" s="18"/>
-      <c r="C42" s="3"/>
-      <c r="D42" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B43" s="18"/>
-      <c r="C43" s="3"/>
-      <c r="D43" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B44" s="18"/>
-      <c r="C44" s="3"/>
-      <c r="D44" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B45" s="18"/>
-      <c r="C45" s="3"/>
-      <c r="D45" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B46" s="18"/>
-      <c r="C46" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="D46" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="47" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B47" s="18"/>
-      <c r="C47" s="3"/>
-      <c r="D47" s="6">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="48" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B48" s="18"/>
-      <c r="C48" s="3"/>
-      <c r="D48" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B49" s="18"/>
-      <c r="C49" s="3"/>
-      <c r="D49" s="6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="50" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B50" s="18"/>
-      <c r="C50" s="3"/>
-      <c r="D50" s="6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="51" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B51" s="18"/>
-      <c r="C51" s="3"/>
-      <c r="D51" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B52" s="18"/>
-      <c r="C52" s="3"/>
-      <c r="D52" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B53" s="18"/>
-      <c r="C53" s="3"/>
-      <c r="D53" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B54" s="18"/>
-      <c r="C54" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="D54" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B55" s="18"/>
-      <c r="C55" s="3"/>
-      <c r="D55" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="56" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B56" s="18"/>
-      <c r="C56" s="3"/>
-      <c r="D56" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B57" s="18"/>
-      <c r="C57" s="3"/>
-      <c r="D57" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="58" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B58" s="18"/>
-      <c r="C58" s="3"/>
-      <c r="D58" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="59" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B59" s="18"/>
-      <c r="C59" s="3"/>
-      <c r="D59" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B60" s="18"/>
-      <c r="C60" s="3"/>
-      <c r="D60" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="61" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B61" s="19"/>
-      <c r="C61" s="3"/>
-      <c r="D61" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62" spans="2:4" ht="72" x14ac:dyDescent="0.45">
-      <c r="B62" s="32" t="s">
-        <v>100</v>
-      </c>
-      <c r="C62" s="3" t="s">
+      <c r="F13" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="G13" s="6">
+        <f>SUMIF('新入社員研修（詳細）'!D209:D257,"要件定義",'新入社員研修（詳細）'!H209:H257)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B14" s="32"/>
+      <c r="C14" s="40"/>
+      <c r="D14" s="40"/>
+      <c r="E14" s="40"/>
+      <c r="F14" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="G14" s="6">
+        <f>SUMIF('新入社員研修（詳細）'!D209:D257,"&lt;&gt;要件定義",'新入社員研修（詳細）'!H209:H257)</f>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7" ht="36" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B15" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C15" s="39" t="s">
+        <v>72</v>
+      </c>
+      <c r="D15" s="39" t="s">
+        <v>72</v>
+      </c>
+      <c r="E15" s="39" t="s">
         <v>167</v>
       </c>
-      <c r="D62" s="6">
-        <f>SUM('新入社員研修（詳細）'!H62:H110)</f>
-        <v>84</v>
-      </c>
-    </row>
-    <row r="63" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B63" s="18"/>
-      <c r="C63" s="27" t="s">
-        <v>159</v>
-      </c>
-      <c r="D63" s="31">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="64" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B64" s="18"/>
-      <c r="C64" s="3"/>
-      <c r="D64" s="6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="65" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B65" s="18"/>
-      <c r="C65" s="3"/>
-      <c r="D65" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B66" s="18"/>
-      <c r="C66" s="3"/>
-      <c r="D66" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="67" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B67" s="18"/>
-      <c r="C67" s="3"/>
-      <c r="D67" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="68" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B68" s="18"/>
-      <c r="C68" s="3"/>
-      <c r="D68" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="69" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B69" s="18"/>
-      <c r="C69" s="3"/>
-      <c r="D69" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="70" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B70" s="18"/>
-      <c r="C70" s="3"/>
-      <c r="D70" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="71" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B71" s="18"/>
-      <c r="C71" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="D71" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="72" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B72" s="18"/>
-      <c r="C72" s="3"/>
-      <c r="D72" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="73" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B73" s="18"/>
-      <c r="C73" s="3"/>
-      <c r="D73" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B74" s="18"/>
-      <c r="C74" s="3"/>
-      <c r="D74" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="75" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B75" s="18"/>
-      <c r="C75" s="3"/>
-      <c r="D75" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="76" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B76" s="18"/>
-      <c r="C76" s="3"/>
-      <c r="D76" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="77" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B77" s="18"/>
-      <c r="C77" s="3"/>
-      <c r="D77" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="78" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B78" s="18"/>
-      <c r="C78" s="3"/>
-      <c r="D78" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="79" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B79" s="18"/>
-      <c r="C79" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="D79" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="80" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B80" s="18"/>
-      <c r="C80" s="3"/>
-      <c r="D80" s="6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="81" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B81" s="18"/>
-      <c r="C81" s="3"/>
-      <c r="D81" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B82" s="18"/>
-      <c r="C82" s="3"/>
-      <c r="D82" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="83" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B83" s="18"/>
-      <c r="C83" s="3"/>
-      <c r="D83" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="84" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B84" s="18"/>
-      <c r="C84" s="3"/>
-      <c r="D84" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="85" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B85" s="18"/>
-      <c r="C85" s="3"/>
-      <c r="D85" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="86" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B86" s="18"/>
-      <c r="C86" s="3"/>
-      <c r="D86" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="87" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B87" s="18"/>
-      <c r="C87" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="D87" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="88" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B88" s="18"/>
-      <c r="C88" s="3"/>
-      <c r="D88" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="89" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B89" s="18"/>
-      <c r="C89" s="3"/>
-      <c r="D89" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B90" s="18"/>
-      <c r="C90" s="3"/>
-      <c r="D90" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="91" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B91" s="18"/>
-      <c r="C91" s="3"/>
-      <c r="D91" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="92" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B92" s="18"/>
-      <c r="C92" s="3"/>
-      <c r="D92" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="93" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B93" s="18"/>
-      <c r="C93" s="3"/>
-      <c r="D93" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="94" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B94" s="18"/>
-      <c r="C94" s="3"/>
-      <c r="D94" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="95" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B95" s="18"/>
-      <c r="C95" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="D95" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="96" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B96" s="18"/>
-      <c r="C96" s="3"/>
-      <c r="D96" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="97" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B97" s="18"/>
-      <c r="C97" s="3"/>
-      <c r="D97" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B98" s="18"/>
-      <c r="C98" s="3"/>
-      <c r="D98" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="99" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B99" s="18"/>
-      <c r="C99" s="3"/>
-      <c r="D99" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="100" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B100" s="18"/>
-      <c r="C100" s="3"/>
-      <c r="D100" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="101" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B101" s="18"/>
-      <c r="C101" s="3"/>
-      <c r="D101" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="102" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B102" s="18"/>
-      <c r="C102" s="3"/>
-      <c r="D102" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="103" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B103" s="18"/>
-      <c r="C103" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="D103" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="104" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B104" s="18"/>
-      <c r="C104" s="3"/>
-      <c r="D104" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="105" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B105" s="18"/>
-      <c r="C105" s="3"/>
-      <c r="D105" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B106" s="18"/>
-      <c r="C106" s="3"/>
-      <c r="D106" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="107" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B107" s="18"/>
-      <c r="C107" s="3"/>
-      <c r="D107" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="108" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B108" s="18"/>
-      <c r="C108" s="3"/>
-      <c r="D108" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="109" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B109" s="18"/>
-      <c r="C109" s="3"/>
-      <c r="D109" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="110" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B110" s="19"/>
-      <c r="C110" s="3"/>
-      <c r="D110" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="111" spans="2:4" ht="90" x14ac:dyDescent="0.45">
-      <c r="B111" s="32" t="s">
-        <v>101</v>
-      </c>
-      <c r="C111" s="3" t="s">
+      <c r="F15" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="G15" s="6">
+        <f>SUMIF('新入社員研修（詳細）'!D258:D298,"要件定義",'新入社員研修（詳細）'!H258:H298)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B16" s="32"/>
+      <c r="C16" s="40"/>
+      <c r="D16" s="40"/>
+      <c r="E16" s="40"/>
+      <c r="F16" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="G16" s="6">
+        <f>SUMIF('新入社員研修（詳細）'!D258:D298,"&lt;&gt;要件定義",'新入社員研修（詳細）'!H258:H298)</f>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9" ht="36" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B17" s="30" t="s">
+        <v>55</v>
+      </c>
+      <c r="C17" s="39" t="s">
+        <v>72</v>
+      </c>
+      <c r="D17" s="39" t="s">
+        <v>72</v>
+      </c>
+      <c r="E17" s="39" t="s">
         <v>168</v>
       </c>
-      <c r="D111" s="6">
-        <f>SUM('新入社員研修（詳細）'!H111:H175)</f>
-        <v>74</v>
-      </c>
-    </row>
-    <row r="112" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B112" s="18"/>
-      <c r="C112" s="27" t="s">
-        <v>132</v>
-      </c>
-      <c r="D112" s="31">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="113" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B113" s="18"/>
-      <c r="C113" s="3"/>
-      <c r="D113" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="114" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B114" s="18"/>
-      <c r="C114" s="3"/>
-      <c r="D114" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B115" s="18"/>
-      <c r="C115" s="3"/>
-      <c r="D115" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B116" s="18"/>
-      <c r="C116" s="3"/>
-      <c r="D116" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B117" s="18"/>
-      <c r="C117" s="3"/>
-      <c r="D117" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="118" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B118" s="18"/>
-      <c r="C118" s="3"/>
-      <c r="D118" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="119" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B119" s="18"/>
-      <c r="C119" s="3"/>
-      <c r="D119" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="120" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B120" s="18"/>
-      <c r="C120" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="D120" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="121" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B121" s="18"/>
-      <c r="C121" s="3"/>
-      <c r="D121" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="122" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B122" s="18"/>
-      <c r="C122" s="3"/>
-      <c r="D122" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="123" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B123" s="18"/>
-      <c r="C123" s="3"/>
-      <c r="D123" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="124" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B124" s="18"/>
-      <c r="C124" s="3"/>
-      <c r="D124" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="125" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B125" s="18"/>
-      <c r="C125" s="3"/>
-      <c r="D125" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="126" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B126" s="18"/>
-      <c r="C126" s="3"/>
-      <c r="D126" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="127" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B127" s="18"/>
-      <c r="C127" s="3"/>
-      <c r="D127" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="128" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B128" s="18"/>
-      <c r="C128" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="D128" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="129" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B129" s="18"/>
-      <c r="C129" s="3"/>
-      <c r="D129" s="6">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="130" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B130" s="18"/>
-      <c r="C130" s="3"/>
-      <c r="D130" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="131" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B131" s="18"/>
-      <c r="C131" s="3"/>
-      <c r="D131" s="6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="132" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B132" s="18"/>
-      <c r="C132" s="3"/>
-      <c r="D132" s="6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="133" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B133" s="18"/>
-      <c r="C133" s="3"/>
-      <c r="D133" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="134" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B134" s="18"/>
-      <c r="C134" s="3"/>
-      <c r="D134" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="135" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B135" s="18"/>
-      <c r="C135" s="3"/>
-      <c r="D135" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="136" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B136" s="18"/>
-      <c r="C136" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="D136" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="137" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B137" s="18"/>
-      <c r="C137" s="3"/>
-      <c r="D137" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="138" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B138" s="18"/>
-      <c r="C138" s="3"/>
-      <c r="D138" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="139" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B139" s="18"/>
-      <c r="C139" s="3"/>
-      <c r="D139" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="140" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B140" s="18"/>
-      <c r="C140" s="3"/>
-      <c r="D140" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="141" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B141" s="18"/>
-      <c r="C141" s="3"/>
-      <c r="D141" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="142" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B142" s="18"/>
-      <c r="C142" s="3"/>
-      <c r="D142" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="143" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B143" s="18"/>
-      <c r="C143" s="3"/>
-      <c r="D143" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="144" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B144" s="18"/>
-      <c r="C144" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="D144" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="145" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B145" s="18"/>
-      <c r="C145" s="3"/>
-      <c r="D145" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="146" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B146" s="18"/>
-      <c r="C146" s="3"/>
-      <c r="D146" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="147" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B147" s="18"/>
-      <c r="C147" s="3"/>
-      <c r="D147" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="148" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B148" s="18"/>
-      <c r="C148" s="3"/>
-      <c r="D148" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="149" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B149" s="18"/>
-      <c r="C149" s="3"/>
-      <c r="D149" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="150" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B150" s="18"/>
-      <c r="C150" s="3"/>
-      <c r="D150" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="151" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B151" s="18"/>
-      <c r="C151" s="3"/>
-      <c r="D151" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="152" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B152" s="18"/>
-      <c r="C152" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="D152" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="153" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B153" s="18"/>
-      <c r="C153" s="3"/>
-      <c r="D153" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="154" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B154" s="18"/>
-      <c r="C154" s="3"/>
-      <c r="D154" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="155" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B155" s="18"/>
-      <c r="C155" s="3"/>
-      <c r="D155" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="156" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B156" s="18"/>
-      <c r="C156" s="3"/>
-      <c r="D156" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="157" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B157" s="18"/>
-      <c r="C157" s="3"/>
-      <c r="D157" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="158" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B158" s="18"/>
-      <c r="C158" s="3"/>
-      <c r="D158" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="159" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B159" s="18"/>
-      <c r="C159" s="3"/>
-      <c r="D159" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="160" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B160" s="18"/>
-      <c r="C160" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="D160" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="161" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B161" s="18"/>
-      <c r="C161" s="3"/>
-      <c r="D161" s="6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="162" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B162" s="18"/>
-      <c r="C162" s="3"/>
-      <c r="D162" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="163" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B163" s="18"/>
-      <c r="C163" s="3"/>
-      <c r="D163" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="164" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B164" s="18"/>
-      <c r="C164" s="3"/>
-      <c r="D164" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="165" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B165" s="18"/>
-      <c r="C165" s="3"/>
-      <c r="D165" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="166" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B166" s="18"/>
-      <c r="C166" s="3"/>
-      <c r="D166" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="167" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B167" s="18"/>
-      <c r="C167" s="3"/>
-      <c r="D167" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="168" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B168" s="18"/>
-      <c r="C168" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="D168" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="169" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B169" s="18"/>
-      <c r="C169" s="3"/>
-      <c r="D169" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="170" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B170" s="18"/>
-      <c r="C170" s="3"/>
-      <c r="D170" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="171" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B171" s="18"/>
-      <c r="C171" s="3"/>
-      <c r="D171" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="172" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B172" s="18"/>
-      <c r="C172" s="3"/>
-      <c r="D172" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="173" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B173" s="18"/>
-      <c r="C173" s="3"/>
-      <c r="D173" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="174" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B174" s="18"/>
-      <c r="C174" s="3"/>
-      <c r="D174" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="175" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B175" s="19"/>
-      <c r="C175" s="3"/>
-      <c r="D175" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="176" spans="2:4" ht="36" x14ac:dyDescent="0.45">
-      <c r="B176" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C176" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="D176" s="6">
-        <f>SUM('新入社員研修（詳細）'!H176:H208)</f>
-        <v>17</v>
-      </c>
-    </row>
-    <row r="177" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B177" s="12"/>
-      <c r="C177" s="27" t="s">
-        <v>136</v>
-      </c>
-      <c r="D177" s="31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="178" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B178" s="18"/>
-      <c r="C178" s="3"/>
-      <c r="D178" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="179" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B179" s="18"/>
-      <c r="C179" s="3"/>
-      <c r="D179" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="180" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B180" s="18"/>
-      <c r="C180" s="3"/>
-      <c r="D180" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="181" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B181" s="18"/>
-      <c r="C181" s="3"/>
-      <c r="D181" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="182" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B182" s="18"/>
-      <c r="C182" s="3"/>
-      <c r="D182" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="183" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B183" s="18"/>
-      <c r="C183" s="3"/>
-      <c r="D183" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="184" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B184" s="18"/>
-      <c r="C184" s="3"/>
-      <c r="D184" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="185" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B185" s="12"/>
-      <c r="C185" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="D185" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="186" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B186" s="18"/>
-      <c r="C186" s="3"/>
-      <c r="D186" s="6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="187" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B187" s="18"/>
-      <c r="C187" s="3"/>
-      <c r="D187" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="188" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B188" s="18"/>
-      <c r="C188" s="3"/>
-      <c r="D188" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="189" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B189" s="18"/>
-      <c r="C189" s="3"/>
-      <c r="D189" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="190" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B190" s="18"/>
-      <c r="C190" s="3"/>
-      <c r="D190" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="191" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B191" s="18"/>
-      <c r="C191" s="3"/>
-      <c r="D191" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="192" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B192" s="18"/>
-      <c r="C192" s="3"/>
-      <c r="D192" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="193" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B193" s="12"/>
-      <c r="C193" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="D193" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="194" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B194" s="18"/>
-      <c r="C194" s="3"/>
-      <c r="D194" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="195" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B195" s="18"/>
-      <c r="C195" s="3"/>
-      <c r="D195" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="196" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B196" s="18"/>
-      <c r="C196" s="3"/>
-      <c r="D196" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="197" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B197" s="18"/>
-      <c r="C197" s="3"/>
-      <c r="D197" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="198" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B198" s="18"/>
-      <c r="C198" s="3"/>
-      <c r="D198" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="199" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B199" s="18"/>
-      <c r="C199" s="3"/>
-      <c r="D199" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="200" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B200" s="18"/>
-      <c r="C200" s="3"/>
-      <c r="D200" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="201" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B201" s="18"/>
-      <c r="C201" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="D201" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="202" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B202" s="18"/>
-      <c r="C202" s="3"/>
-      <c r="D202" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="203" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B203" s="18"/>
-      <c r="C203" s="3"/>
-      <c r="D203" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="204" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B204" s="18"/>
-      <c r="C204" s="3"/>
-      <c r="D204" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="205" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B205" s="18"/>
-      <c r="C205" s="3"/>
-      <c r="D205" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="206" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B206" s="18"/>
-      <c r="C206" s="3"/>
-      <c r="D206" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="207" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B207" s="18"/>
-      <c r="C207" s="3"/>
-      <c r="D207" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="208" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B208" s="19"/>
-      <c r="C208" s="3"/>
-      <c r="D208" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="209" spans="2:4" ht="36" x14ac:dyDescent="0.45">
-      <c r="B209" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C209" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="D209" s="6">
-        <f>SUM('新入社員研修（詳細）'!H209:H257)</f>
-        <v>28</v>
-      </c>
-    </row>
-    <row r="210" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B210" s="12"/>
-      <c r="C210" s="27" t="s">
-        <v>136</v>
-      </c>
-      <c r="D210" s="31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="211" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B211" s="18"/>
-      <c r="C211" s="3"/>
-      <c r="D211" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="212" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B212" s="18"/>
-      <c r="C212" s="3"/>
-      <c r="D212" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="213" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B213" s="18"/>
-      <c r="C213" s="3"/>
-      <c r="D213" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="214" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B214" s="18"/>
-      <c r="C214" s="3"/>
-      <c r="D214" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="215" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B215" s="18"/>
-      <c r="C215" s="3"/>
-      <c r="D215" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="216" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B216" s="18"/>
-      <c r="C216" s="3"/>
-      <c r="D216" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="217" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B217" s="18"/>
-      <c r="C217" s="3"/>
-      <c r="D217" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="218" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B218" s="12"/>
-      <c r="C218" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="D218" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="219" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B219" s="18"/>
-      <c r="C219" s="3"/>
-      <c r="D219" s="6">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="220" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B220" s="18"/>
-      <c r="C220" s="3"/>
-      <c r="D220" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="221" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B221" s="18"/>
-      <c r="C221" s="3"/>
-      <c r="D221" s="6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="222" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B222" s="18"/>
-      <c r="C222" s="3"/>
-      <c r="D222" s="6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="223" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B223" s="18"/>
-      <c r="C223" s="3"/>
-      <c r="D223" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="224" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B224" s="18"/>
-      <c r="C224" s="3"/>
-      <c r="D224" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="225" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B225" s="18"/>
-      <c r="C225" s="3"/>
-      <c r="D225" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="226" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B226" s="12"/>
-      <c r="C226" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="D226" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="227" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B227" s="18"/>
-      <c r="C227" s="3"/>
-      <c r="D227" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="228" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B228" s="18"/>
-      <c r="C228" s="3"/>
-      <c r="D228" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="229" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B229" s="18"/>
-      <c r="C229" s="3"/>
-      <c r="D229" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="230" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B230" s="18"/>
-      <c r="C230" s="3"/>
-      <c r="D230" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="231" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B231" s="18"/>
-      <c r="C231" s="3"/>
-      <c r="D231" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="232" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B232" s="18"/>
-      <c r="C232" s="3"/>
-      <c r="D232" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="233" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B233" s="18"/>
-      <c r="C233" s="3"/>
-      <c r="D233" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="234" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B234" s="18"/>
-      <c r="C234" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="D234" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="235" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B235" s="18"/>
-      <c r="C235" s="3"/>
-      <c r="D235" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="236" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B236" s="18"/>
-      <c r="C236" s="3"/>
-      <c r="D236" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="237" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B237" s="18"/>
-      <c r="C237" s="3"/>
-      <c r="D237" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="238" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B238" s="18"/>
-      <c r="C238" s="3"/>
-      <c r="D238" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="239" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B239" s="18"/>
-      <c r="C239" s="3"/>
-      <c r="D239" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="240" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B240" s="18"/>
-      <c r="C240" s="3"/>
-      <c r="D240" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="241" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B241" s="18"/>
-      <c r="C241" s="3"/>
-      <c r="D241" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="242" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B242" s="18"/>
-      <c r="C242" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="D242" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="243" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B243" s="18"/>
-      <c r="C243" s="3"/>
-      <c r="D243" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="244" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B244" s="18"/>
-      <c r="C244" s="3"/>
-      <c r="D244" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="245" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B245" s="18"/>
-      <c r="C245" s="3"/>
-      <c r="D245" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="246" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B246" s="18"/>
-      <c r="C246" s="3"/>
-      <c r="D246" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="247" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B247" s="18"/>
-      <c r="C247" s="3"/>
-      <c r="D247" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="248" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B248" s="18"/>
-      <c r="C248" s="3"/>
-      <c r="D248" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="249" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B249" s="18"/>
-      <c r="C249" s="3"/>
-      <c r="D249" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="250" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B250" s="18"/>
-      <c r="C250" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="D250" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="251" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B251" s="18"/>
-      <c r="C251" s="3"/>
-      <c r="D251" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="252" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B252" s="18"/>
-      <c r="C252" s="3"/>
-      <c r="D252" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="253" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B253" s="18"/>
-      <c r="C253" s="3"/>
-      <c r="D253" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="254" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B254" s="18"/>
-      <c r="C254" s="3"/>
-      <c r="D254" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="255" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B255" s="18"/>
-      <c r="C255" s="3"/>
-      <c r="D255" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="256" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B256" s="18"/>
-      <c r="C256" s="3"/>
-      <c r="D256" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="257" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B257" s="19"/>
-      <c r="C257" s="3"/>
-      <c r="D257" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="258" spans="2:4" ht="36" x14ac:dyDescent="0.45">
-      <c r="B258" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C258" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="D258" s="6">
-        <f>SUM('新入社員研修（詳細）'!H258:H298)</f>
-        <v>45</v>
-      </c>
-    </row>
-    <row r="259" spans="2:4" ht="108" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B259" s="12"/>
-      <c r="C259" s="27" t="s">
-        <v>156</v>
-      </c>
-      <c r="D259" s="31">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="260" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B260" s="18"/>
-      <c r="D260" s="6">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="261" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B261" s="18"/>
-      <c r="C261" s="3"/>
-      <c r="D261" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="262" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B262" s="18"/>
-      <c r="C262" s="3"/>
-      <c r="D262" s="6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="263" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B263" s="18"/>
-      <c r="C263" s="3"/>
-      <c r="D263" s="6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="264" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B264" s="18"/>
-      <c r="C264" s="3"/>
-      <c r="D264" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="265" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B265" s="18"/>
-      <c r="C265" s="3"/>
-      <c r="D265" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="266" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B266" s="18"/>
-      <c r="C266" s="3"/>
-      <c r="D266" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="267" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B267" s="12"/>
-      <c r="C267" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="D267" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="268" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B268" s="18"/>
-      <c r="C268" s="3"/>
-      <c r="D268" s="6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="269" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B269" s="18"/>
-      <c r="C269" s="3"/>
-      <c r="D269" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="270" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B270" s="18"/>
-      <c r="C270" s="3"/>
-      <c r="D270" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="271" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B271" s="18"/>
-      <c r="C271" s="3"/>
-      <c r="D271" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="272" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B272" s="18"/>
-      <c r="C272" s="3"/>
-      <c r="D272" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="273" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B273" s="18"/>
-      <c r="C273" s="3"/>
-      <c r="D273" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="274" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B274" s="18"/>
-      <c r="C274" s="3"/>
-      <c r="D274" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="275" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B275" s="18"/>
-      <c r="C275" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="D275" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="276" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B276" s="18"/>
-      <c r="C276" s="3"/>
-      <c r="D276" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="277" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B277" s="18"/>
-      <c r="C277" s="3"/>
-      <c r="D277" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="278" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B278" s="18"/>
-      <c r="C278" s="3"/>
-      <c r="D278" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="279" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B279" s="18"/>
-      <c r="C279" s="3"/>
-      <c r="D279" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="280" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B280" s="18"/>
-      <c r="C280" s="3"/>
-      <c r="D280" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="281" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B281" s="18"/>
-      <c r="C281" s="3"/>
-      <c r="D281" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="282" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B282" s="18"/>
-      <c r="C282" s="3"/>
-      <c r="D282" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="283" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B283" s="18"/>
-      <c r="C283" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="D283" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="284" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B284" s="18"/>
-      <c r="D284" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="285" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B285" s="18"/>
-      <c r="C285" s="3"/>
-      <c r="D285" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="286" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B286" s="18"/>
-      <c r="C286" s="3"/>
-      <c r="D286" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="287" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B287" s="18"/>
-      <c r="C287" s="3"/>
-      <c r="D287" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="288" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B288" s="18"/>
-      <c r="C288" s="3"/>
-      <c r="D288" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="289" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B289" s="18"/>
-      <c r="C289" s="3"/>
-      <c r="D289" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="290" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B290" s="18"/>
-      <c r="C290" s="3"/>
-      <c r="D290" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="291" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B291" s="18"/>
-      <c r="C291" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="D291" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="292" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B292" s="18"/>
-      <c r="D292" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="293" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B293" s="18"/>
-      <c r="C293" s="3"/>
-      <c r="D293" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="294" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B294" s="18"/>
-      <c r="C294" s="3"/>
-      <c r="D294" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="295" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B295" s="18"/>
-      <c r="C295" s="3"/>
-      <c r="D295" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="296" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B296" s="18"/>
-      <c r="C296" s="3"/>
-      <c r="D296" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="297" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B297" s="18"/>
-      <c r="C297" s="3"/>
-      <c r="D297" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="298" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B298" s="18"/>
-      <c r="C298" s="3"/>
-      <c r="D298" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="299" spans="2:4" ht="36" x14ac:dyDescent="0.45">
-      <c r="B299" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C299" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="D299" s="6">
-        <f>SUM('新入社員研修（詳細）'!H299:H347)</f>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="300" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B300" s="12"/>
-      <c r="C300" s="27" t="s">
-        <v>136</v>
-      </c>
-      <c r="D300" s="31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="301" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B301" s="18"/>
-      <c r="C301" s="3"/>
-      <c r="D301" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="302" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B302" s="18"/>
-      <c r="C302" s="3"/>
-      <c r="D302" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="303" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B303" s="18"/>
-      <c r="C303" s="3"/>
-      <c r="D303" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="304" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B304" s="18"/>
-      <c r="C304" s="3"/>
-      <c r="D304" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="305" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B305" s="18"/>
-      <c r="C305" s="3"/>
-      <c r="D305" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="306" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B306" s="18"/>
-      <c r="C306" s="3"/>
-      <c r="D306" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="307" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B307" s="18"/>
-      <c r="C307" s="3"/>
-      <c r="D307" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="308" spans="2:4" ht="108" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B308" s="12"/>
-      <c r="C308" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="D308" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="309" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B309" s="18"/>
-      <c r="C309" s="3"/>
-      <c r="D309" s="6">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="310" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B310" s="18"/>
-      <c r="C310" s="3"/>
-      <c r="D310" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="311" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B311" s="18"/>
-      <c r="C311" s="3"/>
-      <c r="D311" s="6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="312" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B312" s="18"/>
-      <c r="C312" s="3"/>
-      <c r="D312" s="6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="313" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B313" s="18"/>
-      <c r="C313" s="3"/>
-      <c r="D313" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="314" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B314" s="18"/>
-      <c r="C314" s="3"/>
-      <c r="D314" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="315" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B315" s="18"/>
-      <c r="C315" s="3"/>
-      <c r="D315" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="316" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B316" s="12"/>
-      <c r="C316" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="D316" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="317" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B317" s="18"/>
-      <c r="C317" s="3"/>
-      <c r="D317" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="318" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B318" s="18"/>
-      <c r="C318" s="3"/>
-      <c r="D318" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="319" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B319" s="18"/>
-      <c r="C319" s="3"/>
-      <c r="D319" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="320" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B320" s="18"/>
-      <c r="C320" s="3"/>
-      <c r="D320" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="321" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B321" s="18"/>
-      <c r="C321" s="3"/>
-      <c r="D321" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="322" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B322" s="18"/>
-      <c r="C322" s="3"/>
-      <c r="D322" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="323" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B323" s="18"/>
-      <c r="C323" s="3"/>
-      <c r="D323" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="324" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B324" s="12"/>
-      <c r="C324" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="D324" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="325" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B325" s="18"/>
-      <c r="C325" s="3"/>
-      <c r="D325" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="326" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B326" s="18"/>
-      <c r="C326" s="3"/>
-      <c r="D326" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="327" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B327" s="18"/>
-      <c r="C327" s="3"/>
-      <c r="D327" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="328" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B328" s="18"/>
-      <c r="C328" s="3"/>
-      <c r="D328" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="329" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B329" s="18"/>
-      <c r="C329" s="3"/>
-      <c r="D329" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="330" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B330" s="18"/>
-      <c r="C330" s="3"/>
-      <c r="D330" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="331" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B331" s="18"/>
-      <c r="C331" s="3"/>
-      <c r="D331" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="332" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B332" s="12"/>
-      <c r="C332" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="D332" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="333" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B333" s="18"/>
-      <c r="C333" s="3"/>
-      <c r="D333" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="334" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B334" s="18"/>
-      <c r="C334" s="3"/>
-      <c r="D334" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="335" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B335" s="18"/>
-      <c r="C335" s="3"/>
-      <c r="D335" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="336" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B336" s="18"/>
-      <c r="C336" s="3"/>
-      <c r="D336" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="337" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B337" s="18"/>
-      <c r="C337" s="3"/>
-      <c r="D337" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="338" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B338" s="18"/>
-      <c r="C338" s="3"/>
-      <c r="D338" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="339" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B339" s="18"/>
-      <c r="C339" s="3"/>
-      <c r="D339" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="340" spans="2:4" ht="126" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B340" s="12"/>
-      <c r="C340" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="D340" s="6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="341" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B341" s="18"/>
-      <c r="C341" s="3"/>
-      <c r="D341" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="342" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B342" s="18"/>
-      <c r="C342" s="3"/>
-      <c r="D342" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="343" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B343" s="18"/>
-      <c r="C343" s="3"/>
-      <c r="D343" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="344" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B344" s="18"/>
-      <c r="C344" s="3"/>
-      <c r="D344" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="345" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B345" s="18"/>
-      <c r="C345" s="3"/>
-      <c r="D345" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="346" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B346" s="18"/>
-      <c r="C346" s="3"/>
-      <c r="D346" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="347" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B347" s="19"/>
-      <c r="C347" s="3"/>
-      <c r="D347" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="348" spans="2:4" ht="36" x14ac:dyDescent="0.45">
-      <c r="B348" s="32" t="s">
+      <c r="F17" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="G17" s="6">
+        <f>SUMIF('新入社員研修（詳細）'!D299:D347,"要件定義",'新入社員研修（詳細）'!H299:H347)</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B18" s="32"/>
+      <c r="C18" s="40"/>
+      <c r="D18" s="40"/>
+      <c r="E18" s="40"/>
+      <c r="F18" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="G18" s="6">
+        <f>SUMIF('新入社員研修（詳細）'!D299:D347,"&lt;&gt;要件定義",'新入社員研修（詳細）'!H299:H347)</f>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9" ht="36" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B19" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="C348" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="D348" s="6">
-        <f>SUM('新入社員研修（詳細）'!H348:H396)</f>
-        <v>33</v>
-      </c>
-    </row>
-    <row r="349" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B349" s="18"/>
-      <c r="C349" s="27" t="s">
-        <v>136</v>
-      </c>
-      <c r="D349" s="31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="350" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B350" s="18"/>
-      <c r="C350" s="3"/>
-      <c r="D350" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="351" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B351" s="18"/>
-      <c r="C351" s="3"/>
-      <c r="D351" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="352" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B352" s="18"/>
-      <c r="C352" s="3"/>
-      <c r="D352" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="353" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B353" s="18"/>
-      <c r="C353" s="3"/>
-      <c r="D353" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="354" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B354" s="18"/>
-      <c r="C354" s="3"/>
-      <c r="D354" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="355" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B355" s="18"/>
-      <c r="C355" s="3"/>
-      <c r="D355" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="356" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B356" s="18"/>
-      <c r="C356" s="3"/>
-      <c r="D356" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="357" spans="2:4" ht="108" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B357" s="18"/>
-      <c r="C357" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="D357" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="358" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B358" s="18"/>
-      <c r="C358" s="3"/>
-      <c r="D358" s="6">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="359" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B359" s="18"/>
-      <c r="C359" s="3"/>
-      <c r="D359" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="360" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B360" s="18"/>
-      <c r="C360" s="3"/>
-      <c r="D360" s="6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="361" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B361" s="18"/>
-      <c r="C361" s="3"/>
-      <c r="D361" s="6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="362" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B362" s="18"/>
-      <c r="C362" s="3"/>
-      <c r="D362" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="363" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B363" s="18"/>
-      <c r="C363" s="3"/>
-      <c r="D363" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="364" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B364" s="18"/>
-      <c r="C364" s="3"/>
-      <c r="D364" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="365" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B365" s="18"/>
-      <c r="C365" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="D365" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="366" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B366" s="18"/>
-      <c r="C366" s="3"/>
-      <c r="D366" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="367" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B367" s="18"/>
-      <c r="C367" s="3"/>
-      <c r="D367" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="368" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B368" s="18"/>
-      <c r="C368" s="3"/>
-      <c r="D368" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="369" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B369" s="18"/>
-      <c r="C369" s="3"/>
-      <c r="D369" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="370" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B370" s="18"/>
-      <c r="C370" s="3"/>
-      <c r="D370" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="371" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B371" s="18"/>
-      <c r="C371" s="3"/>
-      <c r="D371" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="372" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B372" s="18"/>
-      <c r="C372" s="3"/>
-      <c r="D372" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="373" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B373" s="18"/>
-      <c r="C373" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="D373" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="374" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B374" s="18"/>
-      <c r="C374" s="3"/>
-      <c r="D374" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="375" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B375" s="18"/>
-      <c r="C375" s="3"/>
-      <c r="D375" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="376" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B376" s="18"/>
-      <c r="C376" s="3"/>
-      <c r="D376" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="377" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B377" s="18"/>
-      <c r="C377" s="3"/>
-      <c r="D377" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="378" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B378" s="18"/>
-      <c r="C378" s="3"/>
-      <c r="D378" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="379" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B379" s="18"/>
-      <c r="C379" s="3"/>
-      <c r="D379" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="380" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B380" s="18"/>
-      <c r="C380" s="3"/>
-      <c r="D380" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="381" spans="2:4" ht="90" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B381" s="18"/>
-      <c r="C381" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="D381" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="382" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B382" s="18"/>
-      <c r="C382" s="3"/>
-      <c r="D382" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="383" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B383" s="18"/>
-      <c r="C383" s="3"/>
-      <c r="D383" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="384" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B384" s="18"/>
-      <c r="C384" s="3"/>
-      <c r="D384" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="385" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B385" s="18"/>
-      <c r="C385" s="3"/>
-      <c r="D385" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="386" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B386" s="18"/>
-      <c r="C386" s="3"/>
-      <c r="D386" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="387" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B387" s="18"/>
-      <c r="C387" s="3"/>
-      <c r="D387" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="388" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B388" s="18"/>
-      <c r="C388" s="3"/>
-      <c r="D388" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="389" spans="2:4" ht="126" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B389" s="18"/>
-      <c r="C389" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="D389" s="6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="390" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B390" s="18"/>
-      <c r="C390" s="3"/>
-      <c r="D390" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="391" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B391" s="18"/>
-      <c r="C391" s="3"/>
-      <c r="D391" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="392" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B392" s="18"/>
-      <c r="C392" s="3"/>
-      <c r="D392" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="393" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B393" s="18"/>
-      <c r="C393" s="3"/>
-      <c r="D393" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="394" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B394" s="18"/>
-      <c r="C394" s="3"/>
-      <c r="D394" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="395" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B395" s="18"/>
-      <c r="C395" s="3"/>
-      <c r="D395" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="396" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B396" s="19"/>
-      <c r="C396" s="3"/>
-      <c r="D396" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="397" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="D397" s="7">
-        <f>SUM(D3:D396)</f>
-        <v>694</v>
-      </c>
-    </row>
-    <row r="398" spans="2:4" hidden="1" x14ac:dyDescent="0.45">
-      <c r="D398" s="29">
-        <f>ROUNDUP(D397*1.3,0)</f>
-        <v>903</v>
-      </c>
-    </row>
-    <row r="399" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="D399" s="7">
-        <f>'新入社員研修（詳細）'!H397</f>
+      <c r="C19" s="39" t="s">
+        <v>72</v>
+      </c>
+      <c r="D19" s="39" t="s">
+        <v>72</v>
+      </c>
+      <c r="E19" s="39" t="s">
+        <v>168</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="G19" s="6">
+        <f>SUMIF('新入社員研修（詳細）'!D348:D396,"要件定義",'新入社員研修（詳細）'!H348:H396)</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B20" s="32"/>
+      <c r="C20" s="40"/>
+      <c r="D20" s="40"/>
+      <c r="E20" s="40"/>
+      <c r="F20" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="G20" s="6">
+        <f>SUMIF('新入社員研修（詳細）'!D348:D396,"&lt;&gt;要件定義",'新入社員研修（詳細）'!H348:H396)</f>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="G21" s="7">
+        <f>SUM(G3:G20)</f>
         <v>355</v>
       </c>
-    </row>
-    <row r="400" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="D400" s="29">
-        <f>'新入社員研修（詳細）'!H398</f>
+      <c r="H21" s="7">
+        <f>SUMIF(F3:F20,"&lt;&gt;要件定義",G3:G20)</f>
+        <v>299</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="22" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="G22" s="28">
+        <f>ROUNDUP(G21*1.3,0)</f>
         <v>462</v>
       </c>
+      <c r="H22" s="28">
+        <f>ROUNDUP(H21*1.3,0)</f>
+        <v>389</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="B2:D398" xr:uid="{43519A57-0157-4E94-A8ED-B58B74152C39}">
-    <filterColumn colId="0">
-      <customFilters>
-        <customFilter operator="notEqual" val=" "/>
-      </customFilters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="B2:H22" xr:uid="{65F66F02-6446-4992-B24D-AB250ADF6165}"/>
+  <mergeCells count="8">
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="B13:B14"/>
+  </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{627B9FEB-EC02-43EB-A31A-B05F0839AD0E}">
+          <x14:formula1>
+            <xm:f>項目表!$E$3:$E$11</xm:f>
+          </x14:formula1>
+          <xm:sqref>F3 F5 F7 F9 F11 F13 F15 F17 F19</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
@@ -6164,7 +3550,7 @@
         <v>72</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="H3" s="6">
         <v>0</v>
@@ -6178,7 +3564,7 @@
       <c r="D4" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E4" s="28" t="s">
+      <c r="E4" s="27" t="s">
         <v>124</v>
       </c>
       <c r="F4" s="23" t="s">
@@ -6199,7 +3585,7 @@
       <c r="D5" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E5" s="28" t="s">
+      <c r="E5" s="27" t="s">
         <v>124</v>
       </c>
       <c r="F5" s="23" t="s">
@@ -6218,10 +3604,10 @@
       <c r="D6" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E6" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F6" s="28" t="s">
+      <c r="E6" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F6" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G6" s="3"/>
@@ -6235,10 +3621,10 @@
       <c r="D7" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E7" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F7" s="28" t="s">
+      <c r="E7" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F7" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G7" s="3"/>
@@ -6252,10 +3638,10 @@
       <c r="D8" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E8" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F8" s="28" t="s">
+      <c r="E8" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F8" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G8" s="3"/>
@@ -6269,10 +3655,10 @@
       <c r="D9" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E9" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F9" s="28" t="s">
+      <c r="E9" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F9" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G9" s="3"/>
@@ -6286,10 +3672,10 @@
       <c r="D10" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E10" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F10" s="28" t="s">
+      <c r="E10" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F10" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G10" s="3"/>
@@ -6303,10 +3689,10 @@
       <c r="D11" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E11" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F11" s="28" t="s">
+      <c r="E11" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F11" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G11" s="3"/>
@@ -6320,10 +3706,10 @@
       <c r="D12" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E12" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F12" s="28" t="s">
+      <c r="E12" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F12" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G12" s="3"/>
@@ -6358,10 +3744,10 @@
       <c r="D14" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E14" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F14" s="28" t="s">
+      <c r="E14" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F14" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G14" s="3"/>
@@ -6375,10 +3761,10 @@
       <c r="D15" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E15" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F15" s="28" t="s">
+      <c r="E15" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F15" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G15" s="3"/>
@@ -6392,10 +3778,10 @@
       <c r="D16" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E16" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F16" s="28" t="s">
+      <c r="E16" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F16" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G16" s="3"/>
@@ -6409,10 +3795,10 @@
       <c r="D17" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E17" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F17" s="28" t="s">
+      <c r="E17" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F17" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G17" s="3"/>
@@ -6426,10 +3812,10 @@
       <c r="D18" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E18" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F18" s="28" t="s">
+      <c r="E18" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F18" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G18" s="3"/>
@@ -6443,10 +3829,10 @@
       <c r="D19" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E19" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F19" s="28" t="s">
+      <c r="E19" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F19" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G19" s="3"/>
@@ -6460,10 +3846,10 @@
       <c r="D20" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E20" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F20" s="28" t="s">
+      <c r="E20" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F20" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G20" s="3"/>
@@ -6479,10 +3865,10 @@
       <c r="D21" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E21" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F21" s="28" t="s">
+      <c r="E21" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F21" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G21" s="3" t="s">
@@ -6498,10 +3884,10 @@
       <c r="D22" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E22" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F22" s="28" t="s">
+      <c r="E22" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F22" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G22" s="3"/>
@@ -6515,10 +3901,10 @@
       <c r="D23" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E23" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F23" s="28" t="s">
+      <c r="E23" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F23" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G23" s="3"/>
@@ -6532,10 +3918,10 @@
       <c r="D24" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E24" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F24" s="28" t="s">
+      <c r="E24" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F24" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G24" s="3"/>
@@ -6549,10 +3935,10 @@
       <c r="D25" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E25" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F25" s="28" t="s">
+      <c r="E25" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F25" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G25" s="3"/>
@@ -6566,10 +3952,10 @@
       <c r="D26" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E26" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F26" s="28" t="s">
+      <c r="E26" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F26" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G26" s="3"/>
@@ -6583,10 +3969,10 @@
       <c r="D27" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E27" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F27" s="28" t="s">
+      <c r="E27" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F27" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G27" s="3"/>
@@ -6600,10 +3986,10 @@
       <c r="D28" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E28" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F28" s="28" t="s">
+      <c r="E28" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F28" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G28" s="3"/>
@@ -6619,10 +4005,10 @@
       <c r="D29" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E29" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F29" s="28" t="s">
+      <c r="E29" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F29" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G29" s="3" t="s">
@@ -6638,10 +4024,10 @@
       <c r="D30" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E30" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F30" s="28" t="s">
+      <c r="E30" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F30" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G30" s="3"/>
@@ -6655,10 +4041,10 @@
       <c r="D31" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E31" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F31" s="28" t="s">
+      <c r="E31" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F31" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G31" s="3"/>
@@ -6672,10 +4058,10 @@
       <c r="D32" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E32" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F32" s="28" t="s">
+      <c r="E32" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F32" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G32" s="3"/>
@@ -6689,10 +4075,10 @@
       <c r="D33" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E33" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F33" s="28" t="s">
+      <c r="E33" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F33" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G33" s="3"/>
@@ -6706,10 +4092,10 @@
       <c r="D34" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E34" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F34" s="28" t="s">
+      <c r="E34" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F34" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G34" s="3"/>
@@ -6723,10 +4109,10 @@
       <c r="D35" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E35" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F35" s="28" t="s">
+      <c r="E35" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F35" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G35" s="3"/>
@@ -6740,10 +4126,10 @@
       <c r="D36" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E36" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F36" s="28" t="s">
+      <c r="E36" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F36" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G36" s="3"/>
@@ -6782,7 +4168,7 @@
       <c r="D38" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E38" s="28" t="s">
+      <c r="E38" s="27" t="s">
         <v>124</v>
       </c>
       <c r="F38" s="23" t="s">
@@ -6801,10 +4187,10 @@
       <c r="D39" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E39" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F39" s="28" t="s">
+      <c r="E39" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F39" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G39" s="3"/>
@@ -6818,10 +4204,10 @@
       <c r="D40" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E40" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F40" s="28" t="s">
+      <c r="E40" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F40" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G40" s="3"/>
@@ -6835,10 +4221,10 @@
       <c r="D41" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E41" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F41" s="28" t="s">
+      <c r="E41" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F41" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G41" s="3"/>
@@ -6852,10 +4238,10 @@
       <c r="D42" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E42" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F42" s="28" t="s">
+      <c r="E42" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F42" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G42" s="3"/>
@@ -6869,10 +4255,10 @@
       <c r="D43" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E43" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F43" s="28" t="s">
+      <c r="E43" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F43" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G43" s="3"/>
@@ -6886,10 +4272,10 @@
       <c r="D44" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E44" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F44" s="28" t="s">
+      <c r="E44" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F44" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G44" s="3"/>
@@ -6903,10 +4289,10 @@
       <c r="D45" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E45" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F45" s="28" t="s">
+      <c r="E45" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F45" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G45" s="3"/>
@@ -7232,7 +4618,7 @@
         <v>72</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="H63" s="6">
         <v>2</v>
@@ -7372,7 +4758,7 @@
         <v>72</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="H71" s="6">
         <v>1</v>
@@ -7512,7 +4898,7 @@
         <v>72</v>
       </c>
       <c r="G79" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="H79" s="6">
         <v>2</v>
@@ -7652,7 +5038,7 @@
         <v>72</v>
       </c>
       <c r="G87" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="H87" s="6">
         <v>1</v>
@@ -7792,7 +5178,7 @@
         <v>72</v>
       </c>
       <c r="G95" s="3" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="H95" s="6">
         <v>1</v>
@@ -7932,7 +5318,7 @@
         <v>72</v>
       </c>
       <c r="G103" s="3" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="H103" s="6">
         <v>1</v>
@@ -8088,7 +5474,7 @@
       <c r="D112" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E112" s="28" t="s">
+      <c r="E112" s="27" t="s">
         <v>124</v>
       </c>
       <c r="F112" s="23" t="s">
@@ -8106,10 +5492,10 @@
       <c r="D113" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E113" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F113" s="28" t="s">
+      <c r="E113" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F113" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G113" s="3"/>
@@ -8122,10 +5508,10 @@
       <c r="D114" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E114" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F114" s="28" t="s">
+      <c r="E114" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F114" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G114" s="3"/>
@@ -8138,10 +5524,10 @@
       <c r="D115" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E115" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F115" s="28" t="s">
+      <c r="E115" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F115" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G115" s="3"/>
@@ -8154,10 +5540,10 @@
       <c r="D116" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E116" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F116" s="28" t="s">
+      <c r="E116" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F116" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G116" s="3"/>
@@ -8170,10 +5556,10 @@
       <c r="D117" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E117" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F117" s="28" t="s">
+      <c r="E117" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F117" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G117" s="3"/>
@@ -8187,10 +5573,10 @@
       <c r="D118" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E118" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F118" s="28" t="s">
+      <c r="E118" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F118" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G118" s="3"/>
@@ -8204,10 +5590,10 @@
       <c r="D119" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E119" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F119" s="28" t="s">
+      <c r="E119" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F119" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G119" s="3"/>
@@ -8223,7 +5609,7 @@
       <c r="D120" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E120" s="28" t="s">
+      <c r="E120" s="27" t="s">
         <v>124</v>
       </c>
       <c r="F120" s="23" t="s">
@@ -8242,10 +5628,10 @@
       <c r="D121" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E121" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F121" s="28" t="s">
+      <c r="E121" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F121" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G121" s="3"/>
@@ -8259,10 +5645,10 @@
       <c r="D122" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E122" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F122" s="28" t="s">
+      <c r="E122" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F122" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G122" s="3"/>
@@ -8276,10 +5662,10 @@
       <c r="D123" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E123" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F123" s="28" t="s">
+      <c r="E123" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F123" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G123" s="3"/>
@@ -8293,10 +5679,10 @@
       <c r="D124" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E124" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F124" s="28" t="s">
+      <c r="E124" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F124" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G124" s="3"/>
@@ -8310,10 +5696,10 @@
       <c r="D125" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E125" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F125" s="28" t="s">
+      <c r="E125" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F125" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G125" s="3"/>
@@ -8327,10 +5713,10 @@
       <c r="D126" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E126" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F126" s="28" t="s">
+      <c r="E126" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F126" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G126" s="3"/>
@@ -8344,10 +5730,10 @@
       <c r="D127" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E127" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F127" s="28" t="s">
+      <c r="E127" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F127" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G127" s="3"/>
@@ -8643,7 +6029,7 @@
       <c r="D144" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E144" s="28" t="s">
+      <c r="E144" s="27" t="s">
         <v>124</v>
       </c>
       <c r="F144" s="23" t="s">
@@ -8662,10 +6048,10 @@
       <c r="D145" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E145" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F145" s="28" t="s">
+      <c r="E145" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F145" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G145" s="3"/>
@@ -8679,10 +6065,10 @@
       <c r="D146" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E146" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F146" s="28" t="s">
+      <c r="E146" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F146" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G146" s="3"/>
@@ -8696,10 +6082,10 @@
       <c r="D147" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E147" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F147" s="28" t="s">
+      <c r="E147" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F147" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G147" s="3"/>
@@ -8713,10 +6099,10 @@
       <c r="D148" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E148" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F148" s="28" t="s">
+      <c r="E148" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F148" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G148" s="3"/>
@@ -8730,10 +6116,10 @@
       <c r="D149" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E149" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F149" s="28" t="s">
+      <c r="E149" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F149" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G149" s="3"/>
@@ -8747,10 +6133,10 @@
       <c r="D150" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E150" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F150" s="28" t="s">
+      <c r="E150" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F150" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G150" s="3"/>
@@ -8764,10 +6150,10 @@
       <c r="D151" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E151" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F151" s="28" t="s">
+      <c r="E151" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F151" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G151" s="3"/>
@@ -8783,7 +6169,7 @@
       <c r="D152" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E152" s="28" t="s">
+      <c r="E152" s="27" t="s">
         <v>124</v>
       </c>
       <c r="F152" s="23" t="s">
@@ -8801,10 +6187,10 @@
       <c r="D153" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E153" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F153" s="28" t="s">
+      <c r="E153" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F153" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G153" s="3"/>
@@ -8817,10 +6203,10 @@
       <c r="D154" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E154" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F154" s="28" t="s">
+      <c r="E154" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F154" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G154" s="3"/>
@@ -8833,10 +6219,10 @@
       <c r="D155" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E155" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F155" s="28" t="s">
+      <c r="E155" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F155" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G155" s="3"/>
@@ -8849,10 +6235,10 @@
       <c r="D156" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E156" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F156" s="28" t="s">
+      <c r="E156" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F156" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G156" s="3"/>
@@ -8865,10 +6251,10 @@
       <c r="D157" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E157" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F157" s="28" t="s">
+      <c r="E157" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F157" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G157" s="3"/>
@@ -8882,10 +6268,10 @@
       <c r="D158" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E158" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F158" s="28" t="s">
+      <c r="E158" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F158" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G158" s="3"/>
@@ -8898,10 +6284,10 @@
       <c r="D159" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E159" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F159" s="28" t="s">
+      <c r="E159" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F159" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G159" s="3"/>
@@ -8924,7 +6310,7 @@
         <v>72</v>
       </c>
       <c r="G160" s="3" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="H160" s="6">
         <v>2</v>
@@ -9064,7 +6450,7 @@
         <v>72</v>
       </c>
       <c r="G168" s="3" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="H168" s="6">
         <v>1</v>
@@ -9214,10 +6600,10 @@
       <c r="D177" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E177" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F177" s="28" t="s">
+      <c r="E177" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F177" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G177" s="3" t="s">
@@ -9232,10 +6618,10 @@
       <c r="D178" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E178" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F178" s="28" t="s">
+      <c r="E178" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F178" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G178" s="3"/>
@@ -9248,10 +6634,10 @@
       <c r="D179" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E179" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F179" s="28" t="s">
+      <c r="E179" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F179" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G179" s="3"/>
@@ -9264,10 +6650,10 @@
       <c r="D180" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E180" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F180" s="28" t="s">
+      <c r="E180" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F180" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G180" s="3"/>
@@ -9280,10 +6666,10 @@
       <c r="D181" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E181" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F181" s="28" t="s">
+      <c r="E181" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F181" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G181" s="3"/>
@@ -9296,10 +6682,10 @@
       <c r="D182" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E182" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F182" s="28" t="s">
+      <c r="E182" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F182" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G182" s="3"/>
@@ -9313,10 +6699,10 @@
       <c r="D183" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E183" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F183" s="28" t="s">
+      <c r="E183" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F183" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G183" s="3"/>
@@ -9329,10 +6715,10 @@
       <c r="D184" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E184" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F184" s="28" t="s">
+      <c r="E184" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F184" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G184" s="3"/>
@@ -9355,7 +6741,7 @@
         <v>72</v>
       </c>
       <c r="G185" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="H185" s="6">
         <v>2</v>
@@ -9506,10 +6892,10 @@
       <c r="D194" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E194" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F194" s="28" t="s">
+      <c r="E194" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F194" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G194" s="3"/>
@@ -9522,10 +6908,10 @@
       <c r="D195" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E195" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F195" s="28" t="s">
+      <c r="E195" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F195" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G195" s="3"/>
@@ -9538,10 +6924,10 @@
       <c r="D196" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E196" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F196" s="28" t="s">
+      <c r="E196" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F196" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G196" s="3"/>
@@ -9554,10 +6940,10 @@
       <c r="D197" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E197" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F197" s="28" t="s">
+      <c r="E197" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F197" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G197" s="3"/>
@@ -9570,10 +6956,10 @@
       <c r="D198" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E198" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F198" s="28" t="s">
+      <c r="E198" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F198" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G198" s="3"/>
@@ -9587,10 +6973,10 @@
       <c r="D199" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E199" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F199" s="28" t="s">
+      <c r="E199" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F199" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G199" s="3"/>
@@ -9604,10 +6990,10 @@
       <c r="D200" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E200" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F200" s="28" t="s">
+      <c r="E200" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F200" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G200" s="3"/>
@@ -9623,10 +7009,10 @@
       <c r="D201" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E201" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F201" s="28" t="s">
+      <c r="E201" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F201" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G201" s="3" t="s">
@@ -9641,10 +7027,10 @@
       <c r="D202" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E202" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F202" s="28" t="s">
+      <c r="E202" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F202" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G202" s="3"/>
@@ -9657,10 +7043,10 @@
       <c r="D203" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E203" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F203" s="28" t="s">
+      <c r="E203" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F203" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G203" s="3"/>
@@ -9673,10 +7059,10 @@
       <c r="D204" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E204" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F204" s="28" t="s">
+      <c r="E204" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F204" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G204" s="3"/>
@@ -9689,10 +7075,10 @@
       <c r="D205" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E205" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F205" s="28" t="s">
+      <c r="E205" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F205" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G205" s="3"/>
@@ -9705,10 +7091,10 @@
       <c r="D206" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E206" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F206" s="28" t="s">
+      <c r="E206" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F206" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G206" s="3"/>
@@ -9722,10 +7108,10 @@
       <c r="D207" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E207" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F207" s="28" t="s">
+      <c r="E207" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F207" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G207" s="3"/>
@@ -9738,10 +7124,10 @@
       <c r="D208" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E208" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F208" s="28" t="s">
+      <c r="E208" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F208" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G208" s="3"/>
@@ -9780,10 +7166,10 @@
       <c r="D210" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E210" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F210" s="28" t="s">
+      <c r="E210" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F210" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G210" s="3" t="s">
@@ -9798,10 +7184,10 @@
       <c r="D211" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E211" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F211" s="28" t="s">
+      <c r="E211" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F211" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G211" s="3"/>
@@ -9814,10 +7200,10 @@
       <c r="D212" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E212" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F212" s="28" t="s">
+      <c r="E212" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F212" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G212" s="3"/>
@@ -9830,10 +7216,10 @@
       <c r="D213" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E213" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F213" s="28" t="s">
+      <c r="E213" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F213" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G213" s="3"/>
@@ -9846,10 +7232,10 @@
       <c r="D214" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E214" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F214" s="28" t="s">
+      <c r="E214" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F214" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G214" s="3"/>
@@ -9862,10 +7248,10 @@
       <c r="D215" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E215" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F215" s="28" t="s">
+      <c r="E215" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F215" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G215" s="3"/>
@@ -9879,10 +7265,10 @@
       <c r="D216" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E216" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F216" s="28" t="s">
+      <c r="E216" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F216" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G216" s="3"/>
@@ -9895,10 +7281,10 @@
       <c r="D217" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E217" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F217" s="28" t="s">
+      <c r="E217" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F217" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G217" s="3"/>
@@ -9921,7 +7307,7 @@
         <v>72</v>
       </c>
       <c r="G218" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="H218" s="6">
         <v>3</v>
@@ -10072,10 +7458,10 @@
       <c r="D227" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E227" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F227" s="28" t="s">
+      <c r="E227" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F227" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G227" s="3"/>
@@ -10088,10 +7474,10 @@
       <c r="D228" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E228" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F228" s="28" t="s">
+      <c r="E228" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F228" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G228" s="3"/>
@@ -10104,10 +7490,10 @@
       <c r="D229" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E229" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F229" s="28" t="s">
+      <c r="E229" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F229" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G229" s="3"/>
@@ -10120,10 +7506,10 @@
       <c r="D230" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E230" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F230" s="28" t="s">
+      <c r="E230" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F230" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G230" s="3"/>
@@ -10136,10 +7522,10 @@
       <c r="D231" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E231" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F231" s="28" t="s">
+      <c r="E231" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F231" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G231" s="3"/>
@@ -10153,10 +7539,10 @@
       <c r="D232" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E232" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F232" s="28" t="s">
+      <c r="E232" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F232" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G232" s="3"/>
@@ -10170,10 +7556,10 @@
       <c r="D233" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E233" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F233" s="28" t="s">
+      <c r="E233" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F233" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G233" s="3"/>
@@ -10189,7 +7575,7 @@
       <c r="D234" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E234" s="28" t="s">
+      <c r="E234" s="27" t="s">
         <v>124</v>
       </c>
       <c r="F234" s="23" t="s">
@@ -10207,10 +7593,10 @@
       <c r="D235" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E235" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F235" s="28" t="s">
+      <c r="E235" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F235" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G235" s="3"/>
@@ -10223,10 +7609,10 @@
       <c r="D236" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E236" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F236" s="28" t="s">
+      <c r="E236" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F236" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G236" s="3"/>
@@ -10239,10 +7625,10 @@
       <c r="D237" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E237" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F237" s="28" t="s">
+      <c r="E237" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F237" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G237" s="3"/>
@@ -10255,10 +7641,10 @@
       <c r="D238" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E238" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F238" s="28" t="s">
+      <c r="E238" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F238" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G238" s="3"/>
@@ -10271,10 +7657,10 @@
       <c r="D239" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E239" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F239" s="28" t="s">
+      <c r="E239" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F239" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G239" s="3"/>
@@ -10288,10 +7674,10 @@
       <c r="D240" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E240" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F240" s="28" t="s">
+      <c r="E240" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F240" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G240" s="3"/>
@@ -10305,10 +7691,10 @@
       <c r="D241" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E241" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F241" s="28" t="s">
+      <c r="E241" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F241" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G241" s="3"/>
@@ -10342,10 +7728,10 @@
       <c r="D243" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E243" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F243" s="28" t="s">
+      <c r="E243" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F243" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G243" s="3"/>
@@ -10358,10 +7744,10 @@
       <c r="D244" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E244" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F244" s="28" t="s">
+      <c r="E244" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F244" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G244" s="3"/>
@@ -10374,10 +7760,10 @@
       <c r="D245" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E245" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F245" s="28" t="s">
+      <c r="E245" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F245" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G245" s="3"/>
@@ -10390,10 +7776,10 @@
       <c r="D246" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E246" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F246" s="28" t="s">
+      <c r="E246" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F246" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G246" s="3"/>
@@ -10406,10 +7792,10 @@
       <c r="D247" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E247" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F247" s="28" t="s">
+      <c r="E247" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F247" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G247" s="3"/>
@@ -10423,10 +7809,10 @@
       <c r="D248" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E248" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F248" s="28" t="s">
+      <c r="E248" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F248" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G248" s="3"/>
@@ -10440,10 +7826,10 @@
       <c r="D249" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E249" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F249" s="28" t="s">
+      <c r="E249" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F249" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G249" s="3"/>
@@ -10459,10 +7845,10 @@
       <c r="D250" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E250" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F250" s="28" t="s">
+      <c r="E250" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F250" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G250" s="3" t="s">
@@ -10477,10 +7863,10 @@
       <c r="D251" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E251" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F251" s="28" t="s">
+      <c r="E251" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F251" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G251" s="3"/>
@@ -10493,10 +7879,10 @@
       <c r="D252" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E252" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F252" s="28" t="s">
+      <c r="E252" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F252" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G252" s="3"/>
@@ -10509,10 +7895,10 @@
       <c r="D253" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E253" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F253" s="28" t="s">
+      <c r="E253" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F253" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G253" s="3"/>
@@ -10525,10 +7911,10 @@
       <c r="D254" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E254" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F254" s="28" t="s">
+      <c r="E254" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F254" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G254" s="3"/>
@@ -10541,10 +7927,10 @@
       <c r="D255" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E255" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F255" s="28" t="s">
+      <c r="E255" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F255" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G255" s="3"/>
@@ -10558,10 +7944,10 @@
       <c r="D256" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E256" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F256" s="28" t="s">
+      <c r="E256" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F256" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G256" s="3"/>
@@ -10574,10 +7960,10 @@
       <c r="D257" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E257" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F257" s="28" t="s">
+      <c r="E257" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F257" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G257" s="3"/>
@@ -10623,7 +8009,7 @@
         <v>72</v>
       </c>
       <c r="G259" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="H259" s="6">
         <v>2</v>
@@ -10756,7 +8142,7 @@
         <v>72</v>
       </c>
       <c r="G267" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H267" s="6">
         <v>2</v>
@@ -10908,10 +8294,10 @@
       <c r="D276" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E276" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F276" s="28" t="s">
+      <c r="E276" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F276" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G276" s="3"/>
@@ -10925,10 +8311,10 @@
       <c r="D277" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E277" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F277" s="28" t="s">
+      <c r="E277" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F277" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G277" s="3"/>
@@ -10942,10 +8328,10 @@
       <c r="D278" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E278" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F278" s="28" t="s">
+      <c r="E278" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F278" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G278" s="3"/>
@@ -10959,10 +8345,10 @@
       <c r="D279" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E279" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F279" s="28" t="s">
+      <c r="E279" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F279" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G279" s="3"/>
@@ -10976,10 +8362,10 @@
       <c r="D280" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E280" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F280" s="28" t="s">
+      <c r="E280" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F280" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G280" s="3"/>
@@ -10993,10 +8379,10 @@
       <c r="D281" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E281" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F281" s="28" t="s">
+      <c r="E281" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F281" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G281" s="3"/>
@@ -11010,10 +8396,10 @@
       <c r="D282" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E282" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F282" s="28" t="s">
+      <c r="E282" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F282" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G282" s="3"/>
@@ -11029,10 +8415,10 @@
       <c r="D283" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E283" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F283" s="30" t="s">
+      <c r="E283" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F283" s="29" t="s">
         <v>72</v>
       </c>
       <c r="G283" s="3" t="s">
@@ -11047,10 +8433,10 @@
       <c r="D284" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E284" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F284" s="28" t="s">
+      <c r="E284" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F284" s="27" t="s">
         <v>124</v>
       </c>
       <c r="H284" s="6">
@@ -11062,10 +8448,10 @@
       <c r="D285" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E285" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F285" s="28" t="s">
+      <c r="E285" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F285" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G285" s="3"/>
@@ -11078,10 +8464,10 @@
       <c r="D286" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E286" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F286" s="28" t="s">
+      <c r="E286" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F286" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G286" s="3"/>
@@ -11094,10 +8480,10 @@
       <c r="D287" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E287" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F287" s="28" t="s">
+      <c r="E287" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F287" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G287" s="3"/>
@@ -11110,10 +8496,10 @@
       <c r="D288" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E288" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F288" s="28" t="s">
+      <c r="E288" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F288" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G288" s="3"/>
@@ -11127,10 +8513,10 @@
       <c r="D289" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E289" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F289" s="28" t="s">
+      <c r="E289" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F289" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G289" s="3"/>
@@ -11144,10 +8530,10 @@
       <c r="D290" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E290" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F290" s="28" t="s">
+      <c r="E290" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F290" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G290" s="3"/>
@@ -11163,7 +8549,7 @@
       <c r="D291" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E291" s="28" t="s">
+      <c r="E291" s="27" t="s">
         <v>124</v>
       </c>
       <c r="F291" s="23" t="s">
@@ -11181,10 +8567,10 @@
       <c r="D292" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E292" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F292" s="28" t="s">
+      <c r="E292" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F292" s="27" t="s">
         <v>124</v>
       </c>
       <c r="H292" s="6">
@@ -11196,10 +8582,10 @@
       <c r="D293" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E293" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F293" s="28" t="s">
+      <c r="E293" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F293" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G293" s="3"/>
@@ -11212,10 +8598,10 @@
       <c r="D294" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E294" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F294" s="28" t="s">
+      <c r="E294" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F294" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G294" s="3"/>
@@ -11228,10 +8614,10 @@
       <c r="D295" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E295" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F295" s="28" t="s">
+      <c r="E295" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F295" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G295" s="3"/>
@@ -11244,10 +8630,10 @@
       <c r="D296" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E296" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F296" s="28" t="s">
+      <c r="E296" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F296" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G296" s="3"/>
@@ -11261,10 +8647,10 @@
       <c r="D297" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E297" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F297" s="28" t="s">
+      <c r="E297" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F297" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G297" s="3"/>
@@ -11277,10 +8663,10 @@
       <c r="D298" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E298" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F298" s="28" t="s">
+      <c r="E298" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F298" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G298" s="3"/>
@@ -11319,10 +8705,10 @@
       <c r="D300" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E300" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F300" s="28" t="s">
+      <c r="E300" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F300" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G300" s="3" t="s">
@@ -11337,10 +8723,10 @@
       <c r="D301" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E301" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F301" s="28" t="s">
+      <c r="E301" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F301" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G301" s="3"/>
@@ -11353,10 +8739,10 @@
       <c r="D302" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E302" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F302" s="28" t="s">
+      <c r="E302" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F302" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G302" s="3"/>
@@ -11369,10 +8755,10 @@
       <c r="D303" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E303" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F303" s="28" t="s">
+      <c r="E303" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F303" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G303" s="3"/>
@@ -11385,10 +8771,10 @@
       <c r="D304" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E304" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F304" s="28" t="s">
+      <c r="E304" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F304" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G304" s="3"/>
@@ -11401,10 +8787,10 @@
       <c r="D305" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E305" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F305" s="28" t="s">
+      <c r="E305" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F305" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G305" s="3"/>
@@ -11418,10 +8804,10 @@
       <c r="D306" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E306" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F306" s="28" t="s">
+      <c r="E306" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F306" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G306" s="3"/>
@@ -11434,10 +8820,10 @@
       <c r="D307" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E307" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F307" s="28" t="s">
+      <c r="E307" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F307" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G307" s="3"/>
@@ -11460,7 +8846,7 @@
         <v>72</v>
       </c>
       <c r="G308" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="H308" s="6">
         <v>3</v>
@@ -11611,10 +8997,10 @@
       <c r="D317" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E317" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F317" s="28" t="s">
+      <c r="E317" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F317" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G317" s="3"/>
@@ -11627,10 +9013,10 @@
       <c r="D318" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E318" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F318" s="28" t="s">
+      <c r="E318" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F318" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G318" s="3"/>
@@ -11643,10 +9029,10 @@
       <c r="D319" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E319" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F319" s="28" t="s">
+      <c r="E319" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F319" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G319" s="3"/>
@@ -11659,10 +9045,10 @@
       <c r="D320" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E320" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F320" s="28" t="s">
+      <c r="E320" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F320" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G320" s="3"/>
@@ -11675,10 +9061,10 @@
       <c r="D321" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E321" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F321" s="28" t="s">
+      <c r="E321" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F321" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G321" s="3"/>
@@ -11692,10 +9078,10 @@
       <c r="D322" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E322" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F322" s="28" t="s">
+      <c r="E322" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F322" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G322" s="3"/>
@@ -11709,10 +9095,10 @@
       <c r="D323" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E323" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F323" s="28" t="s">
+      <c r="E323" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F323" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G323" s="3"/>
@@ -11728,7 +9114,7 @@
       <c r="D324" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E324" s="28" t="s">
+      <c r="E324" s="27" t="s">
         <v>124</v>
       </c>
       <c r="F324" s="23" t="s">
@@ -11746,10 +9132,10 @@
       <c r="D325" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E325" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F325" s="28" t="s">
+      <c r="E325" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F325" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G325" s="3"/>
@@ -11762,10 +9148,10 @@
       <c r="D326" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E326" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F326" s="28" t="s">
+      <c r="E326" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F326" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G326" s="3"/>
@@ -11778,10 +9164,10 @@
       <c r="D327" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E327" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F327" s="28" t="s">
+      <c r="E327" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F327" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G327" s="3"/>
@@ -11794,10 +9180,10 @@
       <c r="D328" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E328" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F328" s="28" t="s">
+      <c r="E328" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F328" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G328" s="3"/>
@@ -11810,10 +9196,10 @@
       <c r="D329" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E329" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F329" s="28" t="s">
+      <c r="E329" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F329" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G329" s="3"/>
@@ -11827,10 +9213,10 @@
       <c r="D330" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E330" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F330" s="28" t="s">
+      <c r="E330" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F330" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G330" s="3"/>
@@ -11844,10 +9230,10 @@
       <c r="D331" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E331" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F331" s="28" t="s">
+      <c r="E331" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F331" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G331" s="3"/>
@@ -11881,10 +9267,10 @@
       <c r="D333" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E333" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F333" s="28" t="s">
+      <c r="E333" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F333" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G333" s="3"/>
@@ -11897,10 +9283,10 @@
       <c r="D334" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E334" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F334" s="28" t="s">
+      <c r="E334" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F334" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G334" s="3"/>
@@ -11913,10 +9299,10 @@
       <c r="D335" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E335" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F335" s="28" t="s">
+      <c r="E335" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F335" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G335" s="3"/>
@@ -11929,10 +9315,10 @@
       <c r="D336" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E336" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F336" s="28" t="s">
+      <c r="E336" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F336" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G336" s="3"/>
@@ -11945,10 +9331,10 @@
       <c r="D337" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E337" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F337" s="28" t="s">
+      <c r="E337" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F337" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G337" s="3"/>
@@ -11962,10 +9348,10 @@
       <c r="D338" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E338" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F338" s="28" t="s">
+      <c r="E338" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F338" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G338" s="3"/>
@@ -11978,10 +9364,10 @@
       <c r="D339" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E339" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F339" s="28" t="s">
+      <c r="E339" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F339" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G339" s="3"/>
@@ -12016,10 +9402,10 @@
       <c r="D341" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E341" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F341" s="28" t="s">
+      <c r="E341" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F341" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G341" s="3"/>
@@ -12033,10 +9419,10 @@
       <c r="D342" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E342" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F342" s="28" t="s">
+      <c r="E342" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F342" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G342" s="3"/>
@@ -12050,10 +9436,10 @@
       <c r="D343" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E343" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F343" s="28" t="s">
+      <c r="E343" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F343" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G343" s="3"/>
@@ -12067,10 +9453,10 @@
       <c r="D344" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E344" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F344" s="28" t="s">
+      <c r="E344" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F344" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G344" s="3"/>
@@ -12084,10 +9470,10 @@
       <c r="D345" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E345" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F345" s="28" t="s">
+      <c r="E345" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F345" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G345" s="3"/>
@@ -12101,10 +9487,10 @@
       <c r="D346" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E346" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F346" s="28" t="s">
+      <c r="E346" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F346" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G346" s="3"/>
@@ -12118,10 +9504,10 @@
       <c r="D347" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E347" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F347" s="28" t="s">
+      <c r="E347" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F347" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G347" s="3"/>
@@ -12160,10 +9546,10 @@
       <c r="D349" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E349" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F349" s="28" t="s">
+      <c r="E349" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F349" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G349" s="3" t="s">
@@ -12178,10 +9564,10 @@
       <c r="D350" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E350" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F350" s="28" t="s">
+      <c r="E350" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F350" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G350" s="3"/>
@@ -12194,10 +9580,10 @@
       <c r="D351" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E351" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F351" s="28" t="s">
+      <c r="E351" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F351" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G351" s="3"/>
@@ -12210,10 +9596,10 @@
       <c r="D352" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E352" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F352" s="28" t="s">
+      <c r="E352" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F352" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G352" s="3"/>
@@ -12226,10 +9612,10 @@
       <c r="D353" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E353" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F353" s="28" t="s">
+      <c r="E353" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F353" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G353" s="3"/>
@@ -12242,10 +9628,10 @@
       <c r="D354" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E354" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F354" s="28" t="s">
+      <c r="E354" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F354" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G354" s="3"/>
@@ -12259,10 +9645,10 @@
       <c r="D355" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E355" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F355" s="28" t="s">
+      <c r="E355" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F355" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G355" s="3"/>
@@ -12275,10 +9661,10 @@
       <c r="D356" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E356" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F356" s="28" t="s">
+      <c r="E356" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F356" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G356" s="3"/>
@@ -12301,7 +9687,7 @@
         <v>72</v>
       </c>
       <c r="G357" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="H357" s="6">
         <v>3</v>
@@ -12452,10 +9838,10 @@
       <c r="D366" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E366" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F366" s="28" t="s">
+      <c r="E366" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F366" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G366" s="3"/>
@@ -12468,10 +9854,10 @@
       <c r="D367" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E367" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F367" s="28" t="s">
+      <c r="E367" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F367" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G367" s="3"/>
@@ -12484,10 +9870,10 @@
       <c r="D368" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E368" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F368" s="28" t="s">
+      <c r="E368" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F368" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G368" s="3"/>
@@ -12500,10 +9886,10 @@
       <c r="D369" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E369" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F369" s="28" t="s">
+      <c r="E369" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F369" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G369" s="3"/>
@@ -12516,10 +9902,10 @@
       <c r="D370" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E370" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F370" s="28" t="s">
+      <c r="E370" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F370" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G370" s="3"/>
@@ -12533,10 +9919,10 @@
       <c r="D371" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E371" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F371" s="28" t="s">
+      <c r="E371" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F371" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G371" s="3"/>
@@ -12550,10 +9936,10 @@
       <c r="D372" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E372" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F372" s="28" t="s">
+      <c r="E372" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F372" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G372" s="3"/>
@@ -12569,7 +9955,7 @@
       <c r="D373" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E373" s="28" t="s">
+      <c r="E373" s="27" t="s">
         <v>124</v>
       </c>
       <c r="F373" s="23" t="s">
@@ -12587,10 +9973,10 @@
       <c r="D374" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E374" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F374" s="28" t="s">
+      <c r="E374" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F374" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G374" s="3"/>
@@ -12603,10 +9989,10 @@
       <c r="D375" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E375" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F375" s="28" t="s">
+      <c r="E375" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F375" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G375" s="3"/>
@@ -12619,10 +10005,10 @@
       <c r="D376" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E376" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F376" s="28" t="s">
+      <c r="E376" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F376" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G376" s="3"/>
@@ -12635,10 +10021,10 @@
       <c r="D377" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E377" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F377" s="28" t="s">
+      <c r="E377" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F377" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G377" s="3"/>
@@ -12651,10 +10037,10 @@
       <c r="D378" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E378" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F378" s="28" t="s">
+      <c r="E378" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F378" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G378" s="3"/>
@@ -12668,10 +10054,10 @@
       <c r="D379" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E379" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F379" s="28" t="s">
+      <c r="E379" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F379" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G379" s="3"/>
@@ -12685,10 +10071,10 @@
       <c r="D380" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E380" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F380" s="28" t="s">
+      <c r="E380" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F380" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G380" s="3"/>
@@ -12722,10 +10108,10 @@
       <c r="D382" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E382" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F382" s="28" t="s">
+      <c r="E382" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F382" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G382" s="3"/>
@@ -12738,10 +10124,10 @@
       <c r="D383" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E383" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F383" s="28" t="s">
+      <c r="E383" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F383" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G383" s="3"/>
@@ -12754,10 +10140,10 @@
       <c r="D384" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E384" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F384" s="28" t="s">
+      <c r="E384" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F384" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G384" s="3"/>
@@ -12770,10 +10156,10 @@
       <c r="D385" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E385" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F385" s="28" t="s">
+      <c r="E385" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F385" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G385" s="3"/>
@@ -12786,10 +10172,10 @@
       <c r="D386" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E386" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F386" s="28" t="s">
+      <c r="E386" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F386" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G386" s="3"/>
@@ -12803,10 +10189,10 @@
       <c r="D387" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E387" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F387" s="28" t="s">
+      <c r="E387" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F387" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G387" s="3"/>
@@ -12819,10 +10205,10 @@
       <c r="D388" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E388" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F388" s="28" t="s">
+      <c r="E388" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F388" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G388" s="3"/>
@@ -12857,10 +10243,10 @@
       <c r="D390" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E390" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F390" s="28" t="s">
+      <c r="E390" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F390" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G390" s="3"/>
@@ -12874,10 +10260,10 @@
       <c r="D391" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E391" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F391" s="28" t="s">
+      <c r="E391" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F391" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G391" s="3"/>
@@ -12891,10 +10277,10 @@
       <c r="D392" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E392" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F392" s="28" t="s">
+      <c r="E392" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F392" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G392" s="3"/>
@@ -12908,10 +10294,10 @@
       <c r="D393" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E393" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F393" s="28" t="s">
+      <c r="E393" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F393" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G393" s="3"/>
@@ -12925,10 +10311,10 @@
       <c r="D394" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E394" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F394" s="28" t="s">
+      <c r="E394" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F394" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G394" s="3"/>
@@ -12942,10 +10328,10 @@
       <c r="D395" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E395" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F395" s="28" t="s">
+      <c r="E395" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F395" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G395" s="3"/>
@@ -12959,10 +10345,10 @@
       <c r="D396" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E396" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F396" s="28" t="s">
+      <c r="E396" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F396" s="27" t="s">
         <v>124</v>
       </c>
       <c r="G396" s="3"/>
@@ -12977,7 +10363,7 @@
       </c>
     </row>
     <row r="398" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="H398" s="29">
+      <c r="H398" s="28">
         <f>ROUNDUP(H397*1.3,0)</f>
         <v>462</v>
       </c>
@@ -13027,10 +10413,10 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B2" s="41" t="s">
+      <c r="B2" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="41"/>
+      <c r="C2" s="33"/>
       <c r="D2" s="5" t="s">
         <v>0</v>
       </c>
@@ -13053,7 +10439,7 @@
       </c>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B4" s="35" t="s">
+      <c r="B4" s="30" t="s">
         <v>30</v>
       </c>
       <c r="C4" s="2" t="s">
@@ -13067,7 +10453,7 @@
       </c>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B5" s="36"/>
+      <c r="B5" s="31"/>
       <c r="C5" s="2" t="s">
         <v>29</v>
       </c>
@@ -13079,7 +10465,7 @@
       </c>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B6" s="37"/>
+      <c r="B6" s="32"/>
       <c r="C6" s="3" t="s">
         <v>21</v>
       </c>
@@ -13091,7 +10477,7 @@
       </c>
     </row>
     <row r="7" spans="2:6" ht="72" x14ac:dyDescent="0.45">
-      <c r="B7" s="33" t="s">
+      <c r="B7" s="34" t="s">
         <v>4</v>
       </c>
       <c r="C7" s="3" t="s">
@@ -13105,7 +10491,7 @@
       </c>
     </row>
     <row r="8" spans="2:6" ht="180" x14ac:dyDescent="0.45">
-      <c r="B8" s="33"/>
+      <c r="B8" s="34"/>
       <c r="C8" s="3" t="s">
         <v>22</v>
       </c>
@@ -13139,16 +10525,16 @@
       </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B10" s="35" t="s">
+      <c r="B10" s="30" t="s">
         <v>15</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="38" t="s">
+      <c r="D10" s="36" t="s">
         <v>42</v>
       </c>
-      <c r="E10" s="35">
+      <c r="E10" s="30">
         <f>240/8</f>
         <v>30</v>
       </c>
@@ -13157,23 +10543,23 @@
       </c>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B11" s="36"/>
+      <c r="B11" s="31"/>
       <c r="C11" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D11" s="39"/>
-      <c r="E11" s="36"/>
+      <c r="D11" s="37"/>
+      <c r="E11" s="31"/>
     </row>
     <row r="12" spans="2:6" ht="44.4" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B12" s="37"/>
+      <c r="B12" s="32"/>
       <c r="C12" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D12" s="40"/>
-      <c r="E12" s="37"/>
+      <c r="D12" s="38"/>
+      <c r="E12" s="32"/>
     </row>
     <row r="13" spans="2:6" ht="72" x14ac:dyDescent="0.45">
-      <c r="B13" s="35" t="s">
+      <c r="B13" s="30" t="s">
         <v>12</v>
       </c>
       <c r="C13" s="2" t="s">
@@ -13187,7 +10573,7 @@
       </c>
     </row>
     <row r="14" spans="2:6" ht="36" x14ac:dyDescent="0.45">
-      <c r="B14" s="37"/>
+      <c r="B14" s="32"/>
       <c r="C14" s="2" t="s">
         <v>11</v>
       </c>
@@ -13199,7 +10585,7 @@
       </c>
     </row>
     <row r="15" spans="2:6" ht="342" x14ac:dyDescent="0.45">
-      <c r="B15" s="35" t="s">
+      <c r="B15" s="30" t="s">
         <v>8</v>
       </c>
       <c r="C15" s="2" t="s">
@@ -13217,7 +10603,7 @@
       </c>
     </row>
     <row r="16" spans="2:6" ht="342" x14ac:dyDescent="0.45">
-      <c r="B16" s="36"/>
+      <c r="B16" s="31"/>
       <c r="C16" s="2" t="s">
         <v>3</v>
       </c>
@@ -13233,7 +10619,7 @@
       </c>
     </row>
     <row r="17" spans="2:6" ht="342" x14ac:dyDescent="0.45">
-      <c r="B17" s="36"/>
+      <c r="B17" s="31"/>
       <c r="C17" s="2" t="s">
         <v>14</v>
       </c>
@@ -13249,7 +10635,7 @@
       </c>
     </row>
     <row r="18" spans="2:6" ht="54" x14ac:dyDescent="0.45">
-      <c r="B18" s="36"/>
+      <c r="B18" s="31"/>
       <c r="C18" s="2" t="s">
         <v>17</v>
       </c>
@@ -13265,7 +10651,7 @@
       </c>
     </row>
     <row r="19" spans="2:6" ht="270" x14ac:dyDescent="0.45">
-      <c r="B19" s="37"/>
+      <c r="B19" s="32"/>
       <c r="C19" s="2" t="s">
         <v>19</v>
       </c>
@@ -13281,13 +10667,13 @@
       </c>
     </row>
     <row r="20" spans="2:6" ht="36" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B20" s="33" t="s">
+      <c r="B20" s="34" t="s">
         <v>20</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D20" s="34" t="s">
+      <c r="D20" s="35" t="s">
         <v>26</v>
       </c>
       <c r="E20" s="2">
@@ -13295,11 +10681,11 @@
       </c>
     </row>
     <row r="21" spans="2:6" ht="36" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B21" s="33"/>
+      <c r="B21" s="34"/>
       <c r="C21" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D21" s="34"/>
+      <c r="D21" s="35"/>
       <c r="E21" s="2">
         <v>5</v>
       </c>
@@ -13328,16 +10714,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="B10:B12"/>
+    <mergeCell ref="D10:D12"/>
+    <mergeCell ref="B15:B19"/>
     <mergeCell ref="E10:E12"/>
     <mergeCell ref="B13:B14"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B4:B6"/>
     <mergeCell ref="B7:B8"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="B10:B12"/>
-    <mergeCell ref="D10:D12"/>
-    <mergeCell ref="B15:B19"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
